--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2311,7 +2311,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>RE-CHECKED 2026-09-13 (desktop 1440 + mobile 390): still open - aria-pressed is null on both halves of the toggle.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2394,7 +2398,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>RE-CHECKED 2026-09-13 signed in as Sales, on a COLLEAGUE's profile (TEST Limited), desktop and mobile: the 'n of 14 areas' block and the 'No access to ...' list are both still visible.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2477,22 +2485,26 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>RE-CHECKED 2026-09-13 (desktop 1440 + mobile 390): still open - all six fields have no label, aria-label or aria-labelledby.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2522,42 +2534,42 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Compared the desktop scope chips with their mobile counterparts, and confirmed the filtering itself works.</t>
+          <t>Focused a member card with the keyboard, pressed Enter to open the profile, pressed Escape, and read document.activeElement. Repeated as Owner and as Sales.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>The selected scope is exposed to assistive technology on both viewports.</t>
+          <t>Focus returns to the card that opened the dialog, so a keyboard user carries on from where they were.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>crm-scope-customers and crm-scope-suppliers both report aria-pressed=None; crm-scope-mobile-customers reports 'true' and crm-scope-mobile-suppliers 'false'.</t>
+          <t>Enter on team-member-&lt;id&gt; opens the dialog (pass); after Escape activeElement = BODY, as Owner and as Sales.</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>The desktop chip row was built separately from the mobile segmented control and did not carry the ARIA across.</t>
+          <t>The profile dialog has no DialogTrigger - it is opened by setting profileUser state - and MemberProfileDialog returns null the moment u is cleared, so the dialog is unmounted before Radix can restore focus to where it came from.</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -2565,32 +2577,32 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -2600,47 +2612,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Accessibility / tap target</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Opened Add customer and inspected every field for a programmatic label.</t>
+          <t>Measured the close control inside Add member on desktop and mobile.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Each field is named for assistive technology and keeps its name after the user types.</t>
+          <t>A close control is at least 24x24px (WCAG 2.5.8).</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>All six fields report labelled:false and the dialog's label count is zero. Four of the six also carry no data-testid, which makes them hard to assert on.</t>
+          <t>Add member close: 16x16 at 1440x900, 44x44 at 390x844.</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Placeholders are being used as labels throughout the app's forms.</t>
+          <t>components/ui/dialog.jsx renders DialogPrimitive.Close as a bare h-4 w-4 icon with no padding or minimum size.</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -2648,7 +2660,7 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2658,7 +2670,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2668,12 +2680,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -2683,42 +2695,42 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Redundancy</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Listed the buttons in the Add contact dialog.</t>
+          <t>Compared the desktop scope chips with their mobile counterparts, and confirmed the filtering itself works.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>One way to back out of the dialog.</t>
+          <t>The selected scope is exposed to assistive technology on both viewports.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Dialog buttons: Customer, Dealer, Supplier, More details, Cancel, Add contact, Close.</t>
+          <t>crm-scope-customers and crm-scope-suppliers both report aria-pressed=None; crm-scope-mobile-customers reports 'true' and crm-scope-mobile-suppliers 'false'.</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>A footer Cancel was added while the dialog primitive still renders its own close control.</t>
+          <t>The desktop chip row was built separately from the mobile segmented control and did not carry the ARIA across.</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2731,7 +2743,7 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CR-04</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2741,12 +2753,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Add contact menu (mobile)</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2754,9 +2766,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -2766,42 +2778,42 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Responsive / layout</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Tapped the + button in the CRM header on a 375px phone and measured where the menu it opens actually lands.</t>
+          <t>Opened Add customer and inspected every field for a programmatic label.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>The menu opens inside the screen with its options readable.</t>
+          <t>Each field is named for assistive technology and keeps its name after the user types.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Viewport 375px; the menu spans x=315 to x=615, width 300px, overflowing the right edge by 240px -- 80 per cent clipped. Each item is 290px wide starting at x=320, leaving 55px visible.</t>
+          <t>All six fields report labelled:false and the dialog's label count is zero. Four of the six also carry no data-testid, which makes them hard to assert on.</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>The menu is right-anchored to its trigger with a fixed 300px width and no collision handling, which is fine beside a desktop toolbar and wrong beside a button that already sits at the right edge of a phone.</t>
+          <t>Placeholders are being used as labels throughout the app's forms.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -2814,7 +2826,7 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CR-05</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2824,12 +2836,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Filter button (mobile)</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2837,9 +2849,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -2849,42 +2861,42 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Dead control</t>
+          <t>Redundancy</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Tapped the Filter control in the CRM header on a 375px phone and compared the page before and after.</t>
+          <t>Listed the buttons in the Add contact dialog.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>It reveals the status and sort controls, which desktop shows inline.</t>
+          <t>One way to back out of the dialog.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Before and after the tap: body text 746 chars both times, 356 elements both times, 0 dialogs, 0 menus, 0 sheets. crm-status-filter and crm-sort are present but measure 0x0.</t>
+          <t>Dialog buttons: Customer, Dealer, Supplier, More details, Cancel, Add contact, Close.</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>The control was given an icon and an aria-label but never wired to the state that reveals the filter row.</t>
+          <t>A footer Cancel was added while the dialog primitive still renders its own close control.</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -2897,7 +2909,7 @@
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>CR-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2907,7 +2919,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Add contact menu (mobile)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2917,12 +2929,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -2937,37 +2949,37 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Measured the card grid and every text node inside it at 375px.</t>
+          <t>Tapped the + button in the CRM header on a 375px phone and measured where the menu it opens actually lands.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>On a phone a contact list is readable, and a customer's name is not cut off.</t>
+          <t>The menu opens inside the screen with its options readable.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to '160.5px 160.5px' at a 375px viewport; 8 leaf text nodes have scrollWidth greater than clientWidth.</t>
+          <t>Viewport 375px; the menu spans x=315 to x=615, width 300px, overflowing the right edge by 240px -- 80 per cent clipped. Each item is 290px wide starting at x=320, leaving 55px visible.</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>The grid keeps two columns below the breakpoint where the content stops fitting.</t>
+          <t>The menu is right-anchored to its trigger with a fixed 300px width and no collision handling, which is fine beside a desktop toolbar and wrong beside a button that already sits at the right edge of a phone.</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -2980,7 +2992,7 @@
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>CR-05</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2990,22 +3002,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Filter button (mobile)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -3015,42 +3027,42 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Dead control</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Measured the colour of every primary button on the contact profile page and compared it with primaries elsewhere in the app.</t>
+          <t>Tapped the Filter control in the CRM header on a 375px phone and compared the page before and after.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>One primary colour across the product.</t>
+          <t>It reveals the status and sort controls, which desktop shows inline.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Log button background rgb(55,58,205) with white text; the app's primaries elsewhere measure rgb(12,12,13).</t>
+          <t>Before and after the tap: body text 746 chars both times, 356 elements both times, 0 dialogs, 0 menus, 0 sheets. crm-status-filter and crm-sort are present but measure 0x0.</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>An indigo accent from a different design direction survived on this screen when the rest of the app settled on ink.</t>
+          <t>The control was given an icon and an aria-label but never wired to the state that reveals the filter row.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3063,7 +3075,7 @@
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3073,7 +3085,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3098,42 +3110,42 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Data leak to UI</t>
+          <t>Responsive / layout</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Read the 'In progress' accordion on a contact profile where some pending deliveries have no due date.</t>
+          <t>Measured the card grid and every text node inside it at 375px.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>A missing due date is either omitted or says something a person can read.</t>
+          <t>On a phone a contact list is readable, and a customer's name is not cut off.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>ContactProfileMobile.jsx:215 renders {humanDate(d.due_date) || `Due ${d.due_date}`}. humanDate is dueLabel(iso)?.text || null, so a missing date returns null and the fallback interpolates the undefined value straight into the string.</t>
+          <t>grid-template-columns resolves to '160.5px 160.5px' at a 375px viewport; 8 leaf text nodes have scrollWidth greater than clientWidth.</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>The fallback was written for a date the humaniser cannot PARSE, but it also catches a date that is simply ABSENT, and prints it.</t>
+          <t>The grid keeps two columns below the breakpoint where the content stops fitting.</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3146,32 +3158,32 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>OP-01</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Team execution panel</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -3181,47 +3193,47 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Truthfulness</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Read the panel's own caption, then checked the service that produces the numbers underneath it.</t>
+          <t>Measured the colour of every primary button on the contact profile page and compared it with primaries elsewhere in the app.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>A page that states a time window applies it.</t>
+          <t>One primary colour across the product.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>The panel says 'Last 30 days - open anyone to see their full ops'. The service applies no date filter anywhere: tasks, decisions, invoices and the per-employee leaderboard are all queried for the whole tenant with no window at all. So an owner reads a colleague's score believing it reflects the last month, when it carries every task since the workspace opened -- somebody who was slow in August can never recover from it, and somebody who has improved this month does not show it.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py contains no created_at, no timedelta, no days= and no since; the only match for '30' is .to_list(3000). Live data spans 2026-08-08 to 2026-09-09 and all of it is counted.</t>
+          <t>Log button background rgb(55,58,205) with white text; the app's primaries elsewhere measure rgb(12,12,13).</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>The caption was written for an intended windowed metric that was never implemented, or was implemented and later dropped.</t>
+          <t>An indigo accent from a different design direction survived on this screen when the rest of the app settled on ink.</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Decide which is true and make them agree. A rolling window is the more useful of the two -- an operating score should recover when the business recovers -- so filter each query to the last 30 days and keep the caption. If all-time is deliberate, the caption has to say so.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (all queries); the caption is in pages/OperatingScore.js, team-execution section</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
@@ -3229,17 +3241,17 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>OP-02</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>'Do these first' on mobile</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3249,12 +3261,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -3264,47 +3276,47 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Responsive / layout</t>
+          <t>Data leak to UI</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Measured the page's primary call to action against the fixed dark band beneath it on a 375x812 phone.</t>
+          <t>Read the 'In progress' accordion on a contact profile where some pending deliveries have no due date.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>The list of what to do first is readable on a phone.</t>
+          <t>A missing due date is either omitted or says something a person can read.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>It is 90 per cent hidden. 'Do these first' occupies y=425 to 710, and a fixed black 'Team execution' band is pinned from y=454 to the bottom of the screen -- 374px, 46 per cent of the viewport -- covering 256 of its 285px. Scrolling does not help: the document itself does not scroll (scrollHeight equals clientHeight), and the element that does scroll is the dark band, not the page. So the three actions the page exists to recommend are permanently reduced to one visible line.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Band: position fixed, z-index 20, top 454, height 374 of an 812px viewport. Overlap with 'Do these first' measured at 256px. Document scrollHeight 812 = clientHeight 812.</t>
+          <t>ContactProfileMobile.jsx:215 renders {humanDate(d.due_date) || `Due ${d.due_date}`}. humanDate is dueLabel(iso)?.text || null, so a missing date returns null and the fallback interpolates the undefined value straight into the string.</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>A section styled as a full-bleed dark band on desktop keeps position fixed at mobile widths, where there is not room for both it and the content above it.</t>
+          <t>The fallback was written for a date the humaniser cannot PARSE, but it also catches a date that is simply ABSENT, and prints it.</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>On mobile the band should flow with the page rather than being pinned, so the score, the actions and the team list scroll as one column. If it must stay pinned, it needs to collapse to a handle the user can pull up.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (kr-dark-band team-execution section)</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -3312,7 +3324,7 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>OP-03</t>
+          <t>OP-01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -3322,7 +3334,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Team execution panel</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3347,42 +3359,42 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Truthfulness</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Recomputed all four legs from the raw records and compared with the API.</t>
+          <t>Read the panel's own caption, then checked the service that produces the numbers underneath it.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>A score meant to guide the next action responds when that action is taken.</t>
+          <t>A page that states a time window applies it.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Two of the four legs are pinned at the floor and carry no information. Execution reads 0 and Responsiveness reads 0. Responsiveness actually computes to -296 before clamping (100 - 16 complaints x 12 - 68 overdue x 3), so it would take closing 8 complaints AND clearing 33 overdue tasks before the number moves off zero by a single point. The page's own advice is 'Close 16 open complaints' -- doing all of that would leave the score exactly where it is. The owner gets no gradient at precisely the moment they most need one.</t>
+          <t>The panel says 'Last 30 days - open anyone to see their full ops'. The service applies no date filter anywhere: tasks, decisions, invoices and the per-employee leaderboard are all queried for the whole tenant with no window at all. So an owner reads a colleague's score believing it reflects the last month, when it carries every task since the workspace opened -- somebody who was slow in August can never recover from it, and somebody who has improved this month does not show it.</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>API: overall 19, execution 0, finance 57, sales 22, responsiveness 0. Recomputed from 148 tasks: done 11, open 130, overdue 68, completion 0.078; execution = clamp(7.8 - 20.9) = 0. Responsiveness = clamp(100-192-204) = 0.</t>
+          <t>services/operating_score.py contains no created_at, no timedelta, no days= and no since; the only match for '30' is .to_list(3000). Live data spans 2026-08-08 to 2026-09-09 and all of it is counted.</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Both legs subtract unbounded absolute penalties from 100 and then clamp at zero, so any moderately messy workspace saturates.</t>
+          <t>The caption was written for an intended windowed metric that was never implemented, or was implemented and later dropped.</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Score each leg as a bounded rate rather than a penalty subtracted from a constant, so the number always has somewhere to move. Where a leg really is at the floor, say 'below floor' rather than printing a 0 that looks like an empty metric. See ASK-19 for the wider redesign.</t>
+          <t>Decide which is true and make them agree. A rolling window is the more useful of the two -- an operating score should recover when the business recovers -- so filter each query to the last 30 days and keep the caption. If all-time is deliberate, the caption has to say so.</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and the responsiveness expression in _company_operating_view</t>
+          <t>services/operating_score.py (all queries); the caption is in pages/OperatingScore.js, team-execution section</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -3395,7 +3407,7 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>OP-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -3405,12 +3417,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>'Do these first' on mobile</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3418,9 +3430,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -3430,42 +3442,42 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Truthfulness</t>
+          <t>Responsive / layout</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Read what the Sales leg is computed from.</t>
+          <t>Measured the page's primary call to action against the fixed dark band beneath it on a 375x812 phone.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>A category called Sales reflects selling.</t>
+          <t>The list of what to do first is readable on a phone.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
+          <t>It is 90 per cent hidden. 'Do these first' occupies y=425 to 710, and a fixed black 'Team execution' band is pinned from y=454 to the bottom of the screen -- 374px, 46 per cent of the viewport -- covering 256 of its 285px. Scrolling does not help: the document itself does not scroll (scrollHeight equals clientHeight), and the element that does scroll is the dark band, not the page. So the three actions the page exists to recommend are permanently reduced to one visible line.</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>_score_sales(decisions) = approved/total*100. API Sales = 22 with total_decisions 77, approved 17.</t>
+          <t>Band: position fixed, z-index 20, top 454, height 374 of an 812px viewport. Overlap with 'Do these first' measured at 256px. Document scrollHeight 812 = clientHeight 812.</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>The leg was named for the business area it was meant to represent rather than the quantity actually available to compute.</t>
+          <t>A section styled as a full-bleed dark band on desktop keeps position fixed at mobile widths, where there is not room for both it and the content above it.</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
+          <t>On mobile the band should flow with the page rather than being pinned, so the score, the actions and the team list scroll as one column. If it must stay pinned, it needs to collapse to a handle the user can pull up.</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_sales</t>
+          <t>pages/OperatingScore.js (kr-dark-band team-execution section)</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -3478,7 +3490,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>OP-03</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3501,9 +3513,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -3518,37 +3530,37 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Traced where a single overdue task lands in the model.</t>
+          <t>Recomputed all four legs from the raw records and compared with the API.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Each fact is counted once.</t>
+          <t>A score meant to guide the next action responds when that action is taken.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
+          <t>Two of the four legs are pinned at the floor and carry no information. Execution reads 0 and Responsiveness reads 0. Responsiveness actually computes to -296 before clamping (100 - 16 complaints x 12 - 68 overdue x 3), so it would take closing 8 complaints AND clearing 33 overdue tasks before the number moves off zero by a single point. The page's own advice is 'Close 16 open complaints' -- doing all of that would leave the score exactly where it is. The owner gets no gradient at precisely the moment they most need one.</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>_score_execution applies overdue_ratio*40; the responsiveness expression applies overdue*3.</t>
+          <t>API: overall 19, execution 0, finance 57, sales 22, responsiveness 0. Recomputed from 148 tasks: done 11, open 130, overdue 68, completion 0.078; execution = clamp(7.8 - 20.9) = 0. Responsiveness = clamp(100-192-204) = 0.</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>The two legs were designed independently and both reached for the same signal.</t>
+          <t>Both legs subtract unbounded absolute penalties from 100 and then clamp at zero, so any moderately messy workspace saturates.</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
+          <t>Score each leg as a bounded rate rather than a penalty subtracted from a constant, so the number always has somewhere to move. Where a leg really is at the floor, say 'below floor' rather than printing a 0 that looks like an empty metric. See ASK-19 for the wider redesign.</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
+          <t>services/operating_score.py:_score_execution and the responsiveness expression in _company_operating_view</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -3561,7 +3573,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3571,7 +3583,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3596,42 +3608,42 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Truthfulness</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Checked how the penalties behave as a business grows.</t>
+          <t>Read what the Sales leg is computed from.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>The same performance scores the same at any size.</t>
+          <t>A category called Sales reflects selling.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>responsiveness = 100 - open_complaints*12 - overdue*3; finance = collected*100 - overdue_inv*5.</t>
+          <t>_score_sales(decisions) = approved/total*100. API Sales = 22 with total_decisions 77, approved 17.</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Fixed point-costs were chosen against an assumed small tenant.</t>
+          <t>The leg was named for the business area it was meant to represent rather than the quantity actually available to compute.</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_company_operating_view</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -3644,7 +3656,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3654,7 +3666,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3667,9 +3679,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -3684,37 +3696,37 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Read what each leg returns when its denominator is zero.</t>
+          <t>Traced where a single overdue task lands in the model.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>A workspace with no data reads as unknown, not as a grade.</t>
+          <t>Each fact is counted once.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>completion, approved_rate and collected all default to 0.7; enough_data = actionable &gt;= 3 or inv_count &gt; 0.</t>
+          <t>_score_execution applies overdue_ratio*40; the responsiveness expression applies overdue*3.</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>A neutral default was chosen so an empty tenant would not look alarming.</t>
+          <t>The two legs were designed independently and both reached for the same signal.</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -3727,7 +3739,7 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3737,12 +3749,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3750,9 +3762,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -3762,42 +3774,42 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Looked at how a zero-scoring category is drawn.</t>
+          <t>Checked how the penalties behave as a business grows.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>A bad score and a missing score look different.</t>
+          <t>The same performance scores the same at any size.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Desktop screenshot: Execution 0/100 and Responsiveness 0/100 with unfilled tracks, beside Finance 57 and Sales 22 with filled ones.</t>
+          <t>responsiveness = 100 - open_complaints*12 - overdue*3; finance = collected*100 - overdue_inv*5.</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>The bar encodes only the value, and zero has no visual form.</t>
+          <t>Fixed point-costs were chosen against an assumed small tenant.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -3810,7 +3822,7 @@
     <row r="39" ht="82" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>OP-09</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3820,12 +3832,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>'View all' links and the formula panel (mobile)</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3833,9 +3845,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -3845,42 +3857,42 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Responsive / accessibility</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Measured every remaining mobile control on the Ops page.</t>
+          <t>Read what each leg returns when its denominator is zero.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Links are big enough to tap, unobstructed, and the whole page is reachable.</t>
+          <t>A workspace with no data reads as unknown, not as a grade.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>View all: 61x20 at y=751, elementFromPoint returns dex-fab; second at y=947, outside the viewport. operating-formula-toggle: 223x44 at y=1153, inViewport false, and the automated sweep could not click it.</t>
+          <t>completion, approved_rate and collected all default to 0.7; enough_data = actionable &gt;= 3 or inv_count &gt; 0.</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>The same fixed-band layout as OP-02: the document does not scroll, so anything below the fold is unreachable rather than merely below.</t>
+          <t>A neutral default was chosen so an empty tenant would not look alarming.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -3893,32 +3905,32 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FN-01</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Every money figure</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -3928,42 +3940,42 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Localisation</t>
+          <t>Information design</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Read the rendered text of all six Overview tiles and compared it with what Intl produces for the same number in Indian grouping.</t>
+          <t>Looked at how a zero-scoring category is drawn.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>An India-first product groups rupees the Indian way, the same way everywhere.</t>
+          <t>A bad score and a missing score look different.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Tiles read 'Rs 2,685,000'; Intl.NumberFormat('en-IN') gives 'Rs 26,85,000'. Ledger.js:61 uses Intl.NumberFormat(undefined, ...).</t>
+          <t>Desktop screenshot: Execution 0/100 and Responsiveness 0/100 with unfilled tracks, beside Finance 57 and Sales 22 with filled ones.</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Ledger.js defines its own private fmt() with an undefined locale, instead of the shared helper. lib/format.js already exports inr(), which uses en-IN and whose own docstring reads: 'no component formats currency inline -- everything goes through here.' Finance is the component that does.</t>
+          <t>The bar encodes only the value, and zero has no visual form.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -3976,17 +3988,17 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FN-02</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero (mobile)</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3996,12 +4008,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -4011,42 +4023,42 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Truthfulness</t>
+          <t>Responsive / accessibility</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Compared the number under the 'This month' chip with the API figure and with the date range of the underlying records.</t>
+          <t>Measured every remaining mobile control on the Ops page.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>A figure captioned 'This month' covers this month.</t>
+          <t>Links are big enough to tap, unobstructed, and the whole page is reachable.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Hero binds {f(net)} where net = tt.net_profit; ledger_summary applies no date filter; sales invoices span 2026-06-14 to 2026-08-12.</t>
+          <t>View all: 61x20 at y=751, elementFromPoint returns dex-fab; second at y=947, outside the viewport. operating-formula-toggle: 223x44 at y=1153, inViewport false, and the automated sweep could not click it.</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>The chip was written for a windowed figure the endpoint does not provide.</t>
+          <t>The same fixed-band layout as OP-02: the document does not scroll, so anything below the fold is unreachable rather than merely below.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -4059,7 +4071,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FN-03</t>
+          <t>FN-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4069,12 +4081,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Revenue and Net profit trend badges (mobile)</t>
+          <t>Every money figure</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4094,42 +4106,42 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Wrong data</t>
+          <t>Localisation</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Traced the series behind each trend percentage and recomputed it.</t>
+          <t>Read the rendered text of all six Overview tiles and compared it with what Intl produces for the same number in Indian grouping.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>A trend shown beside Revenue describes revenue.</t>
+          <t>An India-first product groups rupees the Indian way, the same way everywhere.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
+          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>months = summary.by_month, which ledger_summary builds by summing EXPENSES per month. pct(839469, 1077500) = -22.1%, exactly what the UI shows. netPoints = months.map(m =&gt; Number(m.net ?? m.amount ?? 0)) -- by_month carries no 'net' key, so every point silently falls through to the expense amount.</t>
+          <t>Tiles read 'Rs 2,685,000'; Intl.NumberFormat('en-IN') gives 'Rs 26,85,000'. Ledger.js:61 uses Intl.NumberFormat(undefined, ...).</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>The frontend was written expecting by_month to carry a net figure per month. The backend never added one, and the ?? fallback turned a missing contract into a plausible-looking wrong number instead of an error.</t>
+          <t>Ledger.js defines its own private fmt() with an undefined locale, instead of the shared helper. lib/format.js already exports inr(), which uses en-IN and whose own docstring reads: 'no component formats currency inline -- everything goes through here.' Finance is the component that does.</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
+          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
+          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -4142,7 +4154,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>FN-02</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -4152,12 +4164,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>Net profit hero (mobile)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4165,9 +4177,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -4177,42 +4189,42 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Truthfulness</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Read what net_profit is composed of and compared it with a cash-basis calculation from the same records.</t>
+          <t>Compared the number under the 'This month' chip with the API figure and with the date range of the underlying records.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>A figure called net profit is close to what an owner means by it.</t>
+          <t>A figure captioned 'This month' covers this month.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>net_profit = revenue_billed - total_spend = 2685000 - 1946966 = 738034, verified against a recomputation. Cash basis (received - paid expenses) = 1936000 - 1291500 = 644500.</t>
+          <t>Hero binds {f(net)} where net = tt.net_profit; ledger_summary applies no date filter; sales invoices span 2026-06-14 to 2026-08-12.</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>A simple difference was given the accounting term that sits closest to it.</t>
+          <t>The chip was written for a windowed figure the endpoint does not provide.</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -4225,7 +4237,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>FN-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4235,12 +4247,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>Revenue and Net profit trend badges (mobile)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4248,9 +4260,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -4260,42 +4272,42 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Wrong data</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Checked ledger_summary for any date filtering.</t>
+          <t>Traced the series behind each trend percentage and recomputed it.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>A finance dashboard can show a period.</t>
+          <t>A trend shown beside Revenue describes revenue.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>ledger_summary contains no date filter; every find() is {tenant_id} only, .to_list(5000).</t>
+          <t>months = summary.by_month, which ledger_summary builds by summing EXPENSES per month. pct(839469, 1077500) = -22.1%, exactly what the UI shows. netPoints = months.map(m =&gt; Number(m.net ?? m.amount ?? 0)) -- by_month carries no 'net' key, so every point silently falls through to the expense amount.</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>The endpoint was built to summarise everything, and the period-aware UI arrived later.</t>
+          <t>The frontend was written expecting by_month to carry a net figure per month. The backend never added one, and the ?? fallback turned a missing contract into a plausible-looking wrong number instead of an error.</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -4308,22 +4320,22 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4331,9 +4343,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -4343,47 +4355,47 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Read what net_profit is composed of and compared it with a cash-basis calculation from the same records.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>A figure called net profit is close to what an owner means by it.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>net_profit = revenue_billed - total_spend = 2685000 - 1946966 = 738034, verified against a recomputation. Cash basis (received - paid expenses) = 1936000 - 1291500 = 644500.</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>A simple difference was given the accounting term that sits closest to it.</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -4391,17 +4403,17 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4414,9 +4426,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -4426,47 +4438,47 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Checked ledger_summary for any date filtering.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>A finance dashboard can show a period.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>ledger_summary contains no date filter; every find() is {tenant_id} only, .to_list(5000).</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>The endpoint was built to summarise everything, and the period-aware UI arrived later.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -4474,7 +4486,7 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -4484,17 +4496,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
@@ -4509,42 +4521,42 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Visual / layout</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Measured the grid that renders each role group on the team roster.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -4557,22 +4569,22 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4580,54 +4592,54 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Information design</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -4635,31 +4647,27 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
-        </is>
-      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-04</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Member profile dialog</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4679,42 +4687,42 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>Each control in a dialog is distinguishable by name.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -4724,95 +4732,269 @@
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
+          <t>VERIFIED FIXED 2026-09-13: the profile dialog now exposes ONE Close (36px desktop, 44px mobile) as Owner and as Sales; Team.js:572 hides the primitive's default close with [&amp;&gt;button.absolute]:hidden.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="82" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="82" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q50"/>
+  <autoFilter ref="A1:Q52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4823,7 +5005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8822,14 +9004,14 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Two visible buttons both named 'Close'</t>
+          <t>Was two buttons named 'Close'; re-checked 2026-09-13 - one Close as Owner and as Sales, both viewports</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9489,37 +9671,37 @@
     <row r="95" ht="82" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>T-300</t>
+          <t>T-230</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner + Sales</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>/crm loads directly with the contact list</t>
+          <t>Search filters by name, email and role, and says when nothing matches</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -9529,7 +9711,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>11 buyer cards; no redirect</t>
+          <t>'priya' 1 of 12; 'sharma.com' 5 of 12; 'production' 2 of 12 (role + email); 'zzqq' 0 of 12 with 'Nobody matches "zzqq".'; clearing restores all 12</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -9537,37 +9719,37 @@
     <row r="96" ht="82" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>T-301</t>
+          <t>T-231</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner + Sales</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>/crm loads and reflows to a single column</t>
+          <t>Every member card opens that member's profile</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -9577,7 +9759,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>207 visible elements, 22 interactive</t>
+          <t>12 of 12 on all four passes</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -9585,17 +9767,17 @@
     <row r="97" ht="82" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>T-302</t>
+          <t>T-232</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Page shell</t>
+          <t>Profile dialog - close</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -9605,17 +9787,17 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner + Sales</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>No horizontal overflow on either viewport</t>
+          <t>Close button, Escape and clicking outside all close the profile</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -9625,7 +9807,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>desktop 1440=1440, mobile 390=390</t>
+          <t>All three close it on both viewports</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -9633,37 +9815,37 @@
     <row r="98" ht="82" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>T-303</t>
+          <t>T-233</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>All controls</t>
+          <t>Profile dialog - fit + targets</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner + Sales</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Every control meets the 24px tap-target minimum</t>
+          <t>The dialog fits the screen and every control is at least 24px</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -9673,7 +9855,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>0 under 24px</t>
+          <t>Desktop 576px wide, mobile full width; Close 36px / 44px, Edit access and Get invite link 30-44px tall</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -9681,32 +9863,32 @@
     <row r="99" ht="82" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>T-304</t>
+          <t>T-234</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>All text</t>
+          <t>Profile dialog - keyboard</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner + Sales</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>All interactive text meets 4.5:1 contrast</t>
+          <t>Enter opens a card and focus returns to it on close</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -9714,32 +9896,36 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>0 below 4.5:1 on either viewport</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr"/>
+          <t>Enter opens it; after Escape focus is on &lt;body&gt;</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>TM-07</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="82" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>T-305</t>
+          <t>T-235</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>All controls</t>
+          <t>Edit access - stacking</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -9754,12 +9940,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Every button and link has an accessible name</t>
+          <t>Edit access opens over the profile, and one Escape returns to the profile</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -9769,7 +9955,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>0 unnamed; 0 images missing alt</t>
+          <t>2 dialogs open, title 'Edit access - Priya Nair'; one Escape leaves the profile open</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -9777,22 +9963,22 @@
     <row r="101" ht="82" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>T-306</t>
+          <t>T-236</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Edit access - permissions</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -9802,12 +9988,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Every control can be pressed without crashing the app</t>
+          <t>Every permission toggle flips and the menu preview follows it</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -9817,7 +10003,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>17 pressed incl. dialogs descended into; 0 crashes</t>
+          <t>14 of 14 toggles flip aria-pressed and back; preview chips for People, Company Brain, Capture, Workflows and Decision Desk strike and un-strike</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
@@ -9825,22 +10011,22 @@
     <row r="102" ht="82" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>T-307</t>
+          <t>T-237</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Edit access - promote to Owner</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -9850,12 +10036,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Every control can be pressed without crashing the app</t>
+          <t>Choosing Owner explains full access and asks before saving</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -9865,7 +10051,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>13 pressed incl. dialogs; 0 crashes</t>
+          <t>Grid swaps for the 'Full company access' note; Save asks 'This makes them a co-owner with FULL control...' (dismissed, nothing sent)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -9873,22 +10059,22 @@
     <row r="103" ht="82" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>T-308</t>
+          <t>T-238</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Scope chips</t>
+          <t>Edit access - failed save</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -9898,7 +10084,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Buyers / Suppliers filter the list correctly</t>
+          <t>A failed save says so and keeps the user's changes open</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -9913,7 +10099,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Buyers 11, Suppliers 6, back to Buyers 11</t>
+          <t>PATCH blocked -&gt; 'Something went wrong. Please try again.', dialog stays open</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
@@ -9921,22 +10107,22 @@
     <row r="104" ht="82" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>T-309</t>
+          <t>T-239</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Scope chips</t>
+          <t>Edit access - Save reachable</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -9946,12 +10132,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>The selected scope is exposed to assistive technology</t>
+          <t>Save access is visible without scrolling</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -9961,34 +10147,34 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Desktop chips have no aria-pressed; the mobile twins set it</t>
+          <t>Desktop: visible. Mobile: off-screen - dialog content 1,309px in a 758px window</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>ASK-14</t>
         </is>
       </c>
     </row>
     <row r="105" ht="82" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>T-310</t>
+          <t>T-240</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog</t>
+          <t>Add member - validation</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -9998,7 +10184,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Add customer opens a complete contact form</t>
+          <t>Each invalid submit is refused with its own reason</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -10013,7 +10199,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Type segmented control, name, company, phone, email, lifecycle, and a 'More details' disclosure for GSTIN</t>
+          <t>Empty -&gt; 'Name and email are required'; 3-char password -&gt; 'Set a 6+ char password...'; OTP with 5-digit phone -&gt; 'A valid mobile number is required...'</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
@@ -10021,22 +10207,22 @@
     <row r="106" ht="82" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>T-311</t>
+          <t>T-241</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog</t>
+          <t>Add member - login method</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -10046,12 +10232,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>The form fits without scrolling</t>
+          <t>Mobile OTP hides the password and makes the phone required; Password restores it</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -10061,7 +10247,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>576x541 with 539px of content - no scroll, unlike Team's 2.17 screens</t>
+          <t>Password field hidden, hint shown, placeholder 'Mobile number (required for OTP login)'; switching back restores the password field</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
@@ -10069,22 +10255,22 @@
     <row r="107" ht="82" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>T-312</t>
+          <t>T-242</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Add contact validation</t>
+          <t>Add member - role + manager</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -10094,7 +10280,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>An empty form is refused with a clear reason</t>
+          <t>Changing role applies that role's default access; manager list is populated</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -10109,7 +10295,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>No API call; dialog stayed open; 'Name is required'</t>
+          <t>Defaults: sales 6, production 6, finance 8 areas; manager select has 12 people + None</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
@@ -10117,22 +10303,22 @@
     <row r="108" ht="82" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>T-313</t>
+          <t>T-243</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog</t>
+          <t>Add member - failed save + reopen</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -10142,49 +10328,45 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Every field is programmatically labelled</t>
+          <t>A failed add keeps the form open; reopening starts blank</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Zero label elements in the dialog; all six fields placeholder-only</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>CR-02</t>
-        </is>
-      </c>
+          <t>POST blocked -&gt; error toast, dialog open; reopened with an empty name field</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
     </row>
     <row r="109" ht="82" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>T-314</t>
+          <t>T-244</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog</t>
+          <t>Add member - Add reachable</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -10194,12 +10376,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>One way to dismiss the dialog</t>
+          <t>The Add button is visible without scrolling</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Redundancy</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -10209,29 +10391,29 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Both a 'Cancel' button and a separate 'Close' X</t>
+          <t>Off-screen on both: content 1,026px in 808px (desktop), 1,535px in 758px (mobile, about two screens)</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>ASK-14</t>
         </is>
       </c>
     </row>
     <row r="110" ht="82" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>T-315</t>
+          <t>T-245</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Contact profile route</t>
+          <t>Dialog close size</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -10246,40 +10428,44 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>A contact card opens that contact's profile page</t>
+          <t>The dialog close control is at least 24px</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>crm-card-&lt;id&gt; navigates to /contacts/&lt;id&gt;; page renders, no errors</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr"/>
+          <t>Add member close is 16x16 on desktop (44x44 on mobile)</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>TM-08</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="82" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>T-316</t>
+          <t>T-246</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Read-only role</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -10289,17 +10475,17 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>No application errors and no failing API calls</t>
+          <t>A non-manager sees the roster read-only, with no edit or invite controls</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -10309,7 +10495,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me</t>
+          <t>Read-only banner shown; no Add member, Edit access or Get invite link; leave history shown on her own profile, hidden on a colleague's</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
@@ -10317,70 +10503,74 @@
     <row r="112" ht="82" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>T-317</t>
+          <t>T-247</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Scope chips</t>
+          <t>Read-only role - colleague access</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Switching to Suppliers reloads the list</t>
+          <t>A colleague's access list is not readable by a non-manager</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Buyers 11 -&gt; Suppliers 6, correct records, chip state flips</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr"/>
+          <t>Sales still reads TEST Limited's 'n of 14 areas' and 'No access to ...'</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>TM-05</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="82" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>T-318</t>
+          <t>T-248</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Sort control</t>
+          <t>Desktop scrolling (after 7d2fabe)</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -10390,12 +10580,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Sorting by outstanding puts the biggest debtor first</t>
+          <t>The roster scrolls and the last member is reachable</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -10405,7 +10595,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Krishna Garments Rs 4,00,000 first, then Nashik Traders Rs 64,000</t>
+          <t>&lt;main&gt; is now the scroll container (scrollTop 643 after one wheel); last card reachable; page title scrolls away, which is by design (common.js KM-25)</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
@@ -10413,22 +10603,22 @@
     <row r="114" ht="82" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>T-319</t>
+          <t>T-249</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Add contact menu</t>
+          <t>Get invite link - pressed</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -10438,7 +10628,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>The menu opens with its three options readable</t>
+          <t>Pressing Get invite link gives feedback and no token is minted by the test</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -10453,7 +10643,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>aria-expanded flips, role=menu appears: New Buyer, New Supplier, Import</t>
+          <t>POST blocked -&gt; 'Something went wrong. Please try again.', profile stays open. End-to-end generation still not run (see T-217)</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
@@ -10461,7 +10651,7 @@
     <row r="115" ht="82" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>T-320</t>
+          <t>T-300</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -10471,12 +10661,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Add contact menu</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -10486,34 +10676,30 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>The menu opens inside the screen</t>
+          <t>/crm loads directly with the contact list</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
-        </is>
-      </c>
-      <c r="H115" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>80% clipped off the right edge; only a 55px strip of icons is visible</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>CR-04</t>
-        </is>
-      </c>
+          <t>11 buyer cards; no redirect</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
     </row>
     <row r="116" ht="82" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>T-321</t>
+          <t>T-301</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -10523,12 +10709,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>New customer dialog</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -10538,12 +10724,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>The form is grouped and fits one screen</t>
+          <t>/crm loads and reflows to a single column</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -10553,7 +10739,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Sections Type / Identity / Contact / Classification, required marked, More details disclosure, Cancel beside Add contact, no scrolling</t>
+          <t>207 visible elements, 22 interactive</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr"/>
@@ -10561,7 +10747,7 @@
     <row r="117" ht="82" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>T-322</t>
+          <t>T-302</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -10571,12 +10757,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Filter control</t>
+          <t>Page shell</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -10586,34 +10772,30 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Filter reveals the status and sort controls</t>
+          <t>No horizontal overflow on either viewport</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H117" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Completely inert; status filter and sort exist at 0x0 so neither is reachable on a phone</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>CR-05</t>
-        </is>
-      </c>
+          <t>desktop 1440=1440, mobile 390=390</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
     </row>
     <row r="118" ht="82" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>T-323</t>
+          <t>T-303</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -10623,49 +10805,45 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Contact cards</t>
+          <t>All controls</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Customer names are readable on a phone</t>
+          <t>Every control meets the 24px tap-target minimum</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
-        </is>
-      </c>
-      <c r="H118" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Two-column grid at 160.5px per card truncates 8 text nodes including names</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>CR-06</t>
-        </is>
-      </c>
+          <t>0 under 24px</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
     </row>
     <row r="119" ht="82" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>T-324</t>
+          <t>T-304</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -10675,12 +10853,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Contact profile</t>
+          <t>All text</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -10690,12 +10868,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>A contact card opens a profile with money and activity</t>
+          <t>All interactive text meets 4.5:1 contrast</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -10705,7 +10883,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Outstanding / Total Billed / Total Paid / Open Complaints tiles, AI scoring, and inline activity logging</t>
+          <t>0 below 4.5:1 on either viewport</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
@@ -10713,7 +10891,7 @@
     <row r="120" ht="82" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>T-325</t>
+          <t>T-305</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -10723,49 +10901,45 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Contact profile</t>
+          <t>All controls</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Primary actions use the app's primary colour</t>
+          <t>Every button and link has an accessible name</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Design system</t>
-        </is>
-      </c>
-      <c r="H120" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Log button is indigo rgb(55,58,205); the app's primaries are rgb(12,12,13)</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>CR-07</t>
-        </is>
-      </c>
+          <t>0 unnamed; 0 images missing alt</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
     </row>
     <row r="121" ht="82" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>T-326</t>
+          <t>T-306</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -10775,12 +10949,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Mobile header controls</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -10790,12 +10964,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Header controls meet the 44px touch guideline</t>
+          <t>Every control can be pressed without crashing the app</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -10805,7 +10979,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Filter 44x44, Add contact 44x44, scope segment 166x44, bell 48x48</t>
+          <t>17 pressed incl. dialogs descended into; 0 crashes</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr"/>
@@ -10813,7 +10987,7 @@
     <row r="122" ht="82" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>T-327</t>
+          <t>T-307</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -10823,49 +10997,45 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - In progress</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>A missing due date does not print raw values to the user</t>
+          <t>Every control can be pressed without crashing the app</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H122" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>CR-08</t>
-        </is>
-      </c>
+          <t>13 pressed incl. dialogs; 0 crashes</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
     </row>
     <row r="123" ht="82" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>T-328</t>
+          <t>T-308</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -10875,59 +11045,55 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - In progress</t>
+          <t>Scope chips</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>The list distinguishes workflows from deliveries and rows are actionable</t>
+          <t>Buyers / Suppliers filter the list correctly</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
-        </is>
-      </c>
-      <c r="H123" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Two entity types share identical styling; titles repeat as bare 'sale'; a 'Delivered' row sits under 'In progress'; no row is tappable</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>ASK-18</t>
-        </is>
-      </c>
+          <t>Buyers 11, Suppliers 6, back to Buyers 11</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
     </row>
     <row r="124" ht="82" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>T-400</t>
+          <t>T-309</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Scope chips</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -10942,45 +11108,49 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>/operating-score loads with the score and all four categories</t>
+          <t>The selected scope is exposed to assistive technology</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Overall 19/100, four category cards, next-moves, quick stats</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="inlineStr"/>
+          <t>Desktop chips have no aria-pressed; the mobile twins set it</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>CR-01</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="82" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>T-401</t>
+          <t>T-310</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Add contact dialog</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -10990,12 +11160,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>/operating-score loads and reflows</t>
+          <t>Add customer opens a complete contact form</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -11005,7 +11175,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>317 visible elements, compact Key scores card</t>
+          <t>Type segmented control, name, company, phone, email, lifecycle, and a 'More details' disclosure for GSTIN</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr"/>
@@ -11013,22 +11183,22 @@
     <row r="126" ht="82" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>T-402</t>
+          <t>T-311</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Page shell</t>
+          <t>Add contact dialog</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -11038,12 +11208,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>No horizontal overflow; every control named; images have alt</t>
+          <t>The form fits without scrolling</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -11053,7 +11223,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>desktop 1440=1440, mobile 390=390, 0 unnamed</t>
+          <t>576x541 with 539px of content - no scroll, unlike Team's 2.17 screens</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr"/>
@@ -11061,22 +11231,22 @@
     <row r="127" ht="82" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>T-403</t>
+          <t>T-312</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Add contact validation</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -11086,12 +11256,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Every control pressed without crashing the app</t>
+          <t>An empty form is refused with a clear reason</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -11101,7 +11271,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>47 checks passed across both viewports; 0 crashes</t>
+          <t>No API call; dialog stayed open; 'Name is required'</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr"/>
@@ -11109,22 +11279,22 @@
     <row r="128" ht="82" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>T-404</t>
+          <t>T-313</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Category breakdown</t>
+          <t>Add contact dialog</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -11134,45 +11304,49 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Each category opens a breakdown that states its weight</t>
+          <t>Every field is programmatically labelled</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Execution 35%, Finance 25%, Sales 20%, Responsiveness 20% - the model is disclosed to the user</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="inlineStr"/>
+          <t>Zero label elements in the dialog; all six fields placeholder-only</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>CR-02</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="82" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>T-405</t>
+          <t>T-314</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Next-move actions</t>
+          <t>Add contact dialog</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -11182,45 +11356,49 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Each recommended action links somewhere real</t>
+          <t>One way to dismiss the dialog</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Redundancy</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>ops-action-overdue -&gt; /my-work?filter=overdue; ops-action-complaints -&gt; /crm</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="inlineStr"/>
+          <t>Both a 'Cancel' button and a separate 'Close' X</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>CR-03</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="82" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>T-406</t>
+          <t>T-315</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Score arithmetic</t>
+          <t>Contact profile route</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -11230,12 +11408,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>The reported legs match a recomputation from raw records</t>
+          <t>A contact card opens that contact's profile page</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -11245,7 +11423,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Recomputed execution 0 and responsiveness 0 from 148 tasks; both match the API exactly - the model is implemented as designed</t>
+          <t>crm-card-&lt;id&gt; navigates to /contacts/&lt;id&gt;; page renders, no errors</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
@@ -11253,17 +11431,17 @@
     <row r="131" ht="82" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>T-407</t>
+          <t>T-316</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Team execution panel</t>
+          <t>Console + network</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -11278,49 +11456,45 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>The stated time window is the one applied</t>
+          <t>No application errors and no failing API calls</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H131" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Caption says 'Last 30 days'; the service applies no date filter at all</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>OP-01</t>
-        </is>
-      </c>
+          <t>Only the pre-login 401 on /auth/me</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
     </row>
     <row r="132" ht="82" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>T-408</t>
+          <t>T-317</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>'Do these first'</t>
+          <t>Scope chips</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -11330,49 +11504,45 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>The primary call to action is readable</t>
+          <t>Switching to Suppliers reloads the list</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
-        </is>
-      </c>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>256 of its 285px sit behind a fixed band; the document cannot scroll</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>OP-02</t>
-        </is>
-      </c>
+          <t>Buyers 11 -&gt; Suppliers 6, correct records, chip state flips</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
     </row>
     <row r="133" ht="82" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>T-409</t>
+          <t>T-318</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Score responsiveness</t>
+          <t>Sort control</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -11382,49 +11552,45 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Acting on the advice moves the score</t>
+          <t>Sorting by outstanding puts the biggest debtor first</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
-        </is>
-      </c>
-      <c r="H133" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Responsiveness computes to -296 before clamping; closing all 16 complaints would leave it at 0</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>OP-03</t>
-        </is>
-      </c>
+          <t>Krishna Garments Rs 4,00,000 first, then Nashik Traders Rs 64,000</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
     </row>
     <row r="134" ht="82" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>T-410</t>
+          <t>T-319</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Add contact menu</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -11434,49 +11600,45 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>The category measures what its label says</t>
+          <t>The menu opens with its three options readable</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
-        </is>
-      </c>
-      <c r="H134" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>It is approved/total decisions; contains no revenue, orders or pipeline</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>OP-04</t>
-        </is>
-      </c>
+          <t>aria-expanded flips, role=menu appears: New Buyer, New Supplier, Import</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
     </row>
     <row r="135" ht="82" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>T-411</t>
+          <t>T-320</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Score model</t>
+          <t>Add contact menu</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -11486,12 +11648,12 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Each underlying fact is counted once</t>
+          <t>The menu opens inside the screen</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
@@ -11501,34 +11663,34 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Overdue tasks are charged to both Execution and Responsiveness</t>
+          <t>80% clipped off the right edge; only a 55px strip of icons is visible</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>CR-04</t>
         </is>
       </c>
     </row>
     <row r="136" ht="82" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>T-412</t>
+          <t>T-321</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Score model</t>
+          <t>New customer dialog</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -11538,49 +11700,45 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>The score means the same at any company size</t>
+          <t>The form is grouped and fits one screen</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
-        </is>
-      </c>
-      <c r="H136" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>complaints x12, overdue x3, overdue invoices x5 are absolute, not rates</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>OP-06</t>
-        </is>
-      </c>
+          <t>Sections Type / Identity / Contact / Classification, required marked, More details disclosure, Cancel beside Add contact, no scrolling</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
     </row>
     <row r="137" ht="82" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>T-413</t>
+          <t>T-322</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Empty workspace</t>
+          <t>Filter control</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -11590,12 +11748,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>A workspace with no data reads as unknown</t>
+          <t>Filter reveals the status and sort controls</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
@@ -11605,49 +11763,49 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Defaults of 0.7 give a brand-new tenant roughly 70/100</t>
+          <t>Completely inert; status filter and sort exist at 0x0 so neither is reachable on a phone</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>CR-05</t>
         </is>
       </c>
     </row>
     <row r="138" ht="82" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>T-414</t>
+          <t>T-323</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Contact cards</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>A floored score looks different from a missing one</t>
+          <t>Customer names are readable on a phone</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -11657,34 +11815,34 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>0/100 with an empty bar is identical to unmeasured</t>
+          <t>Two-column grid at 160.5px per card truncates 8 text nodes including names</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>CR-06</t>
         </is>
       </c>
     </row>
     <row r="139" ht="82" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>T-415</t>
+          <t>T-324</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>'View all' + formula panel</t>
+          <t>Contact profile</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -11694,97 +11852,97 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Links are tappable and the whole page is reachable</t>
+          <t>A contact card opens a profile with money and activity</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H139" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>View all is 61x20 and one is covered by dex-fab; the formula toggle sits at y=1153 on an 812px screen and cannot be reached</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>OP-09</t>
-        </is>
-      </c>
+          <t>Outstanding / Total Billed / Total Paid / Open Complaints tiles, AI scoring, and inline activity logging</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
     </row>
     <row r="140" ht="82" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>T-416</t>
+          <t>T-325</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Next-move honesty</t>
+          <t>Contact profile</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Recommendations do not claim unearned outcomes</t>
+          <t>Primary actions use the app's primary colour</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>scoreActions deliberately removed hardcoded '+6 pts' lift estimates because the score has no history to fit a counterfactual against</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr"/>
+          <t>Log button is indigo rgb(55,58,205); the app's primaries are rgb(12,12,13)</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>CR-07</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="82" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>T-417</t>
+          <t>T-326</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Finance leg</t>
+          <t>Mobile header controls</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -11794,12 +11952,12 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Only inbound payments count as money collected</t>
+          <t>Header controls meet the 44px touch guideline</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11809,7 +11967,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>payments query filters direction='in'; outbound supplier payments excluded</t>
+          <t>Filter 44x44, Add contact 44x44, scope segment 166x44, bell 48x48</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr"/>
@@ -11817,118 +11975,126 @@
     <row r="142" ht="82" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>T-418</t>
+          <t>T-327</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Weighting</t>
+          <t>Contact profile - In progress</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Finance-less roles</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Weights renormalise when a leg is unavailable</t>
+          <t>A missing due date does not print raw values to the user</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>finance is null without the permission and the remaining weights rescale</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr"/>
+          <t>Rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>CR-08</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="82" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>T-500</t>
+          <t>T-328</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Contact profile - In progress</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>/finance loads the Overview with six KPI tiles</t>
+          <t>The list distinguishes workflows from deliveries and rows are actionable</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Revenue billed, Received, Net profit, Total Spend, Asset Value, Inventory Value</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="inlineStr"/>
+          <t>Two entity types share identical styling; titles repeat as bare 'sale'; a 'Delivered' row sits under 'In progress'; no row is tappable</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>ASK-18</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="82" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>T-501</t>
+          <t>T-400</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -11938,12 +12104,12 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>All six tabs switch content</t>
+          <t>/operating-score loads with the score and all four categories</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11953,7 +12119,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Overview, Revenue, Expenses, Assets, Inventory, Inbox all render</t>
+          <t>Overall 19/100, four category cards, next-moves, quick stats</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
@@ -11961,22 +12127,22 @@
     <row r="145" ht="82" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>T-502</t>
+          <t>T-401</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -11986,12 +12152,12 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Every reported figure reconciles with a recomputation from raw records</t>
+          <t>/operating-score loads and reflows</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -12001,7 +12167,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>8 of 8 reconcile to the paisa: billed 26,85,000; received 19,36,000; spend 19,46,966; paid 12,91,500; outstanding 6,55,466; assets 40,85,000; inventory 13,18,800; net 7,38,034</t>
+          <t>317 visible elements, compact Key scores card</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr"/>
@@ -12009,22 +12175,22 @@
     <row r="146" ht="82" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>T-503</t>
+          <t>T-402</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Cross-tab consistency</t>
+          <t>Page shell</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -12034,12 +12200,12 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>The same figure agrees across tabs</t>
+          <t>No horizontal overflow; every control named; images have alt</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -12049,7 +12215,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Overview 'Revenue billed' = Revenue tab 'Billed' = 26,85,000; status buckets (2 paid + 3 unpaid) sum to sales_count 5</t>
+          <t>desktop 1440=1440, mobile 390=390, 0 unnamed</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
@@ -12057,17 +12223,17 @@
     <row r="147" ht="82" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>T-504</t>
+          <t>T-403</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Money formatting</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -12077,153 +12243,141 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Rupees are grouped the Indian way, consistently</t>
+          <t>Every control pressed without crashing the app</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Localisation</t>
-        </is>
-      </c>
-      <c r="H147" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Tiles render Rs 2,685,000 instead of Rs 26,85,000, via a private formatter with an undefined locale; AI panels on the same page use Rs 7.49L</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>FN-01</t>
-        </is>
-      </c>
+          <t>47 checks passed across both viewports; 0 crashes</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
     </row>
     <row r="148" ht="82" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>T-505</t>
+          <t>T-404</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero</t>
+          <t>Category breakdown</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>A figure captioned 'This month' covers this month</t>
+          <t>Each category opens a breakdown that states its weight</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H148" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Shows the all-time 7,38,034 under a 'This month' chip</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>FN-02</t>
-        </is>
-      </c>
+          <t>Execution 35%, Finance 25%, Sales 20%, Responsiveness 20% - the model is disclosed to the user</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
     </row>
     <row r="149" ht="82" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>T-506</t>
+          <t>T-405</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Trend badges</t>
+          <t>Next-move actions</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>A trend beside Revenue describes revenue</t>
+          <t>Each recommended action links somewhere real</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Both Revenue and Net profit trends are the month-on-month change in EXPENSES; pct(839469, 1077500) = -22.1%, exactly what is displayed</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>FN-03</t>
-        </is>
-      </c>
+          <t>ops-action-overdue -&gt; /my-work?filter=overdue; ops-action-complaints -&gt; /crm</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
     </row>
     <row r="150" ht="82" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>T-507</t>
+          <t>T-406</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' definition</t>
+          <t>Score arithmetic</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -12233,69 +12387,65 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>The label matches the formula</t>
+          <t>The reported legs match a recomputation from raw records</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
-        </is>
-      </c>
-      <c r="H150" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>billed minus all expenses; no COGS, no inventory, assets ignored; cash basis differs by 93,534</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>FN-04</t>
-        </is>
-      </c>
+          <t>Recomputed execution 0 and responsiveness 0 from 148 tasks; both match the API exactly - the model is implemented as designed</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
     </row>
     <row r="151" ht="82" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>T-508</t>
+          <t>T-407</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Time window</t>
+          <t>Team execution panel</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>The page can show a period</t>
+          <t>The stated time window is the one applied</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
@@ -12305,34 +12455,34 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>No date filter anywhere; every figure is all-time</t>
+          <t>Caption says 'Last 30 days'; the service applies no date filter at all</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>OP-01</t>
         </is>
       </c>
     </row>
     <row r="152" ht="82" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>T-509</t>
+          <t>T-408</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Revenue tab</t>
+          <t>'Do these first'</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -12342,45 +12492,49 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Billed / Received / Outstanding tiles are correct and unambiguous</t>
+          <t>The primary call to action is readable</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>26,85,000 / 19,36,000 / 7,49,000 - and 'Outstanding' here is receivables, distinct from the payables figure which is not shown as a tile</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr"/>
+          <t>256 of its 285px sit behind a fixed band; the document cannot scroll</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>OP-02</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="82" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>T-510</t>
+          <t>T-409</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Mobile quick actions</t>
+          <t>Score responsiveness</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -12390,45 +12544,49 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>The capture row offers upload, scan, add and export</t>
+          <t>Acting on the advice moves the score</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Upload bill, Scan receipt, Add expense, Export all render</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr"/>
+          <t>Responsiveness computes to -296 before clamping; closing all 16 complaints would leave it at 0</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>OP-03</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="82" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>T-511</t>
+          <t>T-410</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -12438,45 +12596,49 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Every control pressed without crashing the app</t>
+          <t>The category measures what its label says</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>37 checks passed across both viewports; 0 crashes; 8 mutations blocked including POST ledger/ai/brief/refresh</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="inlineStr"/>
+          <t>It is approved/total decisions; contains no revenue, orders or pipeline</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>OP-04</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="82" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>T-512</t>
+          <t>T-411</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>KPI tiles as links</t>
+          <t>Score model</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -12486,45 +12648,49 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Each KPI tile navigates to its tab</t>
+          <t>Each underlying fact is counted once</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>mkpi-revenue is an &lt;a href='/finance?tab=revenue'&gt;; clicking moves the URL from '' to '?tab=revenue'. The sweep first flagged all 14 tiles as dead - a false positive from comparing only the path, now fixed in the harness</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="inlineStr"/>
+          <t>Overdue tasks are charged to both Execution and Responsiveness</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>OP-05</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="82" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>T-513</t>
+          <t>T-412</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Mobile tab strip</t>
+          <t>Score model</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -12534,45 +12700,49 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>The six tabs are reachable on a phone</t>
+          <t>The score means the same at any company size</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H156" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Horizontally scrollable strip: scrollWidth 639 &gt; clientWidth 446, overflow-x auto. The sweep first reported a 130px spill - a false positive on a deliberately scrollable strip, now excluded in the harness</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="inlineStr"/>
+          <t>complaints x12, overdue x3, overdue invoices x5 are absolute, not rates</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>OP-06</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="82" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-413</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Empty workspace</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -12582,40 +12752,44 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>A workspace with no data reads as unknown</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H157" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="inlineStr"/>
+          <t>Defaults of 0.7 give a brand-new tenant roughly 70/100</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>OP-07</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="82" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-414</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -12625,113 +12799,121 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>A floored score looks different from a missing one</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr"/>
+          <t>0/100 with an empty bar is identical to unmeasured</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>OP-08</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="82" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-415</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>'View all' + formula panel</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>Links are tappable and the whole page is reachable</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H159" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="inlineStr"/>
+          <t>View all is 61x20 and one is covered by dex-fab; the formula toggle sits at y=1153 on an 812px screen and cannot be reached</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>OP-09</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="82" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-416</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Next-move honesty</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>Recommendations do not claim unearned outcomes</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12741,7 +12923,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>scoreActions deliberately removed hardcoded '+6 pts' lift estimates because the score has no history to fit a counterfactual against</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr"/>
@@ -12749,37 +12931,37 @@
     <row r="161" ht="82" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-417</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Finance leg</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>Only inbound payments count as money collected</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -12789,7 +12971,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>payments query filters direction='in'; outbound supplier payments excluded</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr"/>
@@ -12797,37 +12979,37 @@
     <row r="162" ht="82" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-418</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Weighting</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Finance-less roles</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>Weights renormalise when a leg is unavailable</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -12837,7 +13019,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>finance is null without the permission and the remaining weights rescale</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr"/>
@@ -12845,22 +13027,22 @@
     <row r="163" ht="82" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-500</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -12870,49 +13052,45 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>/finance loads the Overview with six KPI tiles</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H163" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>Revenue billed, Received, Net profit, Total Spend, Asset Value, Inventory Value</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
     </row>
     <row r="164" ht="82" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-501</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Tabs</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -12922,49 +13100,45 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>All six tabs switch content</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H164" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>MW-04</t>
-        </is>
-      </c>
+          <t>Overview, Revenue, Expenses, Assets, Inventory, Inbox all render</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
     </row>
     <row r="165" ht="82" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-502</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -12974,12 +13148,12 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>Every reported figure reconciles with a recomputation from raw records</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -12989,7 +13163,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
+          <t>8 of 8 reconcile to the paisa: billed 26,85,000; received 19,36,000; spend 19,46,966; paid 12,91,500; outstanding 6,55,466; assets 40,85,000; inventory 13,18,800; net 7,38,034</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr"/>
@@ -12997,53 +13171,1041 @@
     <row r="166" ht="82" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>T-503</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Cross-tab consistency</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1280x800</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>The same figure agrees across tabs</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Overview 'Revenue billed' = Revenue tab 'Billed' = 26,85,000; status buckets (2 paid + 3 unpaid) sum to sales_count 5</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167" ht="82" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>T-504</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Money formatting</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Rupees are grouped the Indian way, consistently</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Localisation</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Tiles render Rs 2,685,000 instead of Rs 26,85,000, via a private formatter with an undefined locale; AI panels on the same page use Rs 7.49L</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>FN-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="82" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>T-505</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Net profit hero</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>A figure captioned 'This month' covers this month</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Shows the all-time 7,38,034 under a 'This month' chip</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>FN-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="82" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>T-506</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Trend badges</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>A trend beside Revenue describes revenue</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Both Revenue and Net profit trends are the month-on-month change in EXPENSES; pct(839469, 1077500) = -22.1%, exactly what is displayed</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>FN-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="82" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>T-507</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>'Net profit' definition</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>The label matches the formula</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>billed minus all expenses; no COGS, no inventory, assets ignored; cash basis differs by 93,534</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>FN-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="82" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>T-508</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Time window</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>The page can show a period</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>No date filter anywhere; every figure is all-time</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>FN-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="82" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>T-509</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Revenue tab</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1280x800</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Billed / Received / Outstanding tiles are correct and unambiguous</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>26,85,000 / 19,36,000 / 7,49,000 - and 'Outstanding' here is receivables, distinct from the payables figure which is not shown as a tile</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173" ht="82" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>T-510</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Mobile quick actions</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>The capture row offers upload, scan, add and export</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Upload bill, Scan receipt, Add expense, Export all render</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174" ht="82" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>T-511</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Every control pressed without crashing the app</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>37 checks passed across both viewports; 0 crashes; 8 mutations blocked including POST ledger/ai/brief/refresh</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175" ht="82" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>T-512</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>KPI tiles as links</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Each KPI tile navigates to its tab</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>mkpi-revenue is an &lt;a href='/finance?tab=revenue'&gt;; clicking moves the URL from '' to '?tab=revenue'. The sweep first flagged all 14 tiles as dead - a false positive from comparing only the path, now fixed in the harness</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176" ht="82" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>T-513</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Mobile tab strip</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>The six tabs are reachable on a phone</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Horizontally scrollable strip: scrollWidth 639 &gt; clientWidth 446, overflow-x auto. The sweep first reported a 130px spill - a false positive on a deliberately scrollable strip, now excluded in the harness</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177" ht="82" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178" ht="82" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179" ht="82" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180" ht="82" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181" ht="82" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182" ht="82" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183" ht="82" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H183" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="82" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="82" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186" ht="82" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H166" s="4" t="inlineStr">
+      <c r="H186" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J166" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J166"/>
+  <autoFilter ref="A1:J186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13292,7 +14454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16392,7 +17554,7 @@
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -16402,12 +17564,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -16422,17 +17584,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -16445,7 +17607,7 @@
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -16455,12 +17617,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -16475,17 +17637,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -16498,7 +17660,7 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -16508,12 +17670,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -16528,17 +17690,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -16551,7 +17713,7 @@
     <row r="61" ht="82" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -16561,12 +17723,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -16581,17 +17743,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -16604,7 +17766,7 @@
     <row r="62" ht="82" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -16614,12 +17776,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -16634,17 +17796,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -16657,7 +17819,7 @@
     <row r="63" ht="82" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -16667,12 +17829,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -16680,24 +17842,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -16710,7 +17872,7 @@
     <row r="64" ht="82" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -16720,12 +17882,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -16733,24 +17895,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -16763,7 +17925,7 @@
     <row r="65" ht="82" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -16773,12 +17935,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -16793,17 +17955,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -16816,7 +17978,7 @@
     <row r="66" ht="82" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -16826,12 +17988,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -16846,17 +18008,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -16869,7 +18031,7 @@
     <row r="67" ht="82" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -16884,7 +18046,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -16899,17 +18061,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -16922,7 +18084,7 @@
     <row r="68" ht="82" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -16932,12 +18094,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -16952,17 +18114,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -16975,58 +18137,164 @@
     <row r="69" ht="82" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="82" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="82" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="4" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K69"/>
+  <autoFilter ref="A1:K71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18038,7 +19306,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>165 (109 pass, 55 fail, 0 blocked, 1 not run)</t>
+          <t>185 (125 pass, 59 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
@@ -18050,7 +19318,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>2 Critical, 15 High, 17 Medium, 8 Low, 7 Nit</t>
+          <t>2 Critical, 15 High, 17 Medium, 10 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4071,17 +4071,17 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FN-01</t>
+          <t>OP-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Every money figure</t>
+          <t>Ops page when the request fails</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4106,42 +4106,42 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Localisation</t>
+          <t>Error handling / dead end</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Read the rendered text of all six Overview tiles and compared it with what Intl produces for the same number in Indian grouping.</t>
+          <t>Opened /operating-score?user=&lt;id&gt; where the API refuses or cannot find the person: as the Owner with an id that does not exist, and as Sales, Production and Finance with the Owner's id. Waited 9-10 seconds each time, on 1440 and 390, and again in the browser preview.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>An India-first product groups rupees the Indian way, the same way everywhere.</t>
+          <t>The page says what went wrong and offers a way back, as /coach already does for exactly the same two errors.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
+          <t>The loading skeleton stays on screen forever, with aria-busy=true and no text at all. The API answered in milliseconds - 404 'Team member not found' for the owner, 403 for the three other roles - but the page never shows it. The user cannot tell a slow page from a broken link or a refused one, and there is no way back except the browser. Any stale shared link (a person who has left, a link forwarded to a teammate) lands here.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Tiles read 'Rs 2,685,000'; Intl.NumberFormat('en-IN') gives 'Rs 26,85,000'. Ledger.js:61 uses Intl.NumberFormat(undefined, ...).</t>
+          <t>8 of 8 attempts: skeleton present after 9s, main text empty. API: 404 {'detail': 'Team member not found'} (owner), 403 (sales, production, finance). Browser preview at 375x812: skeleton=true, busy=true after 10s. Screenshots ops_0913/*_view_as_unknown.png, *_self_forbidden.png.</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Ledger.js defines its own private fmt() with an undefined locale, instead of the shared helper. lib/format.js already exports inr(), which uses en-IN and whose own docstring reads: 'no component formats currency inline -- everything goes through here.' Finance is the component that does.</t>
+          <t>OperatingScore reads only { data, isLoading } from useQuery and renders the skeleton whenever data is missing - 'if (isLoading || !data) return &lt;OperatingScoreSkeleton /&gt;'. A failed query has no data, so it is indistinguishable from loading. WorkCoach.js handles isError with a 403 / other message; this page never got the same branch.</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
+          <t>Read isError and error from the query and render a message: 403 -&gt; 'Only the owner can view another person's operating page', 404 -&gt; 'This person is no longer on the team', otherwise 'Couldn't load'. Each with a link to /operating-score. WorkCoach.js:36-57 is the pattern to copy. Also set retry: false for 4xx so the error shows at once.</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
+          <t>pages/OperatingScore.js:85-92 (useQuery + the skeleton fallback); pages/WorkCoach.js:36-57 (the working pattern)</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -4154,17 +4154,17 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FN-02</t>
+          <t>OP-11</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero (mobile)</t>
+          <t>Personal (self) view - bottom band (mobile)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Sales / Production / Finance</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -4189,42 +4189,42 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Truthfulness</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Compared the number under the 'This month' chip with the API figure and with the date range of the underlying records.</t>
+          <t>Opened Ops as a non-owner on a 375-390px phone, scrolled to the bottom, and measured the dark band and the dock.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>A figure captioned 'This month' covers this month.</t>
+          <t>Content that is pinned to the screen earns the space it takes.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
+          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Hero binds {f(net)} where net = tt.net_profit; ledger_summary applies no date filter; sales invoices span 2026-06-14 to 2026-08-12.</t>
+          <t>operating-self-band: position fixed, rect [0, 652, 375, 176], text 'Among your sales peers you are ranked 2 of 7.'; floating-dock fixed at [16, 724, 267, 72] on top of it. Screenshot ops_0913 and preview capture.</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>The chip was written for a windowed figure the endpoint does not provide.</t>
+          <t>KM-33 made .kr-dark-band a fixed bottom sheet below lg, on the founder's call, because on the OWNER view it holds the decisions to act on and should not scroll away. The self view reuses the same class for a single peer-ranking line, so it inherits a pinned sheet with nothing to act on.</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
+          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
+          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -4237,22 +4237,22 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FN-03</t>
+          <t>OP-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Revenue and Net profit trend badges (mobile)</t>
+          <t>AI Work Coach - entry point</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4260,9 +4260,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -4272,42 +4272,42 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Wrong data</t>
+          <t>Navigation / orphaned feature</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Traced the series behind each trend percentage and recomputed it.</t>
+          <t>Looked for any link to /coach on every Ops screen for all four roles, and searched the frontend for links to the route.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>A trend shown beside Revenue describes revenue.</t>
+          <t>A working feature can be reached without typing its URL.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
+          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>months = summary.by_month, which ledger_summary builds by summing EXPENSES per month. pct(839469, 1077500) = -22.1%, exactly what the UI shows. netPoints = months.map(m =&gt; Number(m.net ?? m.amount ?? 0)) -- by_month carries no 'net' key, so every point silently falls through to the expense amount.</t>
+          <t>coach links found on Ops screens: none, for Owner, Sales, Production and Finance on both viewports. Frontend references to '/coach': the route in App.js:228 and the 'View my coach' link inside WorkCoach's own error page.</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>The frontend was written expecting by_month to carry a net figure per month. The backend never added one, and the ?? fallback turned a missing contract into a plausible-looking wrong number instead of an error.</t>
+          <t>The employee card was repointed to view-as (/operating-score?user=) without moving the coach link anywhere else.</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
+          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
+          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -4320,17 +4320,17 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>OP-13</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>'Back to company' and 'See all' links</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4343,9 +4343,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -4355,42 +4355,42 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Accessibility / tap target</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Read what net_profit is composed of and compared it with a cash-basis calculation from the same records.</t>
+          <t>Measured every interactive element on the view-as page and on the self view for all four roles.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>A figure called net profit is close to what an owner means by it.</t>
+          <t>Links are at least 24px tall (WCAG 2.5.8).</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>net_profit = revenue_billed - total_spend = 2685000 - 1946966 = 738034, verified against a recomputation. Cash basis (received - paid expenses) = 1936000 - 1291500 = 644500.</t>
+          <t>Under-24px list: ['Back to company', 109, 16] / [117, 20]; ['See all', 52, 16] / [55, 20] - Sales, Production and Finance alike.</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>A simple difference was given the accounting term that sits closest to it.</t>
+          <t>Text links styled with text-xs and no vertical padding.</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -4403,17 +4403,17 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>OP-14</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>AI Work Coach - error page</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -4438,42 +4438,42 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Checked ledger_summary for any date filtering.</t>
+          <t>Opened /coach?user=&lt;id that does not exist&gt; as the Owner.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>A finance dashboard can show a period.</t>
+          <t>The page title matches what happened.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>ledger_summary contains no date filter; every find() is {tenant_id} only, .to_list(5000).</t>
+          <t>Title 'Access denied'; coach-error text 'Couldn't load coaching / Something went wrong. Please try again. / View my coach'.</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>The endpoint was built to summarise everything, and the period-aware UI arrived later.</t>
+          <t>PageHeader title is hard-coded to 'Access denied' for every error; only the body text branches on 403.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>pages/WorkCoach.js:36-57</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -4486,32 +4486,32 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-09</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Contact profile (mobile) - Score with AI</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -4521,47 +4521,47 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Feature parity</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Opened the same contact on 1440 and 390 and looked for the Score with AI control; pressed it on desktop with the write blocked.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>An owner can re-score a customer from their phone, or the gap is deliberate and known.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>Desktop: rescore-contact-btn present, POST blocked -&gt; toast 'Could not score right now'. Mobile after 9s: 0 rescore buttons, no visible button mentioning score.</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>ContactProfileMobile.jsx was built without the rescore mutation.</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -4569,17 +4569,17 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>FN-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Every money figure</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4592,9 +4592,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -4604,47 +4604,47 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Localisation</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Read the rendered text of all six Overview tiles and compared it with what Intl produces for the same number in Indian grouping.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>An India-first product groups rupees the Indian way, the same way everywhere.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>Tiles read 'Rs 2,685,000'; Intl.NumberFormat('en-IN') gives 'Rs 26,85,000'. Ledger.js:61 uses Intl.NumberFormat(undefined, ...).</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>Ledger.js defines its own private fmt() with an undefined locale, instead of the shared helper. lib/format.js already exports inr(), which uses en-IN and whose own docstring reads: 'no component formats currency inline -- everything goes through here.' Finance is the component that does.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -4652,109 +4652,105 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>FN-02</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Net profit hero (mobile)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Truthfulness</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Compared the number under the 'This month' chip with the API figure and with the date range of the underlying records.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>A figure captioned 'This month' covers this month.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>Hero binds {f(net)} where net = tt.net_profit; ledger_summary applies no date filter; sales invoices span 2026-06-14 to 2026-08-12.</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>The chip was written for a windowed figure the endpoint does not provide.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13: the profile dialog now exposes ONE Close (36px desktop, 44px mobile) as Owner and as Sales; Team.js:572 hides the primitive's default close with [&amp;&gt;button.absolute]:hidden.</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
     </row>
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>FN-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Revenue and Net profit trend badges (mobile)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4762,239 +4758,741 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Wrong data</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Traced the series behind each trend percentage and recomputed it.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>A trend shown beside Revenue describes revenue.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>months = summary.by_month, which ledger_summary builds by summing EXPENSES per month. pct(839469, 1077500) = -22.1%, exactly what the UI shows. netPoints = months.map(m =&gt; Number(m.net ?? m.amount ?? 0)) -- by_month carries no 'net' key, so every point silently falls through to the expense amount.</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>The frontend was written expecting by_month to carry a net figure per month. The backend never added one, and the ?? fallback turned a missing contract into a plausible-looking wrong number instead of an error.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
     </row>
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Read what net_profit is composed of and compared it with a cash-basis calculation from the same records.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>A figure called net profit is close to what an owner means by it.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>net_profit = revenue_billed - total_spend = 2685000 - 1946966 = 738034, verified against a recomputation. Cash basis (received - paid expenses) = 1936000 - 1291500 = 644500.</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>A simple difference was given the accounting term that sits closest to it.</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
     </row>
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>FN-05</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>All figures</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Checked ledger_summary for any date filtering.</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>A finance dashboard can show a period.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>ledger_summary contains no date filter; every find() is {tenant_id} only, .to_list(5000).</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>The endpoint was built to summarise everything, and the period-aware UI arrived later.</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="82" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Visual / layout</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Measured the grid that renders each role group on the team roster.</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="82" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="82" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Each control in a dialog is distinguishable by name.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13: the profile dialog now exposes ONE Close (36px desktop, 44px mobile) as Owner and as Sales; Team.js:572 hides the primitive's default close with [&amp;&gt;button.absolute]:hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="82" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="82" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="82" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F58" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr">
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q52"/>
+  <autoFilter ref="A1:Q58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5005,7 +5503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13027,22 +13525,22 @@
     <row r="163" ht="82" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>T-500</t>
+          <t>T-419</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>View-as - open</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -13052,7 +13550,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>/finance loads the Overview with six KPI tiles</t>
+          <t>An employee card opens that person's Ops with a banner naming them</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -13067,7 +13565,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Revenue billed, Received, Net profit, Total Spend, Asset Value, Inventory Value</t>
+          <t>/operating-score?user=&lt;id&gt;; banner 'Viewing Priya Nair - sales - Back to company'; her self view renders</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr"/>
@@ -13075,22 +13573,22 @@
     <row r="164" ht="82" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>T-501</t>
+          <t>T-420</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>View-as - leaving</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -13100,12 +13598,12 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>All six tabs switch content</t>
+          <t>Back to company, browser Back and ?user=&lt;own id&gt; all land on the company view</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13115,7 +13613,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Overview, Revenue, Expenses, Assets, Inventory, Inbox all render</t>
+          <t>All three show the leaderboard with no banner</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
@@ -13123,32 +13621,32 @@
     <row r="165" ht="82" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>T-502</t>
+          <t>T-421</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>View-as - accuracy</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner + Sales</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Every reported figure reconciles with a recomputation from raw records</t>
+          <t>The owner sees exactly what the person sees on their own login</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -13163,7 +13661,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>8 of 8 reconcile to the paisa: billed 26,85,000; received 19,36,000; spend 19,46,966; paid 12,91,500; outstanding 6,55,466; assets 40,85,000; inventory 13,18,800; net 7,38,034</t>
+          <t>Priya's own page and the owner's view-as both read Completed 1 / Open 29 / Overdue 20 / Completion 3%; API payloads identical</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr"/>
@@ -13171,22 +13669,22 @@
     <row r="166" ht="82" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>T-503</t>
+          <t>T-422</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Cross-tab consistency</t>
+          <t>View-as - unknown person</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -13196,40 +13694,44 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>The same figure agrees across tabs</t>
+          <t>An unknown ?user= id explains itself</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Overview 'Revenue billed' = Revenue tab 'Billed' = 26,85,000; status buckets (2 paid + 3 unpaid) sum to sales_count 5</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="inlineStr"/>
+          <t>API 404 'Team member not found'; page shows the loading skeleton forever</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>OP-10</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="82" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>T-504</t>
+          <t>T-423</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Money formatting</t>
+          <t>Roles - self view</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -13239,121 +13741,113 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Rupees are grouped the Indian way, consistently</t>
+          <t>Non-owners get their personal view, not the company leaderboard</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Localisation</t>
-        </is>
-      </c>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Tiles render Rs 2,685,000 instead of Rs 26,85,000, via a private formatter with an undefined locale; AI panels on the same page use Rs 7.49L</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>FN-01</t>
-        </is>
-      </c>
+          <t>API view=self; no leaderboard, no banner; stats, open work and peer context render (Production has no peer group)</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
     </row>
     <row r="168" ht="82" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>T-505</t>
+          <t>T-424</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero</t>
+          <t>Roles - self view links</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>A figure captioned 'This month' covers this month</t>
+          <t>Every link on the self view opens a real screen</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Shows the all-time 7,38,034 under a 'This month' chip</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>FN-02</t>
-        </is>
-      </c>
+          <t>/my-work and /my-work?filter=overdue both load</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
     </row>
     <row r="169" ht="82" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>T-506</t>
+          <t>T-425</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Trend badges</t>
+          <t>Roles - viewing someone else</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>A trend beside Revenue describes revenue</t>
+          <t>A non-owner who opens another person's Ops is told they cannot</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="H169" s="7" t="inlineStr">
@@ -13363,49 +13857,49 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Both Revenue and Net profit trends are the month-on-month change in EXPENSES; pct(839469, 1077500) = -22.1%, exactly what is displayed</t>
+          <t>API 403 correctly; page shows the loading skeleton forever with no message</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>FN-03</t>
+          <t>OP-10</t>
         </is>
       </c>
     </row>
     <row r="170" ht="82" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>T-507</t>
+          <t>T-426</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' definition</t>
+          <t>Self view - bottom band</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>The label matches the formula</t>
+          <t>Pinned content is worth the space and is not hidden by the dock</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr">
@@ -13415,34 +13909,34 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>billed minus all expenses; no COGS, no inventory, assets ignored; cash basis differs by 93,534</t>
+          <t>176px fixed black band holding one sentence, mostly behind the dock</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>OP-11</t>
         </is>
       </c>
     </row>
     <row r="171" ht="82" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>T-508</t>
+          <t>T-427</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Time window</t>
+          <t>View-as + self view - link size</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -13452,12 +13946,12 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>The page can show a period</t>
+          <t>Links are at least 24px tall</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H171" s="7" t="inlineStr">
@@ -13467,44 +13961,44 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>No date filter anywhere; every figure is all-time</t>
+          <t>'Back to company' 16-20px tall; 'See all' 16-20px tall</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>OP-13</t>
         </is>
       </c>
     </row>
     <row r="172" ht="82" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>T-509</t>
+          <t>T-428</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Revenue tab</t>
+          <t>AI coach - own</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Billed / Received / Outstanding tiles are correct and unambiguous</t>
+          <t>/coach loads each person's own coach</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -13519,7 +14013,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>26,85,000 / 19,36,000 / 7,49,000 - and 'Outstanding' here is receivables, distinct from the payables figure which is not shown as a tile</t>
+          <t>Owner and Finance: 'No coaching yet' with Generate; Sales and Production: cached review from 29 Aug with Refresh; no overflow</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr"/>
@@ -13527,22 +14021,22 @@
     <row r="173" ht="82" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>T-510</t>
+          <t>T-429</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Mobile quick actions</t>
+          <t>AI coach - a teammate's</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -13552,12 +14046,12 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>The capture row offers upload, scan, add and export</t>
+          <t>The owner can open a teammate's coach</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13567,7 +14061,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Upload bill, Scan receipt, Add expense, Export all render</t>
+          <t>/coach?user=&lt;Priya&gt; reads 'Priya Nair - sales'</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr"/>
@@ -13575,17 +14069,17 @@
     <row r="174" ht="82" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>T-511</t>
+          <t>T-430</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>AI coach - not allowed</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -13595,17 +14089,17 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Every control pressed without crashing the app</t>
+          <t>A non-owner is refused a colleague's coach, with a way back</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -13615,7 +14109,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>37 checks passed across both viewports; 0 crashes; 8 mutations blocked including POST ledger/ai/brief/refresh</t>
+          <t>'Not allowed - Only the owner can view another team member's coaching'; 'View my coach' returns to /coach</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr"/>
@@ -13623,17 +14117,17 @@
     <row r="175" ht="82" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>T-512</t>
+          <t>T-431</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>KPI tiles as links</t>
+          <t>AI coach - unknown person</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -13648,60 +14142,64 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Each KPI tile navigates to its tab</t>
+          <t>An unknown id shows an accurate error</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
-        </is>
-      </c>
-      <c r="H175" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Copy</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>mkpi-revenue is an &lt;a href='/finance?tab=revenue'&gt;; clicking moves the URL from '' to '?tab=revenue'. The sweep first flagged all 14 tiles as dead - a false positive from comparing only the path, now fixed in the harness</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr"/>
+          <t>Shows an error (good) but titles it 'Access denied' for a 404</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>OP-14</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="82" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>T-513</t>
+          <t>T-432</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Mobile tab strip</t>
+          <t>AI coach - refresh failure</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>The six tabs are reachable on a phone</t>
+          <t>A failed Generate / Refresh says so and recovers</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -13711,7 +14209,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Horizontally scrollable strip: scrollWidth 639 &gt; clientWidth 446, overflow-x auto. The sweep first reported a 130px spill - a false positive on a deliberately scrollable strip, now excluded in the harness</t>
+          <t>POST blocked -&gt; 'Could not refresh coaching'; button label restored</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr"/>
@@ -13719,95 +14217,99 @@
     <row r="177" ht="82" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-433</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>AI coach - entry point</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>The coach can be reached from the app</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr"/>
+          <t>No link to /coach on any Ops screen or anywhere else in the app</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>OP-12</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="82" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-434</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>AI coach + Score with AI - live generation</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>A live model run produces a sensible review / score</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H178" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>NOT RUN by choice: refresh overwrites users.coach_summary and rescore overwrites the contact's AI score, both via a paid model call. Awaiting the founder's go, ideally on a TEST account and a test contact</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr"/>
@@ -13815,17 +14317,17 @@
     <row r="179" ht="82" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-435</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Score with AI - failure path</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -13835,17 +14337,17 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>A failed rescore says so and recovers</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -13855,7 +14357,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>POST blocked -&gt; 'Could not score right now'; label restored to 'Score with AI'</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr"/>
@@ -13863,60 +14365,64 @@
     <row r="180" ht="82" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-436</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Score with AI - mobile</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>The rescore action exists on the phone</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Feature parity</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="inlineStr"/>
+          <t>No scoring control on the mobile contact profile; Health row is read-only</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>CR-09</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="82" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-500</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -13926,22 +14432,22 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>/finance loads the Overview with six KPI tiles</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -13951,7 +14457,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>Revenue billed, Received, Net profit, Total Spend, Asset Value, Inventory Value</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr"/>
@@ -13959,22 +14465,22 @@
     <row r="182" ht="82" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-501</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Tabs</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -13984,12 +14490,12 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>All six tabs switch content</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -13999,7 +14505,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>Overview, Revenue, Expenses, Assets, Inventory, Inbox all render</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr"/>
@@ -14007,22 +14513,22 @@
     <row r="183" ht="82" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-502</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -14032,49 +14538,45 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>Every reported figure reconciles with a recomputation from raw records</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H183" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>8 of 8 reconcile to the paisa: billed 26,85,000; received 19,36,000; spend 19,46,966; paid 12,91,500; outstanding 6,55,466; assets 40,85,000; inventory 13,18,800; net 7,38,034</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
     </row>
     <row r="184" ht="82" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-503</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Cross-tab consistency</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -14084,128 +14586,1016 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>The same figure agrees across tabs</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H184" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="inlineStr">
-        <is>
-          <t>MW-04</t>
-        </is>
-      </c>
+          <t>Overview 'Revenue billed' = Revenue tab 'Billed' = 26,85,000; status buckets (2 paid + 3 unpaid) sum to sales_count 5</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
     </row>
     <row r="185" ht="82" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-504</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Money formatting</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>Rupees are grouped the Indian way, consistently</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H185" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Localisation</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="inlineStr"/>
+          <t>Tiles render Rs 2,685,000 instead of Rs 26,85,000, via a private formatter with an undefined locale; AI panels on the same page use Rs 7.49L</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>FN-01</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="82" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
+          <t>T-505</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Net profit hero</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>A figure captioned 'This month' covers this month</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Shows the all-time 7,38,034 under a 'This month' chip</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>FN-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="82" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>T-506</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Trend badges</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>A trend beside Revenue describes revenue</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Both Revenue and Net profit trends are the month-on-month change in EXPENSES; pct(839469, 1077500) = -22.1%, exactly what is displayed</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>FN-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="82" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>T-507</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>'Net profit' definition</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>The label matches the formula</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H188" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>billed minus all expenses; no COGS, no inventory, assets ignored; cash basis differs by 93,534</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>FN-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="82" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>T-508</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Time window</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>The page can show a period</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>No date filter anywhere; every figure is all-time</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>FN-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="82" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>T-509</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Revenue tab</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1280x800</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Billed / Received / Outstanding tiles are correct and unambiguous</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>26,85,000 / 19,36,000 / 7,49,000 - and 'Outstanding' here is receivables, distinct from the payables figure which is not shown as a tile</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191" ht="82" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>T-510</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Mobile quick actions</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>The capture row offers upload, scan, add and export</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H191" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Upload bill, Scan receipt, Add expense, Export all render</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192" ht="82" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>T-511</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Every control pressed without crashing the app</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>37 checks passed across both viewports; 0 crashes; 8 mutations blocked including POST ledger/ai/brief/refresh</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193" ht="82" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>T-512</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>KPI tiles as links</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Each KPI tile navigates to its tab</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>mkpi-revenue is an &lt;a href='/finance?tab=revenue'&gt;; clicking moves the URL from '' to '?tab=revenue'. The sweep first flagged all 14 tiles as dead - a false positive from comparing only the path, now fixed in the harness</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194" ht="82" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>T-513</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Mobile tab strip</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>The six tabs are reachable on a phone</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Horizontally scrollable strip: scrollWidth 639 &gt; clientWidth 446, overflow-x auto. The sweep first reported a 130px spill - a false positive on a deliberately scrollable strip, now excluded in the harness</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195" ht="82" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196" ht="82" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197" ht="82" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198" ht="82" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199" ht="82" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200" ht="82" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201" ht="82" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H201" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="82" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="82" customHeight="1">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204" ht="82" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H186" s="4" t="inlineStr">
+      <c r="H204" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J186" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J186"/>
+  <autoFilter ref="A1:J204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14454,7 +15844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16335,7 +17725,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FN-01</t>
+          <t>OP-10</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -16345,12 +17735,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Every money figure</t>
+          <t>Ops page when the request fails</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -16365,17 +17755,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
+          <t>Read isError and error from the query and render a message: 403 -&gt; 'Only the owner can view another person's operating page', 404 -&gt; 'This person is no longer on the team', otherwise 'Couldn't load'. Each with a link to /operating-score. WorkCoach.js:36-57 is the pattern to copy. Also set retry: false for 4xx so the error shows at once.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
+          <t>The loading skeleton stays on screen forever, with aria-busy=true and no text at all. The API answered in milliseconds - 404 'Team member not found' for the owner, 403 for the three other roles - but the page never shows it. The user cannot tell a slow page from a broken link or a refused one, and there is no way back except the browser. Any stale shared link (a person who has left, a link forwarded to a teammate) lands here.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
+          <t>pages/OperatingScore.js:85-92 (useQuery + the skeleton fallback); pages/WorkCoach.js:36-57 (the working pattern)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -16388,7 +17778,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FN-02</t>
+          <t>FN-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -16403,7 +17793,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero (mobile)</t>
+          <t>Every money figure</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -16418,17 +17808,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
+          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
+          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
+          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -16441,7 +17831,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FN-03</t>
+          <t>FN-02</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -16456,7 +17846,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Revenue and Net profit trend badges (mobile)</t>
+          <t>Net profit hero (mobile)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -16471,17 +17861,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
+          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
+          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
+          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -16494,7 +17884,7 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>FN-03</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -16504,12 +17894,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Revenue and Net profit trend badges (mobile)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -16517,24 +17907,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -16547,7 +17937,7 @@
     <row r="39" ht="82" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -16562,7 +17952,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -16577,17 +17967,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -16600,7 +17990,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -16610,12 +18000,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -16630,17 +18020,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -16653,7 +18043,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -16668,7 +18058,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -16683,17 +18073,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -16706,7 +18096,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MW-17</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -16721,7 +18111,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - two close buttons, invisible focus</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -16736,17 +18126,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -16759,7 +18149,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MW-18</t>
+          <t>MW-17</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -16769,12 +18159,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Application shell at wide widths</t>
+          <t>Task drawer - two close buttons, invisible focus</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -16789,17 +18179,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
+          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
+          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:634 (app-shell className)</t>
+          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -16812,7 +18202,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-18</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -16822,12 +18212,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Application shell at wide widths</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -16842,17 +18232,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>components/Layout.js:634 (app-shell className)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -16865,7 +18255,7 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -16880,7 +18270,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -16895,17 +18285,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -16918,7 +18308,7 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -16928,12 +18318,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -16948,17 +18338,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -16971,7 +18361,7 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -16986,7 +18376,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -17001,17 +18391,17 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -17024,7 +18414,7 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -17039,7 +18429,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -17054,17 +18444,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -17077,7 +18467,7 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -17087,12 +18477,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -17107,17 +18497,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_sales</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -17130,7 +18520,7 @@
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -17145,7 +18535,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -17160,17 +18550,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -17183,7 +18573,7 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -17213,17 +18603,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_company_operating_view</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -17236,7 +18626,7 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>OP-09</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -17251,7 +18641,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>'View all' links and the formula panel (mobile)</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -17266,17 +18656,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -17289,7 +18679,7 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -17299,12 +18689,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -17319,17 +18709,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -17342,7 +18732,7 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>OP-11</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -17352,12 +18742,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>Personal (self) view - bottom band (mobile)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -17372,17 +18762,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -17395,7 +18785,7 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>OP-12</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -17405,12 +18795,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>AI Work Coach - entry point</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -17418,24 +18808,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -17448,7 +18838,7 @@
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MW-19</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -17458,12 +18848,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Department filter dropdown</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -17471,24 +18861,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -17501,7 +18891,7 @@
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -17511,12 +18901,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -17524,24 +18914,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -17554,7 +18944,7 @@
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TM-07</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -17564,12 +18954,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog - closing</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -17584,17 +18974,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -17607,7 +18997,7 @@
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TM-08</t>
+          <t>MW-19</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -17617,12 +19007,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Default close button on every dialog</t>
+          <t>Department filter dropdown</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -17637,17 +19027,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
+          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
+          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx:37-41</t>
+          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -17660,7 +19050,7 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -17670,12 +19060,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -17690,17 +19080,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -17713,7 +19103,7 @@
     <row r="61" ht="82" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -17723,12 +19113,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -17743,17 +19133,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -17766,7 +19156,7 @@
     <row r="62" ht="82" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -17776,12 +19166,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -17796,17 +19186,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -17819,7 +19209,7 @@
     <row r="63" ht="82" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -17829,12 +19219,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -17849,17 +19239,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -17872,7 +19262,7 @@
     <row r="64" ht="82" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -17882,12 +19272,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -17902,17 +19292,17 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -17925,7 +19315,7 @@
     <row r="65" ht="82" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -17935,12 +19325,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -17948,24 +19338,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -17978,7 +19368,7 @@
     <row r="66" ht="82" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -17988,12 +19378,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -18001,24 +19391,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -18031,7 +19421,7 @@
     <row r="67" ht="82" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>OP-13</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -18041,12 +19431,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>'Back to company' and 'See all' links</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -18054,24 +19444,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -18084,7 +19474,7 @@
     <row r="68" ht="82" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>OP-14</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -18094,12 +19484,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>AI Work Coach - error page</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -18107,24 +19497,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/WorkCoach.js:36-57</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -18137,7 +19527,7 @@
     <row r="69" ht="82" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>CR-09</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -18147,12 +19537,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Contact profile (mobile) - Score with AI</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -18160,24 +19550,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -18190,7 +19580,7 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -18205,7 +19595,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -18213,24 +19603,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -18243,58 +19633,376 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Page heading in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="82" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>CR-03</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog - dismiss controls</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="82" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="82" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="82" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="82" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="82" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F77" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="4" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K71"/>
+  <autoFilter ref="A1:K77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19306,7 +21014,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>185 (125 pass, 59 fail, 0 blocked, 1 not run)</t>
+          <t>203 (135 pass, 66 fail, 0 blocked, 2 not run)</t>
         </is>
       </c>
     </row>
@@ -19318,7 +21026,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>2 Critical, 15 High, 17 Medium, 10 Low, 7 Nit</t>
+          <t>2 Critical, 16 High, 19 Medium, 13 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$218</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4569,17 +4569,17 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FN-01</t>
+          <t>CR-10</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Every money figure</t>
+          <t>Contact list when loading fails</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -4604,42 +4604,42 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Localisation</t>
+          <t>Error handling / dead end</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Read the rendered text of all six Overview tiles and compared it with what Intl produces for the same number in Indian grouping.</t>
+          <t>Made the contact list request fail (network abort on GET /api/contacts) and watched /crm for 7 seconds at 1440 and 390.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>An India-first product groups rupees the Indian way, the same way everywhere.</t>
+          <t>The page says the contacts could not be loaded and offers a retry.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
+          <t>The loading skeleton stays forever. On desktop the chips read 'Buyers 0' and 'Suppliers 0' above six blank placeholder cards, so an owner with a flaky connection sees what looks like a CRM with no customers, still loading. On mobile it is the same skeleton with nothing else. No toast, no message, no retry. The same fault as OP-10 on Ops.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Tiles read 'Rs 2,685,000'; Intl.NumberFormat('en-IN') gives 'Rs 26,85,000'. Ledger.js:61 uses Intl.NumberFormat(undefined, ...).</t>
+          <t>After 7s: 0 cards, 18 animate-pulse placeholders, no error or empty wording, no toast, on both viewports. Screenshots crm_0913/desk1440_list_failed.png, mob390_list_failed.png.</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Ledger.js defines its own private fmt() with an undefined locale, instead of the shared helper. lib/format.js already exports inr(), which uses en-IN and whose own docstring reads: 'no component formats currency inline -- everything goes through here.' Finance is the component that does.</t>
+          <t>CRM reads only { data, isLoading } from the contacts query; a failed query has no data, so the skeleton branch never ends and the scope counts compute from an empty list.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
+          <t>Read isError from the query and render 'Couldn't load your contacts' with a Retry that calls refetch(). Show '-' rather than 0 in the scope chips while loading or failed. Same fix pattern as OP-10 - worth one shared &lt;QueryError&gt; component.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
+          <t>pages/CRM.js:524-527 (contacts useQuery), scope-count chips :819-835</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -4652,32 +4652,32 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FN-02</t>
+          <t>CR-11</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero (mobile)</t>
+          <t>Contact profile when loading fails</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -4687,42 +4687,42 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Truthfulness</t>
+          <t>Copy / misleading error</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Compared the number under the 'This month' chip with the API figure and with the date range of the underlying records.</t>
+          <t>Made the profile request fail (network abort on GET /api/contacts/&lt;id&gt;/profile) for a contact that exists.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>A figure captioned 'This month' covers this month.</t>
+          <t>A connection failure is reported as a connection failure.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
+          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Hero binds {f(net)} where net = tt.net_profit; ledger_summary applies no date filter; sales invoices span 2026-06-14 to 2026-08-12.</t>
+          <t>Aborted profile request -&gt; 'That contact isn't here. It may have been merged or removed. Everyone else is still in People.' on 1440 and 390; the same text a genuinely missing id produces.</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>The chip was written for a windowed figure the endpoint does not provide.</t>
+          <t>Both profile pages send error and '!data?.contact' down one branch. The comment at ContactProfile.js:145-150 explains why the empty-body case was added, but a network error and a missing contact now share its copy.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
+          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
+          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FN-03</t>
+          <t>CR-12</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Revenue and Net profit trend badges (mobile)</t>
+          <t>GET /api/crm/outstanding</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>n/a (API)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Sales / Production / Finance</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -4770,42 +4770,42 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Wrong data</t>
+          <t>Permissions / data exposure</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Traced the series behind each trend percentage and recomputed it.</t>
+          <t>Called the endpoints the CRM page uses while signed in as Sales, who holds neither the People nor the Finance permission.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>A trend shown beside Revenue describes revenue.</t>
+          <t>Per-customer money figures follow the same permission as the contact list and the finance profile.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
+          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>months = summary.by_month, which ledger_summary builds by summing EXPENSES per month. pct(839469, 1077500) = -22.1%, exactly what the UI shows. netPoints = months.map(m =&gt; Number(m.net ?? m.amount ?? 0)) -- by_month carries no 'net' key, so every point silently falls through to the expense amount.</t>
+          <t>As Sales: /contacts 403, /contacts/&lt;id&gt;/profile 403, /crm/outstanding 200 {&lt;contact_id&gt;: {receivables: 400000, payables: 0, invoice_count: 1, oldest_days: 61}, ...}.</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>The frontend was written expecting by_month to carry a net figure per month. The backend never added one, and the ?? fallback turned a missing contract into a plausible-looking wrong number instead of an error.</t>
+          <t>outstanding_by_contact depends only on get_current_user - no require_perm.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
+          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
+          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -4818,17 +4818,17 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>CR-13</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Sales / Production / Finance</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -4853,42 +4853,42 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Navigation / dead end</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Read what net_profit is composed of and compared it with a cash-basis calculation from the same records.</t>
+          <t>Signed in as each non-owner role and listed every visible link that leads into CRM.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>A figure called net profit is close to what an owner means by it.</t>
+          <t>Roles that cannot open CRM are not offered links into it.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>net_profit = revenue_billed - total_spend = 2685000 - 1946966 = 738034, verified against a recomputation. Cash basis (received - paid expenses) = 1936000 - 1291500 = 644500.</t>
+          <t>Sales, Production and Finance: /inbox has one link into CRM - kpi-complaints (desktop) / kpi-complaints-m (mobile), href /crm.</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>A simple difference was given the accounting term that sits closest to it.</t>
+          <t>The Desk KPI tiles hard-code to="/crm" without checking the People permission that the nav already checks.</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -4901,32 +4901,32 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>CR-14</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>Contact profile - 'Back to CRM' (desktop)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -4936,42 +4936,42 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Accessibility / tap target</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Checked ledger_summary for any date filtering.</t>
+          <t>Measured the interactive elements on the desktop contact profile.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>A finance dashboard can show a period.</t>
+          <t>Controls are at least 24px tall.</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>ledger_summary contains no date filter; every find() is {tenant_id} only, .to_list(5000).</t>
+          <t>Under-24px list on the desktop profile: ['Back to CRM', 103, 20].</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>The endpoint was built to summarise everything, and the period-aware UI arrived later.</t>
+          <t>Text link with no vertical padding.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>py-1 or min-h-6 on the back link.</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>pages/ContactProfile.js:205 (profile-back)</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -4984,22 +4984,22 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>FN-01</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Every money figure</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -5007,9 +5007,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -5019,47 +5019,47 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Localisation</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Read the rendered text of all six Overview tiles and compared it with what Intl produces for the same number in Indian grouping.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>An India-first product groups rupees the Indian way, the same way everywhere.</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>Tiles read 'Rs 2,685,000'; Intl.NumberFormat('en-IN') gives 'Rs 26,85,000'. Ledger.js:61 uses Intl.NumberFormat(undefined, ...).</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>Ledger.js defines its own private fmt() with an undefined locale, instead of the shared helper. lib/format.js already exports inr(), which uses en-IN and whose own docstring reads: 'no component formats currency inline -- everything goes through here.' Finance is the component that does.</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -5067,22 +5067,22 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>FN-02</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Net profit hero (mobile)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5090,9 +5090,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -5102,47 +5102,47 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Truthfulness</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Compared the number under the 'This month' chip with the API figure and with the date range of the underlying records.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>A figure captioned 'This month' covers this month.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>Hero binds {f(net)} where net = tt.net_profit; ledger_summary applies no date filter; sales invoices span 2026-06-14 to 2026-08-12.</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>The chip was written for a windowed figure the endpoint does not provide.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -5150,109 +5150,105 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>FN-03</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Revenue and Net profit trend badges (mobile)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Wrong data</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Traced the series behind each trend percentage and recomputed it.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>A trend shown beside Revenue describes revenue.</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>months = summary.by_month, which ledger_summary builds by summing EXPENSES per month. pct(839469, 1077500) = -22.1%, exactly what the UI shows. netPoints = months.map(m =&gt; Number(m.net ?? m.amount ?? 0)) -- by_month carries no 'net' key, so every point silently falls through to the expense amount.</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>The frontend was written expecting by_month to carry a net figure per month. The backend never added one, and the ?? fallback turned a missing contract into a plausible-looking wrong number instead of an error.</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13: the profile dialog now exposes ONE Close (36px desktop, 44px mobile) as Owner and as Sales; Team.js:572 hides the primitive's default close with [&amp;&gt;button.absolute]:hidden.</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
     </row>
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5260,239 +5256,658 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Read what net_profit is composed of and compared it with a cash-basis calculation from the same records.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>A figure called net profit is close to what an owner means by it.</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>net_profit = revenue_billed - total_spend = 2685000 - 1946966 = 738034, verified against a recomputation. Cash basis (received - paid expenses) = 1936000 - 1291500 = 644500.</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>A simple difference was given the accounting term that sits closest to it.</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
     </row>
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Checked ledger_summary for any date filtering.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>A finance dashboard can show a period.</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>ledger_summary contains no date filter; every find() is {tenant_id} only, .to_list(5000).</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>The endpoint was built to summarise everything, and the period-aware UI arrived later.</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
     </row>
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Visual / layout</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Measured the grid that renders each role group on the team roster.</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="82" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="82" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Each control in a dialog is distinguishable by name.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13: the profile dialog now exposes ONE Close (36px desktop, 44px mobile) as Owner and as Sales; Team.js:572 hides the primitive's default close with [&amp;&gt;button.absolute]:hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="82" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="82" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="82" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F58" s="9" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q58"/>
+  <autoFilter ref="A1:Q63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5503,7 +5918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:J218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12577,22 +12992,22 @@
     <row r="144" ht="82" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>T-400</t>
+          <t>T-329</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Cards -&gt; profile -&gt; back</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -12602,7 +13017,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>/operating-score loads with the score and all four categories</t>
+          <t>Every contact card opens its profile and Back returns to the list</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -12617,7 +13032,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Overall 19/100, four category cards, next-moves, quick stats</t>
+          <t>11 of 11 open and 11 of 11 return, on both viewports</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
@@ -12625,17 +13040,17 @@
     <row r="145" ht="82" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>T-401</t>
+          <t>T-330</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Profile sections + actions (mobile)</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -12650,12 +13065,12 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>/operating-score loads and reflows</t>
+          <t>Every section expands and collapses; Call and Email are real links</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -12665,7 +13080,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>317 visible elements, compact Key scores card</t>
+          <t>7 of 7 sections toggle aria-expanded; tel:+919820044558, mailto:deepak@anandfabrics.in</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr"/>
@@ -12673,22 +13088,22 @@
     <row r="146" ht="82" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>T-402</t>
+          <t>T-331</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Page shell</t>
+          <t>Log activity</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -12698,12 +13113,12 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>No horizontal overflow; every control named; images have alt</t>
+          <t>Empty activity is refused; a failed save says so and keeps the text</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -12713,7 +13128,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>desktop 1440=1440, mobile 390=390, 0 unnamed</t>
+          <t>Save disabled when empty; 6 kinds; blocked POST -&gt; 'Could not save', text kept</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
@@ -12721,17 +13136,17 @@
     <row r="147" ht="82" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>T-403</t>
+          <t>T-332</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Missing contact</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -12746,12 +13161,12 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Every control pressed without crashing the app</t>
+          <t>An unknown contact id explains itself with a way back</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -12761,7 +13176,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>47 checks passed across both viewports; 0 crashes</t>
+          <t>'That contact isn't here...' + 'Back to People' -&gt; /crm</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr"/>
@@ -12769,17 +13184,17 @@
     <row r="148" ht="82" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>T-404</t>
+          <t>T-333</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Category breakdown</t>
+          <t>List scrolling + slow load</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -12794,12 +13209,12 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Each category opens a breakdown that states its weight</t>
+          <t>The last card is reachable; a slow list shows loading, not 'empty'</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -12809,7 +13224,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Execution 35%, Finance 25%, Sales 20%, Responsiveness 20% - the model is disclosed to the user</t>
+          <t>Last card within the viewport after scrolling; 18 skeleton placeholders during a 5s delay</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr"/>
@@ -12817,22 +13232,22 @@
     <row r="149" ht="82" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>T-405</t>
+          <t>T-334</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Next-move actions</t>
+          <t>Contact list fails</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -12842,45 +13257,49 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Each recommended action links somewhere real</t>
+          <t>A failed contact list says so</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>ops-action-overdue -&gt; /my-work?filter=overdue; ops-action-complaints -&gt; /crm</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr"/>
+          <t>Skeleton forever with 'Buyers 0 / Suppliers 0'; no message, no retry</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>CR-10</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="82" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>T-406</t>
+          <t>T-335</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Score arithmetic</t>
+          <t>Profile fails</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -12890,40 +13309,44 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>The reported legs match a recomputation from raw records</t>
+          <t>A failed profile request is reported as a failure</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Recomputed execution 0 and responsiveness 0 from 148 tasks; both match the API exactly - the model is implemented as designed</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr"/>
+          <t>Says the contact 'may have been merged or removed'</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>CR-11</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="82" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>T-407</t>
+          <t>T-336</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Team execution panel</t>
+          <t>Roles - navigation</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -12933,101 +13356,93 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>The stated time window is the one applied</t>
+          <t>CRM is hidden from roles without the People permission</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Caption says 'Last 30 days'; the service applies no date filter at all</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>OP-01</t>
-        </is>
-      </c>
+          <t>No nav-crm on desktop; no /crm in the mobile More panel</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
     </row>
     <row r="152" ht="82" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>T-408</t>
+          <t>T-337</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>'Do these first'</t>
+          <t>Roles - direct links</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>The primary call to action is readable</t>
+          <t>/crm and /contacts/&lt;id&gt; refuse clearly with a way out</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
-        </is>
-      </c>
-      <c r="H152" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>256 of its 285px sit behind a fixed band; the document cannot scroll</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>OP-02</t>
-        </is>
-      </c>
+          <t>Access Denied on both; 'Go to My Work' leaves the page</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
     </row>
     <row r="153" ht="82" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>T-409</t>
+          <t>T-338</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Score responsiveness</t>
+          <t>Roles - server</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -13037,49 +13452,45 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Finance</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Acting on the advice moves the score</t>
+          <t>The API refuses contact data to roles without the permission</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Responsiveness computes to -296 before clamping; closing all 16 complaints would leave it at 0</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>OP-03</t>
-        </is>
-      </c>
+          <t>GET /contacts 403 for both; /contacts/&lt;id&gt;/profile 403 for Sales (200 for Finance, which holds the finance permission, though the page itself is refused)</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
     </row>
     <row r="154" ht="82" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>T-410</t>
+          <t>T-339</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Roles - outstanding totals</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -13089,17 +13500,17 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>The category measures what its label says</t>
+          <t>Per-customer money figures are permission-gated</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
@@ -13109,49 +13520,49 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>It is approved/total decisions; contains no revenue, orders or pipeline</t>
+          <t>GET /crm/outstanding returns receivables/payables per contact to any signed-in user</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>CR-12</t>
         </is>
       </c>
     </row>
     <row r="155" ht="82" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>T-411</t>
+          <t>T-340</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Score model</t>
+          <t>Roles - links from elsewhere</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Each underlying fact is counted once</t>
+          <t>No link offers these roles a page they cannot open</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
@@ -13161,34 +13572,34 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Overdue tasks are charged to both Execution and Responsiveness</t>
+          <t>Decision Desk 'Complaints' tile links to /crm -&gt; Access Denied</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>CR-13</t>
         </is>
       </c>
     </row>
     <row r="156" ht="82" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>T-412</t>
+          <t>T-341</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Score model</t>
+          <t>Profile - link size</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -13198,12 +13609,12 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>The score means the same at any company size</t>
+          <t>Controls are at least 24px tall</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -13213,34 +13624,34 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>complaints x12, overdue x3, overdue invoices x5 are absolute, not rates</t>
+          <t>'Back to CRM' is 103x20</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>CR-14</t>
         </is>
       </c>
     </row>
     <row r="157" ht="82" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>T-413</t>
+          <t>T-342</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Empty workspace</t>
+          <t>CR-08 re-check</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -13250,12 +13661,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>A workspace with no data reads as unknown</t>
+          <t>Pending deliveries without a due date do not print 'undefined'</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Data leak to UI</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
@@ -13265,19 +13676,19 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Defaults of 0.7 give a brand-new tenant roughly 70/100</t>
+          <t>Browser preview 2026-09-13: 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000' still shown under In progress</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>CR-08</t>
         </is>
       </c>
     </row>
     <row r="158" ht="82" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>T-414</t>
+          <t>T-400</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -13287,7 +13698,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -13302,34 +13713,30 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>A floored score looks different from a missing one</t>
+          <t>/operating-score loads with the score and all four categories</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
-        </is>
-      </c>
-      <c r="H158" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>0/100 with an empty bar is identical to unmeasured</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>OP-08</t>
-        </is>
-      </c>
+          <t>Overall 19/100, four category cards, next-moves, quick stats</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
     </row>
     <row r="159" ht="82" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>T-415</t>
+          <t>T-401</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -13339,7 +13746,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>'View all' + formula panel</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -13354,34 +13761,30 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Links are tappable and the whole page is reachable</t>
+          <t>/operating-score loads and reflows</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H159" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>View all is 61x20 and one is covered by dex-fab; the formula toggle sits at y=1153 on an 812px screen and cannot be reached</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>OP-09</t>
-        </is>
-      </c>
+          <t>317 visible elements, compact Key scores card</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
     </row>
     <row r="160" ht="82" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>T-416</t>
+          <t>T-402</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -13391,12 +13794,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Next-move honesty</t>
+          <t>Page shell</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -13406,12 +13809,12 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Recommendations do not claim unearned outcomes</t>
+          <t>No horizontal overflow; every control named; images have alt</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -13421,7 +13824,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>scoreActions deliberately removed hardcoded '+6 pts' lift estimates because the score has no history to fit a counterfactual against</t>
+          <t>desktop 1440=1440, mobile 390=390, 0 unnamed</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr"/>
@@ -13429,7 +13832,7 @@
     <row r="161" ht="82" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>T-417</t>
+          <t>T-403</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -13439,12 +13842,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Finance leg</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -13454,12 +13857,12 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Only inbound payments count as money collected</t>
+          <t>Every control pressed without crashing the app</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -13469,7 +13872,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>payments query filters direction='in'; outbound supplier payments excluded</t>
+          <t>47 checks passed across both viewports; 0 crashes</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr"/>
@@ -13477,7 +13880,7 @@
     <row r="162" ht="82" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>T-418</t>
+          <t>T-404</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -13487,22 +13890,22 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Weighting</t>
+          <t>Category breakdown</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Finance-less roles</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Weights renormalise when a leg is unavailable</t>
+          <t>Each category opens a breakdown that states its weight</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -13517,7 +13920,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>finance is null without the permission and the remaining weights rescale</t>
+          <t>Execution 35%, Finance 25%, Sales 20%, Responsiveness 20% - the model is disclosed to the user</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr"/>
@@ -13525,7 +13928,7 @@
     <row r="163" ht="82" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>T-419</t>
+          <t>T-405</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -13535,12 +13938,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>View-as - open</t>
+          <t>Next-move actions</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -13550,7 +13953,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>An employee card opens that person's Ops with a banner naming them</t>
+          <t>Each recommended action links somewhere real</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -13565,7 +13968,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>/operating-score?user=&lt;id&gt;; banner 'Viewing Priya Nair - sales - Back to company'; her self view renders</t>
+          <t>ops-action-overdue -&gt; /my-work?filter=overdue; ops-action-complaints -&gt; /crm</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr"/>
@@ -13573,7 +13976,7 @@
     <row r="164" ht="82" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>T-420</t>
+          <t>T-406</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -13583,12 +13986,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>View-as - leaving</t>
+          <t>Score arithmetic</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -13598,12 +14001,12 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Back to company, browser Back and ?user=&lt;own id&gt; all land on the company view</t>
+          <t>The reported legs match a recomputation from raw records</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13613,7 +14016,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>All three show the leaderboard with no banner</t>
+          <t>Recomputed execution 0 and responsiveness 0 from 148 tasks; both match the API exactly - the model is implemented as designed</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
@@ -13621,7 +14024,7 @@
     <row r="165" ht="82" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>T-421</t>
+          <t>T-407</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -13631,7 +14034,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>View-as - accuracy</t>
+          <t>Team execution panel</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -13641,12 +14044,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Owner + Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>The owner sees exactly what the person sees on their own login</t>
+          <t>The stated time window is the one applied</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -13654,22 +14057,26 @@
           <t>Data quality</t>
         </is>
       </c>
-      <c r="H165" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>Priya's own page and the owner's view-as both read Completed 1 / Open 29 / Overdue 20 / Completion 3%; API payloads identical</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr"/>
+          <t>Caption says 'Last 30 days'; the service applies no date filter at all</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>OP-01</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="82" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>T-422</t>
+          <t>T-408</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -13679,12 +14086,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>View-as - unknown person</t>
+          <t>'Do these first'</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -13694,12 +14101,12 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>An unknown ?user= id explains itself</t>
+          <t>The primary call to action is readable</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Error handling</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr">
@@ -13709,19 +14116,19 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>API 404 'Team member not found'; page shows the loading skeleton forever</t>
+          <t>256 of its 285px sit behind a fixed band; the document cannot scroll</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>OP-10</t>
+          <t>OP-02</t>
         </is>
       </c>
     </row>
     <row r="167" ht="82" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>T-423</t>
+          <t>T-409</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -13731,45 +14138,49 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Roles - self view</t>
+          <t>Score responsiveness</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Sales / Production / Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Non-owners get their personal view, not the company leaderboard</t>
+          <t>Acting on the advice moves the score</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>API view=self; no leaderboard, no banner; stats, open work and peer context render (Production has no peer group)</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="inlineStr"/>
+          <t>Responsiveness computes to -296 before clamping; closing all 16 complaints would leave it at 0</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>OP-03</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="82" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>T-424</t>
+          <t>T-410</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -13779,45 +14190,49 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Roles - self view links</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Sales / Production / Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Every link on the self view opens a real screen</t>
+          <t>The category measures what its label says</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>/my-work and /my-work?filter=overdue both load</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="inlineStr"/>
+          <t>It is approved/total decisions; contains no revenue, orders or pipeline</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>OP-04</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="82" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>T-425</t>
+          <t>T-411</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -13827,27 +14242,27 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Roles - viewing someone else</t>
+          <t>Score model</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Sales / Production / Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>A non-owner who opens another person's Ops is told they cannot</t>
+          <t>Each underlying fact is counted once</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Error handling</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="H169" s="7" t="inlineStr">
@@ -13857,19 +14272,19 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>API 403 correctly; page shows the loading skeleton forever with no message</t>
+          <t>Overdue tasks are charged to both Execution and Responsiveness</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>OP-10</t>
+          <t>OP-05</t>
         </is>
       </c>
     </row>
     <row r="170" ht="82" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>T-426</t>
+          <t>T-412</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -13879,27 +14294,27 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Self view - bottom band</t>
+          <t>Score model</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Sales / Production / Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Pinned content is worth the space and is not hidden by the dock</t>
+          <t>The score means the same at any company size</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Layout</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr">
@@ -13909,19 +14324,19 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>176px fixed black band holding one sentence, mostly behind the dock</t>
+          <t>complaints x12, overdue x3, overdue invoices x5 are absolute, not rates</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>OP-11</t>
+          <t>OP-06</t>
         </is>
       </c>
     </row>
     <row r="171" ht="82" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>T-427</t>
+          <t>T-413</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -13931,27 +14346,27 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>View-as + self view - link size</t>
+          <t>Empty workspace</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Links are at least 24px tall</t>
+          <t>A workspace with no data reads as unknown</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="H171" s="7" t="inlineStr">
@@ -13961,19 +14376,19 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' 16-20px tall; 'See all' 16-20px tall</t>
+          <t>Defaults of 0.7 give a brand-new tenant roughly 70/100</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>OP-13</t>
+          <t>OP-07</t>
         </is>
       </c>
     </row>
     <row r="172" ht="82" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>T-428</t>
+          <t>T-414</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -13983,45 +14398,49 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>AI coach - own</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>/coach loads each person's own coach</t>
+          <t>A floored score looks different from a missing one</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Owner and Finance: 'No coaching yet' with Generate; Sales and Production: cached review from 29 Aug with Refresh; no overflow</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
+          <t>0/100 with an empty bar is identical to unmeasured</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>OP-08</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="82" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>T-429</t>
+          <t>T-415</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -14031,12 +14450,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>AI coach - a teammate's</t>
+          <t>'View all' + formula panel</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -14046,30 +14465,34 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>The owner can open a teammate's coach</t>
+          <t>Links are tappable and the whole page is reachable</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>/coach?user=&lt;Priya&gt; reads 'Priya Nair - sales'</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr"/>
+          <t>View all is 61x20 and one is covered by dex-fab; the formula toggle sits at y=1153 on an 812px screen and cannot be reached</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>OP-09</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="82" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>T-430</t>
+          <t>T-416</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -14079,27 +14502,27 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>AI coach - not allowed</t>
+          <t>Next-move honesty</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Sales / Production / Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>A non-owner is refused a colleague's coach, with a way back</t>
+          <t>Recommendations do not claim unearned outcomes</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -14109,7 +14532,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>'Not allowed - Only the owner can view another team member's coaching'; 'View my coach' returns to /coach</t>
+          <t>scoreActions deliberately removed hardcoded '+6 pts' lift estimates because the score has no history to fit a counterfactual against</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr"/>
@@ -14117,7 +14540,7 @@
     <row r="175" ht="82" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>T-431</t>
+          <t>T-417</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -14127,12 +14550,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>AI coach - unknown person</t>
+          <t>Finance leg</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -14142,34 +14565,30 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>An unknown id shows an accurate error</t>
+          <t>Only inbound payments count as money collected</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Copy</t>
-        </is>
-      </c>
-      <c r="H175" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Shows an error (good) but titles it 'Access denied' for a 404</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>OP-14</t>
-        </is>
-      </c>
+          <t>payments query filters direction='in'; outbound supplier payments excluded</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
     </row>
     <row r="176" ht="82" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>T-432</t>
+          <t>T-418</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -14179,27 +14598,27 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>AI coach - refresh failure</t>
+          <t>Weighting</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Finance-less roles</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>A failed Generate / Refresh says so and recovers</t>
+          <t>Weights renormalise when a leg is unavailable</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Error handling</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -14209,7 +14628,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>POST blocked -&gt; 'Could not refresh coaching'; button label restored</t>
+          <t>finance is null without the permission and the remaining weights rescale</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr"/>
@@ -14217,7 +14636,7 @@
     <row r="177" ht="82" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>T-433</t>
+          <t>T-419</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -14227,7 +14646,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>AI coach - entry point</t>
+          <t>View-as - open</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -14237,39 +14656,35 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>The coach can be reached from the app</t>
+          <t>An employee card opens that person's Ops with a banner naming them</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Navigation</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>No link to /coach on any Ops screen or anywhere else in the app</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>OP-12</t>
-        </is>
-      </c>
+          <t>/operating-score?user=&lt;id&gt;; banner 'Viewing Priya Nair - sales - Back to company'; her self view renders</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
     </row>
     <row r="178" ht="82" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>T-434</t>
+          <t>T-420</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -14279,7 +14694,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>AI coach + Score with AI - live generation</t>
+          <t>View-as - leaving</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -14294,22 +14709,22 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>A live model run produces a sensible review / score</t>
+          <t>Back to company, browser Back and ?user=&lt;own id&gt; all land on the company view</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H178" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>NOT RUN by choice: refresh overwrites users.coach_summary and rescore overwrites the contact's AI score, both via a paid model call. Awaiting the founder's go, ideally on a TEST account and a test contact</t>
+          <t>All three show the leaderboard with no banner</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr"/>
@@ -14317,37 +14732,37 @@
     <row r="179" ht="82" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>T-435</t>
+          <t>T-421</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Score with AI - failure path</t>
+          <t>View-as - accuracy</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner + Sales</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>A failed rescore says so and recovers</t>
+          <t>The owner sees exactly what the person sees on their own login</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Error handling</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14357,7 +14772,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>POST blocked -&gt; 'Could not score right now'; label restored to 'Score with AI'</t>
+          <t>Priya's own page and the owner's view-as both read Completed 1 / Open 29 / Overdue 20 / Completion 3%; API payloads identical</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr"/>
@@ -14365,22 +14780,22 @@
     <row r="180" ht="82" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>T-436</t>
+          <t>T-422</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Score with AI - mobile</t>
+          <t>View-as - unknown person</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -14390,12 +14805,12 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>The rescore action exists on the phone</t>
+          <t>An unknown ?user= id explains itself</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Feature parity</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="H180" s="7" t="inlineStr">
@@ -14405,49 +14820,49 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>No scoring control on the mobile contact profile; Health row is read-only</t>
+          <t>API 404 'Team member not found'; page shows the loading skeleton forever</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>CR-09</t>
+          <t>OP-10</t>
         </is>
       </c>
     </row>
     <row r="181" ht="82" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>T-500</t>
+          <t>T-423</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Roles - self view</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>/finance loads the Overview with six KPI tiles</t>
+          <t>Non-owners get their personal view, not the company leaderboard</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14457,7 +14872,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>Revenue billed, Received, Net profit, Total Spend, Asset Value, Inventory Value</t>
+          <t>API view=self; no leaderboard, no banner; stats, open work and peer context render (Production has no peer group)</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr"/>
@@ -14465,37 +14880,37 @@
     <row r="182" ht="82" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>T-501</t>
+          <t>T-424</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>Roles - self view links</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>All six tabs switch content</t>
+          <t>Every link on the self view opens a real screen</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14505,7 +14920,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Overview, Revenue, Expenses, Assets, Inventory, Inbox all render</t>
+          <t>/my-work and /my-work?filter=overdue both load</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr"/>
@@ -14513,113 +14928,121 @@
     <row r="183" ht="82" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>T-502</t>
+          <t>T-425</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Roles - viewing someone else</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Every reported figure reconciles with a recomputation from raw records</t>
+          <t>A non-owner who opens another person's Ops is told they cannot</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H183" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H183" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>8 of 8 reconcile to the paisa: billed 26,85,000; received 19,36,000; spend 19,46,966; paid 12,91,500; outstanding 6,55,466; assets 40,85,000; inventory 13,18,800; net 7,38,034</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="inlineStr"/>
+          <t>API 403 correctly; page shows the loading skeleton forever with no message</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>OP-10</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="82" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>T-503</t>
+          <t>T-426</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Cross-tab consistency</t>
+          <t>Self view - bottom band</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>The same figure agrees across tabs</t>
+          <t>Pinned content is worth the space and is not hidden by the dock</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H184" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Overview 'Revenue billed' = Revenue tab 'Billed' = 26,85,000; status buckets (2 paid + 3 unpaid) sum to sales_count 5</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="inlineStr"/>
+          <t>176px fixed black band holding one sentence, mostly behind the dock</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>OP-11</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="82" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>T-504</t>
+          <t>T-427</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Money formatting</t>
+          <t>View-as + self view - link size</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -14634,12 +15057,12 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Rupees are grouped the Indian way, consistently</t>
+          <t>Links are at least 24px tall</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Localisation</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr">
@@ -14649,205 +15072,193 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Tiles render Rs 2,685,000 instead of Rs 26,85,000, via a private formatter with an undefined locale; AI panels on the same page use Rs 7.49L</t>
+          <t>'Back to company' 16-20px tall; 'See all' 16-20px tall</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>FN-01</t>
+          <t>OP-13</t>
         </is>
       </c>
     </row>
     <row r="186" ht="82" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>T-505</t>
+          <t>T-428</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero</t>
+          <t>AI coach - own</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>A figure captioned 'This month' covers this month</t>
+          <t>/coach loads each person's own coach</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H186" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Shows the all-time 7,38,034 under a 'This month' chip</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>FN-02</t>
-        </is>
-      </c>
+          <t>Owner and Finance: 'No coaching yet' with Generate; Sales and Production: cached review from 29 Aug with Refresh; no overflow</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
     </row>
     <row r="187" ht="82" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>T-506</t>
+          <t>T-429</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Trend badges</t>
+          <t>AI coach - a teammate's</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>A trend beside Revenue describes revenue</t>
+          <t>The owner can open a teammate's coach</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="H187" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Both Revenue and Net profit trends are the month-on-month change in EXPENSES; pct(839469, 1077500) = -22.1%, exactly what is displayed</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>FN-03</t>
-        </is>
-      </c>
+          <t>/coach?user=&lt;Priya&gt; reads 'Priya Nair - sales'</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
     </row>
     <row r="188" ht="82" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>T-507</t>
+          <t>T-430</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' definition</t>
+          <t>AI coach - not allowed</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>The label matches the formula</t>
+          <t>A non-owner is refused a colleague's coach, with a way back</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
-        </is>
-      </c>
-      <c r="H188" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>billed minus all expenses; no COGS, no inventory, assets ignored; cash basis differs by 93,534</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t>FN-04</t>
-        </is>
-      </c>
+          <t>'Not allowed - Only the owner can view another team member's coaching'; 'View my coach' returns to /coach</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
     </row>
     <row r="189" ht="82" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>T-508</t>
+          <t>T-431</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Time window</t>
+          <t>AI coach - unknown person</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>The page can show a period</t>
+          <t>An unknown id shows an accurate error</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Metric design</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
@@ -14857,49 +15268,49 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>No date filter anywhere; every figure is all-time</t>
+          <t>Shows an error (good) but titles it 'Access denied' for a 404</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>OP-14</t>
         </is>
       </c>
     </row>
     <row r="190" ht="82" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>T-509</t>
+          <t>T-432</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Revenue tab</t>
+          <t>AI coach - refresh failure</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1280x800</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Billed / Received / Outstanding tiles are correct and unambiguous</t>
+          <t>A failed Generate / Refresh says so and recovers</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -14909,7 +15320,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>26,85,000 / 19,36,000 / 7,49,000 - and 'Outstanding' here is receivables, distinct from the payables figure which is not shown as a tile</t>
+          <t>POST blocked -&gt; 'Could not refresh coaching'; button label restored</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
@@ -14917,65 +15328,69 @@
     <row r="191" ht="82" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>T-510</t>
+          <t>T-433</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Mobile quick actions</t>
+          <t>AI coach - entry point</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>The capture row offers upload, scan, add and export</t>
+          <t>The coach can be reached from the app</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H191" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Upload bill, Scan receipt, Add expense, Export all render</t>
-        </is>
-      </c>
-      <c r="J191" s="2" t="inlineStr"/>
+          <t>No link to /coach on any Ops screen or anywhere else in the app</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>OP-12</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="82" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>T-511</t>
+          <t>T-434</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>AI coach + Score with AI - live generation</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -14990,22 +15405,22 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Every control pressed without crashing the app</t>
+          <t>A live model run produces a sensible review / score</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H192" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H192" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>37 checks passed across both viewports; 0 crashes; 8 mutations blocked including POST ledger/ai/brief/refresh</t>
+          <t>NOT RUN by choice: refresh overwrites users.coach_summary and rescore overwrites the contact's AI score, both via a paid model call. Awaiting the founder's go, ideally on a TEST account and a test contact</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
@@ -15013,22 +15428,22 @@
     <row r="193" ht="82" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>T-512</t>
+          <t>T-435</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>KPI tiles as links</t>
+          <t>Score with AI - failure path</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -15038,12 +15453,12 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Each KPI tile navigates to its tab</t>
+          <t>A failed rescore says so and recovers</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15053,7 +15468,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>mkpi-revenue is an &lt;a href='/finance?tab=revenue'&gt;; clicking moves the URL from '' to '?tab=revenue'. The sweep first flagged all 14 tiles as dead - a false positive from comparing only the path, now fixed in the harness</t>
+          <t>POST blocked -&gt; 'Could not score right now'; label restored to 'Score with AI'</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
@@ -15061,22 +15476,22 @@
     <row r="194" ht="82" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>T-513</t>
+          <t>T-436</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Mobile tab strip</t>
+          <t>Score with AI - mobile</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Mobile 375x812</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -15086,35 +15501,39 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>The six tabs are reachable on a phone</t>
+          <t>The rescore action exists on the phone</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Responsive</t>
-        </is>
-      </c>
-      <c r="H194" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Feature parity</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Horizontally scrollable strip: scrollWidth 639 &gt; clientWidth 446, overflow-x auto. The sweep first reported a 130px spill - a false positive on a deliberately scrollable strip, now excluded in the harness</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="inlineStr"/>
+          <t>No scoring control on the mobile contact profile; Health row is read-only</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>CR-09</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="82" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-500</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -15124,7 +15543,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -15134,12 +15553,12 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>/finance loads the Overview with six KPI tiles</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15149,7 +15568,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+          <t>Revenue billed, Received, Net profit, Total Spend, Asset Value, Inventory Value</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr"/>
@@ -15157,37 +15576,37 @@
     <row r="196" ht="82" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-501</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Tabs</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>All six tabs switch content</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15197,7 +15616,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>Overview, Revenue, Expenses, Assets, Inventory, Inbox all render</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr"/>
@@ -15205,37 +15624,37 @@
     <row r="197" ht="82" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-502</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>Every reported figure reconciles with a recomputation from raw records</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15245,7 +15664,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>8 of 8 reconcile to the paisa: billed 26,85,000; received 19,36,000; spend 19,46,966; paid 12,91,500; outstanding 6,55,466; assets 40,85,000; inventory 13,18,800; net 7,38,034</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr"/>
@@ -15253,37 +15672,37 @@
     <row r="198" ht="82" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-503</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Cross-tab consistency</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>The same figure agrees across tabs</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -15293,7 +15712,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>Overview 'Revenue billed' = Revenue tab 'Billed' = 26,85,000; status buckets (2 paid + 3 unpaid) sum to sales_count 5</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr"/>
@@ -15301,133 +15720,141 @@
     <row r="199" ht="82" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-504</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Money formatting</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>Rupees are grouped the Indian way, consistently</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H199" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Localisation</t>
+        </is>
+      </c>
+      <c r="H199" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
-        </is>
-      </c>
-      <c r="J199" s="2" t="inlineStr"/>
+          <t>Tiles render Rs 2,685,000 instead of Rs 26,85,000, via a private formatter with an undefined locale; AI panels on the same page use Rs 7.49L</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>FN-01</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="82" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-505</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Net profit hero</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>A figure captioned 'This month' covers this month</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H200" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H200" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
-        </is>
-      </c>
-      <c r="J200" s="2" t="inlineStr"/>
+          <t>Shows the all-time 7,38,034 under a 'This month' chip</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>FN-02</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="82" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-506</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Trend badges</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>A trend beside Revenue describes revenue</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H201" s="7" t="inlineStr">
@@ -15437,49 +15864,49 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
+          <t>Both Revenue and Net profit trends are the month-on-month change in EXPENSES; pct(839469, 1077500) = -22.1%, exactly what is displayed</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>FN-03</t>
         </is>
       </c>
     </row>
     <row r="202" ht="82" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-507</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>'Net profit' definition</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>The label matches the formula</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="H202" s="7" t="inlineStr">
@@ -15489,113 +15916,797 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
+          <t>billed minus all expenses; no COGS, no inventory, assets ignored; cash basis differs by 93,534</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>FN-04</t>
         </is>
       </c>
     </row>
     <row r="203" ht="82" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-508</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Time window</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>The page can show a period</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H203" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
-        </is>
-      </c>
-      <c r="J203" s="2" t="inlineStr"/>
+          <t>No date filter anywhere; every figure is all-time</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>FN-05</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="82" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
+          <t>T-509</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Revenue tab</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1280x800</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Billed / Received / Outstanding tiles are correct and unambiguous</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>26,85,000 / 19,36,000 / 7,49,000 - and 'Outstanding' here is receivables, distinct from the payables figure which is not shown as a tile</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205" ht="82" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>T-510</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Mobile quick actions</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>The capture row offers upload, scan, add and export</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H205" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>Upload bill, Scan receipt, Add expense, Export all render</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206" ht="82" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>T-511</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Every control pressed without crashing the app</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>37 checks passed across both viewports; 0 crashes; 8 mutations blocked including POST ledger/ai/brief/refresh</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207" ht="82" customHeight="1">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>T-512</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>KPI tiles as links</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Each KPI tile navigates to its tab</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>mkpi-revenue is an &lt;a href='/finance?tab=revenue'&gt;; clicking moves the URL from '' to '?tab=revenue'. The sweep first flagged all 14 tiles as dead - a false positive from comparing only the path, now fixed in the harness</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208" ht="82" customHeight="1">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>T-513</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Mobile tab strip</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>The six tabs are reachable on a phone</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Horizontally scrollable strip: scrollWidth 639 &gt; clientWidth 446, overflow-x auto. The sweep first reported a 130px spill - a false positive on a deliberately scrollable strip, now excluded in the harness</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209" ht="82" customHeight="1">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210" ht="82" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211" ht="82" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H211" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212" ht="82" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213" ht="82" customHeight="1">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H213" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214" ht="82" customHeight="1">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215" ht="82" customHeight="1">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H215" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="82" customHeight="1">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H216" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="82" customHeight="1">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218" ht="82" customHeight="1">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H204" s="4" t="inlineStr">
+      <c r="H218" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr">
+      <c r="I218" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J204" s="2" t="inlineStr"/>
+      <c r="J218" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J204"/>
+  <autoFilter ref="A1:J218"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15844,7 +16955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17778,7 +18889,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FN-01</t>
+          <t>CR-10</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -17788,12 +18899,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Every money figure</t>
+          <t>Contact list when loading fails</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -17808,17 +18919,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
+          <t>Read isError from the query and render 'Couldn't load your contacts' with a Retry that calls refetch(). Show '-' rather than 0 in the scope chips while loading or failed. Same fix pattern as OP-10 - worth one shared &lt;QueryError&gt; component.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
+          <t>The loading skeleton stays forever. On desktop the chips read 'Buyers 0' and 'Suppliers 0' above six blank placeholder cards, so an owner with a flaky connection sees what looks like a CRM with no customers, still loading. On mobile it is the same skeleton with nothing else. No toast, no message, no retry. The same fault as OP-10 on Ops.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
+          <t>pages/CRM.js:524-527 (contacts useQuery), scope-count chips :819-835</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -17831,7 +18942,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FN-02</t>
+          <t>FN-01</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -17846,7 +18957,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero (mobile)</t>
+          <t>Every money figure</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -17861,17 +18972,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
+          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
+          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
+          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -17884,7 +18995,7 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FN-03</t>
+          <t>FN-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -17899,7 +19010,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Revenue and Net profit trend badges (mobile)</t>
+          <t>Net profit hero (mobile)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -17914,17 +19025,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
+          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
+          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
+          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -17937,7 +19048,7 @@
     <row r="39" ht="82" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>FN-03</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -17947,12 +19058,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Revenue and Net profit trend badges (mobile)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -17960,24 +19071,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -17990,7 +19101,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -18005,7 +19116,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -18020,17 +19131,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -18043,7 +19154,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -18053,12 +19164,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -18073,17 +19184,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -18096,7 +19207,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -18111,7 +19222,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -18126,17 +19237,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -18149,7 +19260,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MW-17</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -18164,7 +19275,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - two close buttons, invisible focus</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -18179,17 +19290,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -18202,7 +19313,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MW-18</t>
+          <t>MW-17</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -18212,12 +19323,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Application shell at wide widths</t>
+          <t>Task drawer - two close buttons, invisible focus</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -18232,17 +19343,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
+          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
+          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:634 (app-shell className)</t>
+          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -18255,7 +19366,7 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-18</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -18265,12 +19376,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Application shell at wide widths</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -18285,17 +19396,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>components/Layout.js:634 (app-shell className)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -18308,7 +19419,7 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -18323,7 +19434,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -18338,17 +19449,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -18361,7 +19472,7 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -18371,12 +19482,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -18391,17 +19502,17 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -18414,7 +19525,7 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -18429,7 +19540,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -18444,17 +19555,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -18467,7 +19578,7 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -18482,7 +19593,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -18497,17 +19608,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -18520,7 +19631,7 @@
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -18530,12 +19641,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -18550,17 +19661,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_sales</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -18573,7 +19684,7 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -18588,7 +19699,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -18603,17 +19714,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -18626,7 +19737,7 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -18656,17 +19767,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_company_operating_view</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -18679,7 +19790,7 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>OP-09</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -18694,7 +19805,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>'View all' links and the formula panel (mobile)</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -18709,17 +19820,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -18732,7 +19843,7 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>OP-11</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -18747,7 +19858,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Personal (self) view - bottom band (mobile)</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -18762,17 +19873,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -18785,7 +19896,7 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>OP-12</t>
+          <t>OP-11</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -18800,7 +19911,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - entry point</t>
+          <t>Personal (self) view - bottom band (mobile)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -18815,17 +19926,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
+          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
+          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
+          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -18838,7 +19949,7 @@
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>OP-12</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -18848,12 +19959,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>AI Work Coach - entry point</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -18868,17 +19979,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -18891,7 +20002,7 @@
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>CR-11</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -18901,12 +20012,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>Contact profile when loading fails</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -18921,17 +20032,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -18944,7 +20055,7 @@
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>CR-12</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -18954,12 +20065,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>GET /api/crm/outstanding</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -18967,24 +20078,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -18997,7 +20108,7 @@
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>MW-19</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -19007,12 +20118,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Department filter dropdown</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -19020,24 +20131,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -19050,7 +20161,7 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -19060,12 +20171,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -19073,24 +20184,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -19103,7 +20214,7 @@
     <row r="61" ht="82" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TM-07</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -19113,12 +20224,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog - closing</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -19133,17 +20244,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -19156,7 +20267,7 @@
     <row r="62" ht="82" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TM-08</t>
+          <t>MW-19</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -19166,12 +20277,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Default close button on every dialog</t>
+          <t>Department filter dropdown</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -19186,17 +20297,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
+          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
+          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx:37-41</t>
+          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -19209,7 +20320,7 @@
     <row r="63" ht="82" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -19219,12 +20330,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -19239,17 +20350,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -19262,7 +20373,7 @@
     <row r="64" ht="82" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -19272,12 +20383,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -19292,17 +20403,17 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -19315,7 +20426,7 @@
     <row r="65" ht="82" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -19325,12 +20436,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -19345,17 +20456,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -19368,7 +20479,7 @@
     <row r="66" ht="82" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -19378,12 +20489,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -19398,17 +20509,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -19421,7 +20532,7 @@
     <row r="67" ht="82" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>OP-13</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -19431,12 +20542,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' and 'See all' links</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -19451,17 +20562,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -19474,7 +20585,7 @@
     <row r="68" ht="82" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>OP-14</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -19489,7 +20600,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - error page</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -19504,17 +20615,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>pages/WorkCoach.js:36-57</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -19527,7 +20638,7 @@
     <row r="69" ht="82" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>CR-09</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -19537,12 +20648,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - Score with AI</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -19557,17 +20668,17 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -19580,7 +20691,7 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>OP-13</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -19590,12 +20701,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>'Back to company' and 'See all' links</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -19610,17 +20721,17 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -19633,7 +20744,7 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>OP-14</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -19643,12 +20754,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>AI Work Coach - error page</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -19656,24 +20767,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/WorkCoach.js:36-57</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -19686,7 +20797,7 @@
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>CR-09</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -19701,7 +20812,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Contact profile (mobile) - Score with AI</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -19709,24 +20820,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -19739,7 +20850,7 @@
     <row r="73" ht="82" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-13</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -19749,12 +20860,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -19762,24 +20873,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -19792,7 +20903,7 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>CR-14</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -19802,12 +20913,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Contact profile - 'Back to CRM' (desktop)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -19815,24 +20926,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>py-1 or min-h-6 on the back link.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/ContactProfile.js:205 (profile-back)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -19845,7 +20956,7 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -19855,12 +20966,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -19868,24 +20979,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -19898,7 +21009,7 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -19913,7 +21024,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -19928,17 +21039,17 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -19951,58 +21062,323 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>CR-03</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog - dismiss controls</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="82" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="82" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="82" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="82" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="82" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="4" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K77"/>
+  <autoFilter ref="A1:K82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21014,7 +22390,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>203 (135 pass, 66 fail, 0 blocked, 2 not run)</t>
+          <t>217 (143 pass, 72 fail, 0 blocked, 2 not run)</t>
         </is>
       </c>
     </row>
@@ -21026,7 +22402,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>2 Critical, 16 High, 19 Medium, 13 Low, 7 Nit</t>
+          <t>2 Critical, 17 High, 21 Medium, 15 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$233</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5399,32 +5399,32 @@
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>FN-06</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Delete on expenses, invoices and payments</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>Owner / Finance</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -5434,47 +5434,47 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Destructive action / data loss</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Pressed the delete (trash) control on an expense, a sales invoice and a received payment, as Owner and as Finance, at 1440 and 390, with the DELETE request blocked at the network layer.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>Removing a money record asks first - it changes every total on the page and there is no undo.</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>One tap sends the DELETE straight away. No confirmation dialog, no 'are you sure', no undo toast - for all three record types, both viewports, both roles. The trash icon is a 36px target at the end of each row, so a stray tap while scrolling a phone ledger deletes a real invoice or payment and silently changes Revenue, Received and Net profit. (The harness blocked every DELETE, so nothing was removed.)</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>DELETE /api/expenses/&lt;id&gt;, /api/revenue/invoice/&lt;id&gt; and /api/revenue/payment/&lt;id&gt; each fired on the first click; confirmation shown = false in 12 of 12 attempts. With the write blocked the page then reports 'Could not delete'.</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>The tables call onDelete(id) directly from the trash button, and Ledger's del()/delRevenue() call api.delete immediately. Contrast Team's delete-task, which has a confirm step.</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Put a confirm step in del() and delRevenue(): an AlertDialog naming the record and amount ('Delete invoice SBT/25-26/0431 for Rs 2,85,000?'). Alternatively delete optimistically with an Undo toast and commit after a few seconds. Either way, one tap must not be final.</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Ledger.js:1541-1549 (del, delRevenue); :886 and :912 (revenue invoice/payment trash); :1264 (expense trash)</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -5482,17 +5482,17 @@
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>FN-07</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Finance for Sales and Production</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>Sales / Production</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -5517,47 +5517,47 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Permissions / dead end</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Signed in as Sales and as Production (neither holds ledger or finance), opened Finance from the nav / Money dock, and visited every tab.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>A role either cannot reach Finance, or reaches a version of it that works for them and says what they can do.</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Both roles see Finance in the nav and the Money dock and can open it - then every ledger request is refused (6 x 403). The Overview sits on 'Loading...' forever. Revenue, Expenses, Assets and Inventory each show their empty state ('No expenses yet...'), telling the user the company has no money records rather than that they are not allowed to see them. Only the capture bar works. So the page misinforms rather than refuses.</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>Sales and Production, 1440 and 390: /ledger/summary, /expenses, /assets, /inventory, /revenue, /payables all 403; /captures/pending-count 200; overview text ends 'Loading...'; four tabs show empty-state copy.</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>The route admits perms ['ledger','finance','data_input'] (App.js:237) and the nav/dock use the same list, but the backend's require_ledger accepts only ledger or finance. Every Sales/Production user has data_input by default, so they pass the front door and fail every request behind it; the page has no isError handling to notice.</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Decide what data_input-only users should get. If it is capture only, show them the capture bar and Inbox with a line such as 'You can upload bills here; totals are visible to Finance and the Owner', and hide the money tabs. If they should not be here at all, drop data_input from the route and nav perms. In both cases handle 403 in the page (see FN-09).</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>App.js:237 (route perms); components/Layout.js:79 (nav perms); routers/ledger.py:619-625 (require_ledger); pages/Ledger.js:1522-1527 (queries without isError), :1641-1642 (Loading...)</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -5565,349 +5565,847 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>FN-08</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Adding records on a phone</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Owner / Finance</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Missing function / dead control</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>At 375-390px, looked for a way to add income, an expense, an asset and an inventory item on every tab, and tapped the 'Add expense' tile in the capture card - by script and in the browser preview.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>An owner can record an expense or income from their phone - the capture card itself offers 'Add expense'.</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>There is no way to add a record manually on a phone. The four Add buttons (Add income / expense / asset / inventory) are rendered but hidden below lg. The 'Add expense' tile in 'Simplify your finances' does nothing on any tab: it looks for an element that does not exist. Upload and scan still work, so a cash expense with no bill cannot be recorded from the phone at all.</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>Preview 375x812: tapping finance-hero-add-m opened 0 dialogs on Overview and 0 on Expenses. add-income-btn, add-expense-btn, add-asset-btn and add-inventory-btn are in the DOM but invisible on all four tabs; the only visible 'Add' is the dead tile.</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>The tile's onClick runs document.querySelector('[data-testid="ledger-add-expense"]')?.click(), but no element carries that testid - the real trigger is add-expense-btn, and it sits inside 'hidden lg:block' (Ledger.js:1630).</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Render the per-tab Add button on mobile too (drop hidden lg:block, or add a mobile placement), and have the tile open AddExpenseDialog directly through state rather than clicking a DOM node by testid.</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Ledger.js:1422-1429 (tile + querySelector), :1630 ('hidden lg:block' addBtn), :1551-1557 (addBtn per tab)</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13: the profile dialog now exposes ONE Close (36px desktop, 44px mobile) as Owner and as Sales; Team.js:572 hides the primitive's default close with [&amp;&gt;button.absolute]:hidden.</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="82" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>FN-09</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Finance when a request fails</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Aborted GET /api/ledger/summary, then separately GET /api/expenses, and read the page at 1440 and 390.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>A failed load says so and offers a retry.</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>Summary aborted: text ends 'Loading...' after 5s, both viewports. Expenses aborted: 0 rows, 'No expenses yet' shown. Screenshot finance_0913/desk_expenses_failed_v2.png.</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>Ledger's six queries read only data / isLoading; tables default to 'data || []' and render their empty state.</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
     </row>
     <row r="62" ht="82" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>FN-10</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Mobile capture card - 'Export' tile</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Owner / Finance / Sales / Production</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Copy / wrong label</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Read the four capture tiles on mobile and checked what each does.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>A tile labelled Export exports.</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>finance-hero-csv-m text 'Export CSV, Excel'; it wraps &lt;input type=file accept='.csv,.xlsx,.xls'&gt; posting to /ingest/csv.</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>Label copied from a reference design that had an export action.</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Ledger.js:1430-1437</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
     </row>
     <row r="63" ht="82" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>FN-11</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Mobile overview - 'View all 3+ action items'</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Owner / Finance</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility / tap target</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Measured interactive elements on the mobile Overview.</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Controls are at least 24px tall.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Under-24px list at 390x844: ['View all 3+ action items', 322, 20].</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>Text link with no vertical padding.</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>py-1 on the link.</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="82" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Visual / layout</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Measured the grid that renders each role group on the team roster.</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="82" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="82" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Each control in a dialog is distinguishable by name.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13: the profile dialog now exposes ONE Close (36px desktop, 44px mobile) as Owner and as Sales; Team.js:572 hides the primitive's default close with [&amp;&gt;button.absolute]:hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="82" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="82" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="82" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O63" s="2" t="inlineStr">
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr">
+      <c r="P69" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q63"/>
+  <autoFilter ref="A1:Q69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5918,7 +6416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J218"/>
+  <dimension ref="A1:J233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16220,37 +16718,37 @@
     <row r="209" ht="82" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-514</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Tabs by role</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>All six tabs open without crashing or overflowing</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16260,7 +16758,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+          <t>Overview, Revenue, Expenses, Assets, Inventory, Inbox - 0 crashes, 0 overflow</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr"/>
@@ -16268,37 +16766,37 @@
     <row r="210" ht="82" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-515</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Capture - uploads</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>Upload bill, Photo / Scan receipt and CSV report a failed upload and recover</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16308,7 +16806,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>Blocked POST /ingest/document and /ingest/csv -&gt; error toast each; 'Extracting...' clears (checked on fresh pages)</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr"/>
@@ -16316,17 +16814,17 @@
     <row r="211" ht="82" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-516</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Add dialogs - validation</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -16336,17 +16834,17 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>Empty income / expense / asset / inventory forms are refused before sending</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -16356,7 +16854,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>'Add a title, customer or amount', 'Add a title/amount or attach a bill', 'Add a name or attach a bill', 'Add an item or attach a bill'; no request sent</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr"/>
@@ -16364,17 +16862,17 @@
     <row r="212" ht="82" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-517</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Add dialogs - failed save</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -16384,17 +16882,17 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>A failed save says so and keeps the form open</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -16404,7 +16902,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>'Could not record income' / 'Failed'; dialog stays open</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr"/>
@@ -16412,65 +16910,69 @@
     <row r="213" ht="82" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-518</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Delete</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>Deleting a money record asks first</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H213" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Destructive action</t>
+        </is>
+      </c>
+      <c r="H213" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
-        </is>
-      </c>
-      <c r="J213" s="2" t="inlineStr"/>
+          <t>Expense, invoice and payment DELETE fire on the first tap; no confirmation</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>FN-06</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="82" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-519</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Revenue filters</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -16480,17 +16982,17 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>Each status filter narrows the invoice list</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -16500,7 +17002,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>all 5 / awaiting 3 / partial 0 / paid 2 / overdue 3</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr"/>
@@ -16508,69 +17010,65 @@
     <row r="215" ht="82" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-520</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>AI analysis</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>Refresh and Ask report failure and keep the question</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H215" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H215" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J215" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>'Could not refresh analysis'; 'AI is busy, try again' with the question kept</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
     </row>
     <row r="216" ht="82" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-521</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Mobile quick links</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -16580,49 +17078,45 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>View all and the Inbox arrow go where they say</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H216" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
-        </is>
-      </c>
-      <c r="J216" s="2" t="inlineStr">
-        <is>
-          <t>MW-04</t>
-        </is>
-      </c>
+          <t>View all -&gt; ?tab=revenue; Inbox arrow selects the Inbox tab</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr"/>
     </row>
     <row r="217" ht="82" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-522</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Mobile - add a record</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -16632,81 +17126,833 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>Income, expenses, assets and inventory can be added on a phone</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H217" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H217" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
-        </is>
-      </c>
-      <c r="J217" s="2" t="inlineStr"/>
+          <t>All four Add buttons hidden below lg; the 'Add expense' tile is dead</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>FN-08</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="82" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
+          <t>T-523</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Mobile - capture labels</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Each capture tile's label matches its action</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>Copy</t>
+        </is>
+      </c>
+      <c r="H218" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>'Export - CSV, Excel' uploads a spreadsheet</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>FN-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="82" customHeight="1">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>T-524</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Mobile - link size</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Owner / Finance</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Controls are at least 24px tall</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H219" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>'View all 3+ action items' is 20px tall</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>FN-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="82" customHeight="1">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>T-525</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Finance role</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>The Finance login gets the full ledger</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>All ledger calls 200; same tabs, dialogs and filters as the Owner</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221" ht="82" customHeight="1">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>T-526</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Sales / Production</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Sales / Production</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>A role without ledger access is refused clearly, not shown empty books</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H221" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Money in nav/dock; page opens; 6 ledger calls 403; overview 'Loading...' forever; four tabs say 'No ... yet'</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>FN-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="82" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>T-527</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Failed loads</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>A failed summary or expenses request says so</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>Summary: 'Loading...' forever. Expenses: 'No expenses yet'</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>FN-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="82" customHeight="1">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>T-528</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>FN-01 / FN-02 re-check</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Rupees grouped the Indian way; 'This month' shows a monthly figure</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Localisation</t>
+        </is>
+      </c>
+      <c r="H223" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>Preview 2026-09-13: still Rs 738,034 under 'This month', Revenue Rs 2,685,000</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>FN-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="82" customHeight="1">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225" ht="82" customHeight="1">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226" ht="82" customHeight="1">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227" ht="82" customHeight="1">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228" ht="82" customHeight="1">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229" ht="82" customHeight="1">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230" ht="82" customHeight="1">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H230" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="82" customHeight="1">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H231" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="82" customHeight="1">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233" ht="82" customHeight="1">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H218" s="4" t="inlineStr">
+      <c r="H233" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I218" s="2" t="inlineStr">
+      <c r="I233" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J218" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J218"/>
+  <autoFilter ref="A1:J233"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16955,7 +18201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19101,7 +20347,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>FN-06</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -19111,12 +20357,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Delete on expenses, invoices and payments</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -19124,24 +20370,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Put a confirm step in del() and delRevenue(): an AlertDialog naming the record and amount ('Delete invoice SBT/25-26/0431 for Rs 2,85,000?'). Alternatively delete optimistically with an Undo toast and commit after a few seconds. Either way, one tap must not be final.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>One tap sends the DELETE straight away. No confirmation dialog, no 'are you sure', no undo toast - for all three record types, both viewports, both roles. The trash icon is a 36px target at the end of each row, so a stray tap while scrolling a phone ledger deletes a real invoice or payment and silently changes Revenue, Received and Net profit. (The harness blocked every DELETE, so nothing was removed.)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/Ledger.js:1541-1549 (del, delRevenue); :886 and :912 (revenue invoice/payment trash); :1264 (expense trash)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -19154,7 +20400,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>FN-07</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -19164,12 +20410,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Finance for Sales and Production</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -19177,24 +20423,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Decide what data_input-only users should get. If it is capture only, show them the capture bar and Inbox with a line such as 'You can upload bills here; totals are visible to Finance and the Owner', and hide the money tabs. If they should not be here at all, drop data_input from the route and nav perms. In both cases handle 403 in the page (see FN-09).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>Both roles see Finance in the nav and the Money dock and can open it - then every ledger request is refused (6 x 403). The Overview sits on 'Loading...' forever. Revenue, Expenses, Assets and Inventory each show their empty state ('No expenses yet...'), telling the user the company has no money records rather than that they are not allowed to see them. Only the capture bar works. So the page misinforms rather than refuses.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>App.js:237 (route perms); components/Layout.js:79 (nav perms); routers/ledger.py:619-625 (require_ledger); pages/Ledger.js:1522-1527 (queries without isError), :1641-1642 (Loading...)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -19207,7 +20453,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>FN-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -19217,12 +20463,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Adding records on a phone</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -19230,24 +20476,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Render the per-tab Add button on mobile too (drop hidden lg:block, or add a mobile placement), and have the tile open AddExpenseDialog directly through state rather than clicking a DOM node by testid.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>There is no way to add a record manually on a phone. The four Add buttons (Add income / expense / asset / inventory) are rendered but hidden below lg. The 'Add expense' tile in 'Simplify your finances' does nothing on any tab: it looks for an element that does not exist. Upload and scan still work, so a cash expense with no bill cannot be recorded from the phone at all.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>pages/Ledger.js:1422-1429 (tile + querySelector), :1630 ('hidden lg:block' addBtn), :1551-1557 (addBtn per tab)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -19260,7 +20506,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -19270,12 +20516,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -19290,17 +20536,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -19313,7 +20559,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MW-17</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -19323,12 +20569,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - two close buttons, invisible focus</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -19343,17 +20589,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -19366,7 +20612,7 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MW-18</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -19376,12 +20622,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Application shell at wide widths</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -19396,17 +20642,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:634 (app-shell className)</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -19419,7 +20665,7 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -19429,12 +20675,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -19449,17 +20695,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -19472,7 +20718,7 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>MW-17</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -19482,12 +20728,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Task drawer - two close buttons, invisible focus</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -19502,17 +20748,17 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -19525,7 +20771,7 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>MW-18</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -19535,12 +20781,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Application shell at wide widths</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -19555,17 +20801,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>components/Layout.js:634 (app-shell className)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -19578,7 +20824,7 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -19588,12 +20834,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -19608,17 +20854,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -19631,7 +20877,7 @@
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -19641,12 +20887,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -19661,17 +20907,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -19684,7 +20930,7 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -19694,12 +20940,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -19714,17 +20960,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_sales</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -19737,7 +20983,7 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -19747,12 +20993,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -19767,17 +21013,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -19790,7 +21036,7 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -19800,12 +21046,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -19820,17 +21066,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_company_operating_view</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -19843,7 +21089,7 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>OP-09</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -19858,7 +21104,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>'View all' links and the formula panel (mobile)</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -19873,17 +21119,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -19896,7 +21142,7 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>OP-11</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -19911,7 +21157,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Personal (self) view - bottom band (mobile)</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -19926,17 +21172,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -19949,7 +21195,7 @@
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>OP-12</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -19964,7 +21210,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - entry point</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -19979,17 +21225,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -20002,7 +21248,7 @@
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>CR-11</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -20012,12 +21258,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Contact profile when loading fails</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -20032,17 +21278,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -20055,7 +21301,7 @@
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CR-12</t>
+          <t>OP-11</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -20065,12 +21311,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>GET /api/crm/outstanding</t>
+          <t>Personal (self) view - bottom band (mobile)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -20085,17 +21331,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
+          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
+          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
+          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -20108,7 +21354,7 @@
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>OP-12</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -20118,12 +21364,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>AI Work Coach - entry point</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -20138,17 +21384,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -20161,7 +21407,7 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>CR-11</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -20171,12 +21417,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>Contact profile when loading fails</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -20191,17 +21437,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -20214,7 +21460,7 @@
     <row r="61" ht="82" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>CR-12</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -20224,12 +21470,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>GET /api/crm/outstanding</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -20237,24 +21483,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -20267,7 +21513,7 @@
     <row r="62" ht="82" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MW-19</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -20277,12 +21523,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Department filter dropdown</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -20290,24 +21536,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -20320,7 +21566,7 @@
     <row r="63" ht="82" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -20330,12 +21576,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -20343,24 +21589,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -20373,7 +21619,7 @@
     <row r="64" ht="82" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TM-07</t>
+          <t>FN-09</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -20383,12 +21629,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog - closing</t>
+          <t>Finance when a request fails</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -20396,24 +21642,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
+          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
+          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
+          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -20426,7 +21672,7 @@
     <row r="65" ht="82" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TM-08</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -20436,12 +21682,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Default close button on every dialog</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -20456,17 +21702,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx:37-41</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -20479,7 +21725,7 @@
     <row r="66" ht="82" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>MW-19</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -20489,12 +21735,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Department filter dropdown</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -20509,17 +21755,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -20532,7 +21778,7 @@
     <row r="67" ht="82" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -20542,12 +21788,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -20562,17 +21808,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -20585,7 +21831,7 @@
     <row r="68" ht="82" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -20595,12 +21841,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -20615,17 +21861,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -20638,7 +21884,7 @@
     <row r="69" ht="82" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -20648,12 +21894,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -20668,17 +21914,17 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -20691,7 +21937,7 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>OP-13</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -20701,12 +21947,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' and 'See all' links</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -20721,17 +21967,17 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -20744,7 +21990,7 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>OP-14</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -20754,12 +22000,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - error page</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -20774,17 +22020,17 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>pages/WorkCoach.js:36-57</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -20797,7 +22043,7 @@
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>CR-09</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -20807,12 +22053,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - Score with AI</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -20827,17 +22073,17 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -20850,7 +22096,7 @@
     <row r="73" ht="82" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>CR-13</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -20860,12 +22106,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -20880,17 +22126,17 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -20903,7 +22149,7 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>CR-14</t>
+          <t>OP-13</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -20913,12 +22159,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - 'Back to CRM' (desktop)</t>
+          <t>'Back to company' and 'See all' links</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -20933,17 +22179,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>py-1 or min-h-6 on the back link.</t>
+          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
+          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:205 (profile-back)</t>
+          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -20956,7 +22202,7 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>OP-14</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -20966,12 +22212,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>AI Work Coach - error page</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -20986,17 +22232,17 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/WorkCoach.js:36-57</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -21009,7 +22255,7 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>CR-09</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -21019,12 +22265,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Contact profile (mobile) - Score with AI</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -21032,24 +22278,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -21062,7 +22308,7 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>CR-13</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -21077,7 +22323,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -21085,24 +22331,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -21115,7 +22361,7 @@
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-14</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -21125,12 +22371,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Contact profile - 'Back to CRM' (desktop)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -21138,24 +22384,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>py-1 or min-h-6 on the back link.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/ContactProfile.js:205 (profile-back)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -21168,7 +22414,7 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>FN-10</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -21178,12 +22424,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Mobile capture card - 'Export' tile</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -21191,24 +22437,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Ledger.js:1430-1437</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -21221,7 +22467,7 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>FN-11</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -21231,12 +22477,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Mobile overview - 'View all 3+ action items'</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -21244,24 +22490,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>py-1 on the link.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -21274,7 +22520,7 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -21289,7 +22535,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -21297,24 +22543,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -21327,58 +22573,376 @@
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Page heading in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="82" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>CR-03</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog - dismiss controls</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="82" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="82" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="82" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="82" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="82" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr">
+      <c r="F88" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="4" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K82"/>
+  <autoFilter ref="A1:K88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22390,7 +23954,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>217 (143 pass, 72 fail, 0 blocked, 2 not run)</t>
+          <t>232 (151 pass, 79 fail, 0 blocked, 2 not run)</t>
         </is>
       </c>
     </row>
@@ -22402,7 +23966,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>2 Critical, 17 High, 21 Medium, 15 Low, 7 Nit</t>
+          <t>2 Critical, 20 High, 22 Medium, 17 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$233</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6404,8 +6404,1253 @@
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
     </row>
+    <row r="70" ht="82" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GL-01</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Desktop header - notification bell</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Broken control</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Real mouse click on the desktop bell on My Work, Decision Desk, Team and Finance, tracing aria-expanded, the dropdown and document.activeElement every 25ms.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>The bell opens the notification dropdown and it stays open until dismissed.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>/inbox: pointerdown 20ms -&gt; expanded true + dropdown at 138ms -&gt; expanded false, dropdown gone, focus BODY at 541ms. /finance: opens at 148ms and stays open. elementFromPoint at the bell centre is the bell on every page (nothing covering).</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Likely a remount: Bellicon is declared as a component INSIDE Layout's render (const Bellicon = (...) =&gt; &lt;Popover&gt;...). Every Layout re-render creates a new component type, so React unmounts the open Popover and mounts a closed one. Pages whose data refreshes around the click (Desk polls every 30s, notifications refetch) re-render Layout in that window; Finance happened not to.</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="82" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GL-02</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Mobile More panel - non-owners</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Sales / Production / Finance</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Navigation parity</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Signed in as each non-owner at 390px, opened More and listed every tile; searched the Desk for any other link to Ops, Team or Settings.</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>A page a role can open on desktop can be reached on the phone.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>More tiles for all three roles: ['Workflows', 'Leave']; visible links on their Desk to /operating-score, /team, /settings: 0, 0, 0. Desktop nav pills for the same users include nav-ops and nav-team.</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>AllAppsPanel filters Ops and Settings with ownerOnly and Team with perm: 'team_manage', while the routes and the desktop nav use looser rules.</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="82" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GL-03</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>/login while signed in</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Signed in as the owner, then opened /login directly.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>An already signed-in user is taken into the app.</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Owner session, /login -&gt; stays on /login showing 'Sign in - Access your company brain', both viewports.</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Login.js does not check for an existing session before rendering.</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js (component top)</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="82" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>DD-01</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>/decisions/:id - missing or not yours</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Dead end / misleading error</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Opened /decisions/does-not-exist as all four roles, and a real pending decision as a non-participant; tried Escape and an outside tap; checked in the browser preview.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>The page says what went wrong and offers a way back.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>All 4 roles x 1440/390: controls inside the dialog = []; Escape leaves = false; outside tap leaves = false. API 404 for the unknown id, 403 for a non-participant. Preview at 375x812 confirms.</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>DecisionDialog's isError branch renders only a title and a sentence - the Close button exists only in the success branch - while variant='page' prevents Escape and outside dismissal (KM-28). isError also does not look at the status code.</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="82" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>DD-02</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Desk board when loading fails</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Error handling / misleading</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Aborted GET /api/desk?chip=* and read the Desk at 1440 and 390.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>The Desk says it could not load.</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Board text after the abort: 'Decision desk Nothing waiting on you Needs your decision 0 On fire 0 Due today 0 Important 0'. Without the abort: 53 / 58 / 0 / 0.</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>The four useQueries read only data; counters fall back to all-zero when no query has data, and the sections render their empty copy.</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="82" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>DD-03</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Money tiles for Sales / Production</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Sales / Production</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Permissions / endless loading</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Signed in as Sales and Production and read every KPI tile on the Desk.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Tiles a role cannot see are hidden; tiles it can see load.</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Sales desktop tiles: Delayed 20 / Complaints 16 / Score mix - / To collect (overdue) Rs 7.5 L / Net profit ... / Spend, this month .... GET /ledger/summary 403.</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>useDeskMetrics fetches the ledger summary for every role and the tiles render a loading glyph when the data never arrives; the receivables figure comes from an ungated source (see CR-12).</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76" ht="82" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>DD-04</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Company / You switch (mobile)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Missing function</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>At 375-390px, listed the scope controls on the Desk.</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>The owner can switch between the company score and their own on a phone.</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>desk-scope-pills and desk-scope-pills-side: width 0 at 375px (preview) and 390px (script); both visible and working at 1440.</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Both placements are gated to lg and no mobile placement was kept.</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Show the joined pill pair above the score below lg.</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="82" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>DD-05</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Decision review - note mic</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Dead control</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Pressed the microphone under 'Send a note' on a pending decision.</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>The mic records a voice note, as its helper line promises ('Or tap the mic - speaking is faster than typing').</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Toast text on both viewports; no recording state, no permission prompt.</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>onClick is a placeholder toast.</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>components/DecisionDialog.js:421-445</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="82" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>CL-01</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Notifications, People, Journal, Calendar when loading fails</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Error handling / misleading</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Aborted each page's main GET (notifications, users, journal, calendar) at 1440 and 390.</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Each page says it could not load.</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Text after each abort, both viewports: see T-650..T-653.</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>The pages read only data / isLoading and fall through to their empty states.</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="82" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>CL-02</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Calendar events</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Dead end</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Tapped an event in Week view (script at 1440/390 and the browser preview).</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>An event opens what it is - the task, meeting, payment or leave it came from.</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>cal-event-*: tag DIV, no href, no role, cursor auto; URL unchanged after a tap; no dialog opened. 9 events in the week, all the same.</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>Calendar renders events for display only.</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>pages/Calendar.js:233 (cal-event)</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="82" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>CL-03</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Mark all read</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Silent failure</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Pressed Mark all read with the request blocked, on a fresh page.</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>A failed action says so.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>POST /notifications/read-all blocked -&gt; toasts [], unread dots 28 -&gt; 28.</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>The mutation has no onError.</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>toast.error('Couldn't mark notifications read') in onError.</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>pages/Notifications.js:17-21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="82" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>CL-04</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Operations tab - add links</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility / tap target</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Measured controls on Settings at 1440.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Controls are at least 24px tall.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Under-24px list on /settings at 1440.</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>Text buttons without vertical padding.</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>py-1 / min-h-6 on both.</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="82" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>AU-01</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Login, sign-up and admin fields</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Checked every input on /login, /signup and /admin for a programmatic label.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Each field is named for assistive technology.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Unlabelled: login-email-input, login-password-input, signup-input-company_name, admin-email-input, admin-password-input (both viewports; admin also in preview).</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>Placeholder / visual captions instead of &lt;label htmlFor&gt;.</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="82" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>AU-02</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Mobile OTP - phone number</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Entered a 3-digit number on the Mobile OTP tab and pressed Send (request blocked).</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>An obviously invalid number is refused before a code is requested.</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>POST /auth/otp/request fired for '123'; error 'Something went wrong. Please try again.'</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>No client-side length/format check on otp-phone-input.</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js:179-190, :317</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="82" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>AU-03</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Login - header links (desktop)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility / tap target</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Measured controls on /login at 1440.</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Links are at least 24px tall.</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Under-24px list on /login at 1440; both fine on mobile.</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Inline text links without padding.</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>py-1 on both links.</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js:241-246</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q69"/>
+  <autoFilter ref="A1:Q84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6416,7 +7661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J233"/>
+  <dimension ref="A1:J271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17951,8 +19196,1888 @@
       </c>
       <c r="J233" s="2" t="inlineStr"/>
     </row>
+    <row r="234" ht="82" customHeight="1">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>T-600</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Signed-out access</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Every protected route sends a signed-out visitor to sign-in</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>15 of 15 redirect to /login</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235" ht="82" customHeight="1">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>T-601</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Role x route matrix</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Each role gets Access Denied exactly where its permissions say</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H235" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>Journal owner-only and CRM needs People: Access Denied for Sales, Production and Finance; everything else opens</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr"/>
+    </row>
+    <row r="236" ht="82" customHeight="1">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>T-602</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Redirects</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Every retired route lands on its new home</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>13 of 13: /brief, /dashboard, /leave, /review, /ingest, /tasks, /priorities, /meetings, /ledger, /ask, /contacts, /inbox-legacy, unknown path</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237" ht="82" customHeight="1">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>T-603</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Desktop nav + search + user menu</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Nav pills route and mark current; search (button + Ctrl+K) hands to Dex; Settings only for owner</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H237" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>0 problems across 4 roles; language switcher shows 3 options</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238" ht="82" customHeight="1">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>T-604</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Mobile dock + More</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Every dock item and More tile opens a page the role can use</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>Owner 7 tiles, others 2; 0 dead ends</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239" ht="82" customHeight="1">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>T-605</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Desktop notification bell</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>The bell dropdown opens and stays open</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H239" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>Closes itself ~0.4s after opening on Desk, My Work and Team; stays on Finance</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>GL-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="82" customHeight="1">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>T-606</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Mobile notification bell</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>The bell dropdown opens on a phone</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>Preview: dropdown with 7 items and '28 new'</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241" ht="82" customHeight="1">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>T-607</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>Mobile reach - non-owners</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>Sales / Production / Finance</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Ops, Team and Settings are reachable on a phone</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="H241" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>More shows only Workflows and Leave; no other link</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>GL-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="82" customHeight="1">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>T-608</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>/login while signed in</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>A signed-in user is taken into the app</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H242" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in form shown again</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>GL-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="82" customHeight="1">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>T-620</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Desk load</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>The Desk loads with its KPI tiles and sections</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>Owner 53 decisions / 58 on fire; 0 overflow; 0 undersized controls</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244" ht="82" customHeight="1">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>T-621</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Scope pills</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Company / You switches the score</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>19 &lt;-&gt; 4</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245" ht="82" customHeight="1">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>T-622</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Scope pills</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Company / You is available on a phone</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>Missing function</t>
+        </is>
+      </c>
+      <c r="H245" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>Pills hidden at phone width</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>DD-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="82" customHeight="1">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>T-623</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>KPI tiles</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Every KPI tile opens its page</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>6 desktop / 4 mobile tiles, 0 dead ends</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247" ht="82" customHeight="1">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>T-624</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>KPI tiles - non-owners</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Sales / Production</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Money tiles load or are hidden</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H247" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Net profit and Spend stay '...'; receivables shown</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>DD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="82" customHeight="1">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>T-625</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Card action Review</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Review opens the decision page; Close returns to the Desk</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>-&gt; /decisions/&lt;id&gt;; Close -&gt; /inbox (re-checked on a fresh page)</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249" ht="82" customHeight="1">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>T-626</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Approve / Reject / note</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Reject needs a second tap; failures report and keep the page</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Reject warning first; 'Could not reject' / 'Could not approve' / 'Could not post note'; Send note disabled while empty</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250" ht="82" customHeight="1">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>T-627</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Leave approvals</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Approve, Reject and Info each respond</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>Approve sends (blocked -&gt; 'Action failed'); Reject and Info open a note with Send / Cancel</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251" ht="82" customHeight="1">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>T-628</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Decision - missing or not yours</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>The page explains itself and offers a way back</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Dead end</t>
+        </is>
+      </c>
+      <c r="H251" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>'Access restricted', no controls, Escape and outside tap disabled</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>DD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="82" customHeight="1">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>T-629</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Desk - failed load</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>A failed board load says so</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H252" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>'Nothing waiting on you' with zeros</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>DD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="82" customHeight="1">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>T-630</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Decision - note mic</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>The mic records a note</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Dead control</t>
+        </is>
+      </c>
+      <c r="H253" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>Toast only</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>DD-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="82" customHeight="1">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>T-640</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Ask Dex</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>A failed question is reported in the chat and not left spinning</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>'AI service error. Please try again.'; Clear resets; mic says 'Microphone not available'; /brain?q= asks</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255" ht="82" customHeight="1">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>T-641</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Documents panel loads; Add is owner-only; empty upload refused; delete asks first</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>'No documents in the Brain yet' (preview); add button owner only; submit disabled when empty</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256" ht="82" customHeight="1">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>T-642</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Views, week navigation, day selection, search and a decision's timeline work</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>Timeline/Calendar views; Aug &lt;-&gt; Sep; timeline dialog with events; no-match copy</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257" ht="82" customHeight="1">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>T-643</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Modes, week navigation and filters work</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>Day/Week; filters change counts (meetings 2, tasks 5, leave 2)</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258" ht="82" customHeight="1">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>T-644</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Calendar events</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>An event opens its source</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>Dead end</t>
+        </is>
+      </c>
+      <c r="H258" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>Events are plain divs; tap does nothing</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>CL-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="82" customHeight="1">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>T-645</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Notifications list</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>The list loads with unread markers</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H259" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>Owner 100 / 28 unread; Sales 66</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260" ht="82" customHeight="1">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>T-646</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Mark all read failure</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>A failed Mark all read says so</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Silent failure</t>
+        </is>
+      </c>
+      <c r="H260" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>No toast, dots unchanged</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>CL-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="82" customHeight="1">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>T-647</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Owner tabs open and deep-link; others get Profile + Security; saves report failure</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H261" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>4 tabs with ?tab=; Business/Operations/Money/Account saves report 'Could not save' etc. (Money re-checked on a fresh page); theme toggles</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262" ht="82" customHeight="1">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>T-648</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Settings add links</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Controls are at least 24px tall</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H262" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>'Add operational task' and 'Add approval rule' 20px</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>CL-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="82" customHeight="1">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>T-649</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>People tabs</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Tabs switch; non-managers see a read-only banner</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H263" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>Employees / Buyers / Suppliers; banner names the missing permission</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264" ht="82" customHeight="1">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>T-650</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Failed loads - Notifications / People / Journal / Calendar</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Each page says it could not load</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H264" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>'You're all caught up' / 'No team members yet' / header only / all 0</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>CL-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="82" customHeight="1">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>T-670</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Login validation</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Empty and malformed sign-ins are refused before sending</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H265" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>Browser validation on email and password; no request</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266" ht="82" customHeight="1">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>T-671</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Login failures</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>A failed sign-in, demo seat or OTP send is reported</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>'Something went wrong. Please try again.' each time; stays on /login</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267" ht="82" customHeight="1">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>T-672</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>Invite link</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>A bad invite link says it is invalid</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="H267" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>'This invite link is invalid or has already been used'; no SMS request</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268" ht="82" customHeight="1">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>T-673</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Sign-up validation</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Empty company name is refused before anything is created</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>'Tell us your company name', focus moved to the field (preview)</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269" ht="82" customHeight="1">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>T-674</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Field labels</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Every sign-in field is labelled</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H269" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>Login, sign-up company name and admin fields unlabelled</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>AU-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="82" customHeight="1">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>T-675</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>OTP number</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>An invalid mobile number is refused before sending</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H270" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>3-digit number sent</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>AU-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="82" customHeight="1">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>T-676</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Admin portal gating</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Signed out / Owner</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Only platform admins reach the portal</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>Signed out and tenant owner both get the admin sign-in; /admin/me 401; deep link /admin/tenants too</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J233"/>
+  <autoFilter ref="A1:J271"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17963,7 +21088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18189,8 +21314,89 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="82" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>N-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>The OTP flow auto-fills a 'Dev OTP' returned by the server - looks like a leaked login code.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>The server only includes dev_otp when a separate DEV_OTP_IN_RESPONSE flag is on AND no SMS provider is configured (FIX-006-C / S0-04). It cannot happen silently in production.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Read services/otp.py:152-163 and config.py:167-170.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="82" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>N-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Sales, Production and Finance see every Desk section at 0 while Ops shows them 20 overdue tasks.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>By design: for non-owners 'On fire' and 'Due today' list work they are waiting on from OTHER people; their own tasks live on My Work (desk.py docstrings).</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Read routers/desk.py:499-601; Priya's overdue tasks appear on /my-work?filter=overdue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="82" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>N-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Is the admin console reachable by a signed-in company owner?</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No. /admin has its own session; a tenant owner sees the admin sign-in and GET /api/admin/me answers 401.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Scripted at 1440 and 390 and checked in the browser preview.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18201,7 +21407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20506,7 +23712,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>DD-01</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -20516,12 +23722,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>/decisions/:id - missing or not yours</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -20529,24 +23735,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -20559,7 +23765,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>DD-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -20569,12 +23775,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Desk board when loading fails</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -20582,24 +23788,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -20612,7 +23818,7 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -20622,12 +23828,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -20642,17 +23848,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -20665,7 +23871,7 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -20675,12 +23881,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -20695,17 +23901,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -20718,7 +23924,7 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MW-17</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -20733,7 +23939,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - two close buttons, invisible focus</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -20748,17 +23954,17 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -20771,7 +23977,7 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MW-18</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -20781,12 +23987,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Application shell at wide widths</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -20801,17 +24007,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:634 (app-shell className)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -20824,7 +24030,7 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-17</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -20834,12 +24040,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Task drawer - two close buttons, invisible focus</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -20854,17 +24060,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -20877,7 +24083,7 @@
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>MW-18</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -20887,12 +24093,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Application shell at wide widths</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -20907,17 +24113,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>components/Layout.js:634 (app-shell className)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -20930,7 +24136,7 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -20940,12 +24146,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -20960,17 +24166,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -20983,7 +24189,7 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -20993,12 +24199,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -21013,17 +24219,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -21036,7 +24242,7 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -21051,7 +24257,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -21066,17 +24272,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -21089,7 +24295,7 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -21099,12 +24305,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -21119,17 +24325,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_sales</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -21142,7 +24348,7 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -21152,12 +24358,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -21172,17 +24378,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -21195,7 +24401,7 @@
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -21210,7 +24416,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -21225,17 +24431,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_company_operating_view</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -21248,7 +24454,7 @@
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>OP-09</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -21263,7 +24469,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>'View all' links and the formula panel (mobile)</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -21278,17 +24484,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -21301,7 +24507,7 @@
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>OP-11</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -21316,7 +24522,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Personal (self) view - bottom band (mobile)</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -21331,17 +24537,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -21354,7 +24560,7 @@
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>OP-12</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -21369,7 +24575,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - entry point</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -21384,17 +24590,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -21407,7 +24613,7 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CR-11</t>
+          <t>OP-11</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -21417,12 +24623,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Contact profile when loading fails</t>
+          <t>Personal (self) view - bottom band (mobile)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -21437,17 +24643,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
+          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
+          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
+          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -21460,7 +24666,7 @@
     <row r="61" ht="82" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>CR-12</t>
+          <t>OP-12</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -21470,12 +24676,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>GET /api/crm/outstanding</t>
+          <t>AI Work Coach - entry point</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -21490,17 +24696,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
+          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
+          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
+          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -21513,7 +24719,7 @@
     <row r="62" ht="82" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>CR-11</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -21523,12 +24729,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>Contact profile when loading fails</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -21543,17 +24749,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -21566,7 +24772,7 @@
     <row r="63" ht="82" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>CR-12</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -21576,12 +24782,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>GET /api/crm/outstanding</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -21596,17 +24802,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -21619,7 +24825,7 @@
     <row r="64" ht="82" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FN-09</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -21634,7 +24840,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Finance when a request fails</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -21649,17 +24855,17 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -21672,7 +24878,7 @@
     <row r="65" ht="82" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -21682,12 +24888,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -21695,24 +24901,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -21725,7 +24931,7 @@
     <row r="66" ht="82" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MW-19</t>
+          <t>FN-09</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -21735,12 +24941,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Department filter dropdown</t>
+          <t>Finance when a request fails</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -21748,24 +24954,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
+          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
+          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
+          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -21778,7 +24984,7 @@
     <row r="67" ht="82" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>GL-01</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -21788,12 +24994,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Desktop header - notification bell</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -21801,24 +25007,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -21831,7 +25037,7 @@
     <row r="68" ht="82" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TM-07</t>
+          <t>GL-02</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -21841,12 +25047,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog - closing</t>
+          <t>Mobile More panel - non-owners</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -21854,24 +25060,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
+          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
+          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
+          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -21884,7 +25090,7 @@
     <row r="69" ht="82" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TM-08</t>
+          <t>DD-03</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -21894,12 +25100,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Default close button on every dialog</t>
+          <t>Money tiles for Sales / Production</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -21907,24 +25113,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
+          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
+          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx:37-41</t>
+          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -21937,7 +25143,7 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>CL-01</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -21947,12 +25153,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Notifications, People, Journal, Calendar when loading fails</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -21960,24 +25166,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -21990,7 +25196,7 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>CL-02</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -22000,12 +25206,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Calendar events</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -22013,24 +25219,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/Calendar.js:233 (cal-event)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -22043,7 +25249,7 @@
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -22053,12 +25259,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -22073,17 +25279,17 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -22096,7 +25302,7 @@
     <row r="73" ht="82" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>MW-19</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -22106,12 +25312,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Department filter dropdown</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -22126,17 +25332,17 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -22149,7 +25355,7 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>OP-13</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -22159,12 +25365,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' and 'See all' links</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -22179,17 +25385,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -22202,7 +25408,7 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>OP-14</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -22212,12 +25418,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - error page</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -22232,17 +25438,17 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>pages/WorkCoach.js:36-57</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -22255,7 +25461,7 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>CR-09</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -22265,12 +25471,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - Score with AI</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -22285,17 +25491,17 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -22308,7 +25514,7 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>CR-13</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -22323,7 +25529,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -22338,17 +25544,17 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -22361,7 +25567,7 @@
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>CR-14</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -22376,7 +25582,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - 'Back to CRM' (desktop)</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -22391,17 +25597,17 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>py-1 or min-h-6 on the back link.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:205 (profile-back)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -22414,7 +25620,7 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FN-10</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -22424,12 +25630,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Mobile capture card - 'Export' tile</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -22444,17 +25650,17 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1430-1437</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -22467,7 +25673,7 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FN-11</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -22477,12 +25683,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Mobile overview - 'View all 3+ action items'</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -22497,17 +25703,17 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>py-1 on the link.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -22520,7 +25726,7 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>OP-13</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -22530,12 +25736,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>'Back to company' and 'See all' links</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -22550,17 +25756,17 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -22573,7 +25779,7 @@
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>OP-14</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -22583,12 +25789,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>AI Work Coach - error page</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -22596,24 +25802,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/WorkCoach.js:36-57</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -22626,7 +25832,7 @@
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>CR-09</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -22641,7 +25847,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Contact profile (mobile) - Score with AI</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -22649,24 +25855,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -22679,7 +25885,7 @@
     <row r="84" ht="82" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-13</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -22689,12 +25895,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -22702,24 +25908,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -22732,7 +25938,7 @@
     <row r="85" ht="82" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>CR-14</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -22742,12 +25948,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Contact profile - 'Back to CRM' (desktop)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -22755,24 +25961,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>py-1 or min-h-6 on the back link.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/ContactProfile.js:205 (profile-back)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -22785,7 +25991,7 @@
     <row r="86" ht="82" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>FN-10</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -22795,12 +26001,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Mobile capture card - 'Export' tile</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -22808,24 +26014,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Ledger.js:1430-1437</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -22838,7 +26044,7 @@
     <row r="87" ht="82" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>FN-11</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -22848,12 +26054,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Mobile overview - 'View all 3+ action items'</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -22861,24 +26067,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>py-1 on the link.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -22891,58 +26097,853 @@
     <row r="88" ht="82" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="82" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GL-03</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>/login while signed in</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js (component top)</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="82" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>DD-04</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Company / You switch (mobile)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Show the joined pill pair above the score below lg.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="82" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>DD-05</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Decision review - note mic</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>components/DecisionDialog.js:421-445</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="82" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>CL-03</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Mark all read</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>toast.error('Couldn't mark notifications read') in onError.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>pages/Notifications.js:17-21</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="82" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>CL-04</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Operations tab - add links</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>py-1 / min-h-6 on both.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="82" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>AU-01</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Login, sign-up and admin fields</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="82" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>AU-02</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Mobile OTP - phone number</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js:179-190, :317</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="82" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>AU-03</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Login - header links (desktop)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>py-1 on both links.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js:241-246</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="82" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Page heading in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="82" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>CR-03</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog - dismiss controls</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="82" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="82" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="82" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="82" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="82" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="F103" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="4" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K88"/>
+  <autoFilter ref="A1:K103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23954,7 +27955,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>232 (151 pass, 79 fail, 0 blocked, 2 not run)</t>
+          <t>270 (175 pass, 93 fail, 0 blocked, 2 not run)</t>
         </is>
       </c>
     </row>
@@ -23966,7 +27967,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>2 Critical, 20 High, 22 Medium, 17 Low, 7 Nit</t>
+          <t>2 Critical, 22 High, 27 Medium, 25 Low, 7 Nit</t>
         </is>
       </c>
     </row>
@@ -23978,7 +27979,7 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -1672,9 +1672,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1722,7 +1722,11 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 (0a57743): clicking the title, empty space, status, Log update and Add manually leaves the drawer open - 5 of 5 at 1440 and 5 of 5 at 390.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="82" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1755,9 +1759,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1805,7 +1809,11 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 (0a57743): 'View details' at the foot of the drawer opens the detail dialog; Delete task is there and asks for confirmation before any DELETE is sent (1440 and 390).</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="82" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1838,9 +1846,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1890,7 +1898,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED 2026-09-13 on the newest code (78d01df): close tab still at x=-43 and stock close still under the title. Tapping inside the drawer now closes it, but only because of MW-20; once MW-20 is fixed this dead end returns, so fix both together.</t>
+          <t>VERIFIED FIXED 2026-09-13 (0a57743, 89ed015): at 390px the close sits in the drawer header, 44x44 and tappable; the drawer is 92% wide so tapping the strip beside it closes it; Escape still closes.</t>
         </is>
       </c>
     </row>
@@ -1925,9 +1933,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1977,7 +1985,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED 2026-09-13 on the newest code: tapping Log update now closes the drawer outright (MW-20) and no form mounts. The hidden-body cause below still applies once MW-20 is fixed.</t>
+          <t>VERIFIED FIXED 2026-09-13 (0a57743): on a phone, Log update opens a visible update form inside the drawer.</t>
         </is>
       </c>
     </row>
@@ -2012,9 +2020,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2062,7 +2070,11 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 (0a57743): one close control ('Close task') at 1440 and 390, and focus lands on it when the drawer opens.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2095,9 +2107,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2145,7 +2157,11 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 (0a57743): at 1920 /finance and /team are capped at 1400px again; /my-work keeps the full 1920.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2178,9 +2194,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2228,7 +2244,11 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 (0a57743): Department lists only departments holding work ('All 25', 'Logistics 1'); Completed moved to the Status filter.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -10464,14 +10484,14 @@
           <t>Usability</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Lists 'Completed' as a department and six 0-count options; picking one is silently undone</t>
+          <t>Was: Completed listed as a department + six 0-count options (MW-19). Re-checked after 0a57743: All 25 / Logistics 1; Completed is under Status</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -10516,14 +10536,14 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Opens (672px, whole card and Enter both work, checkbox does not open it) - but on the newest code any click inside closes it</t>
+          <t>Was: any click inside closed it (MW-20). Re-checked after 0a57743: stays open for all 5 inside clicks</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -10620,14 +10640,14 @@
           <t>Regression</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Passed on 2a17592 (form visible, no crash); after 78d01df the click closes the drawer and no form appears</t>
+          <t>Re-checked after 0a57743: form visible, drawer stays open</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -10672,14 +10692,14 @@
           <t>Navigation</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Close tab at x=-43 off-screen, stock close under the title, no scrim, Back leaves the page</t>
+          <t>Was: no reachable close (MW-15). Re-checked after 0a57743 + 89ed015: 44px close in the header, scrim strip tap closes, Escape closes</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -10724,14 +10744,14 @@
           <t>Regression</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Form mounts inside the display:none desktop body</t>
+          <t>Was: form inside a hidden body (MW-16). Re-checked after 0a57743: form visible</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -10776,14 +10796,14 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Two close buttons; initial focus on the stock one hidden under the title</t>
+          <t>Was: two closes, focus hidden (MW-17). Re-checked after 0a57743: one close, focus on it</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -10828,14 +10848,14 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Cap removed in shared Layout; Finance tiles and Team cards stretch to ~610px</t>
+          <t>Was: cap removed globally (MW-18). Re-checked after 0a57743: Finance and Team 1400px, My Work 1920px</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -10880,14 +10900,14 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>10 of 10 clicks closed the drawer across 1440 and 390</t>
+          <t>Was: 10 of 10 closed it (MW-20). Re-checked after 0a57743: 10 of 10 stay open</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -10932,14 +10952,14 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>No Delete / View details control anywhere; the detail dialog has no opener</t>
+          <t>Was: unreachable (MW-21). Re-checked after 0a57743: View details -&gt; Delete task -&gt; confirm step</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -27955,7 +27975,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>270 (175 pass, 93 fail, 0 blocked, 2 not run)</t>
+          <t>270 (184 pass, 84 fail, 0 blocked, 2 not run)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$273</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6427,27 +6427,27 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GL-01</t>
+          <t>MW-22</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Desktop header - notification bell</t>
+          <t>Task card - bulk-select checkbox (mobile)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -6462,42 +6462,42 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Broken control</t>
+          <t>Accessibility / mis-tap</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Real mouse click on the desktop bell on My Work, Decision Desk, Team and Finance, tracing aria-expanded, the dropdown and document.activeElement every 25ms.</t>
+          <t>Measured the bulk-select checkbox on a 390px phone after the card redesign, and hit-tested taps 10px to its left, above and right.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>The bell opens the notification dropdown and it stays open until dismissed.</t>
+          <t>The checkbox has at least a 24px tap area (it had 44x114 through its padded wrapper when N-01 was recorded), and a near-miss does not trigger something else.</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
+          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>/inbox: pointerdown 20ms -&gt; expanded true + dropdown at 138ms -&gt; expanded false, dropdown gone, focus BODY at 541ms. /finance: opens at 148ms and stays open. elementFromPoint at the bell centre is the bell on every page (nothing covering).</t>
+          <t>Full control sweep at 390x844: 25 controls under 24px, the bulk-select-* checkboxes at 16x22. Probe: own 16x16, label 16x22; taps at -10px left / top / right hit the card (false, false, false for the checkbox).</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Likely a remount: Bellicon is declared as a component INSIDE Layout's render (const Bellicon = (...) =&gt; &lt;Popover&gt;...). Every Layout re-render creates a new component type, so React unmounts the open Popover and mounts a closed one. Pages whose data refreshes around the click (Desk polls every 30s, notifications refetch) re-render Layout in that window; Finance happened not to.</t>
+          <t>98b43f4 moved the checkbox to the card's top-left corner and dropped the padded wrapper that gave it the 44x114 hit box N-01 relied on.</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
+          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
+          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GL-02</t>
+          <t>GL-01</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -6520,17 +6520,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Mobile More panel - non-owners</t>
+          <t>Desktop header - notification bell</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Sales / Production / Finance</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -6545,42 +6545,42 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Navigation parity</t>
+          <t>Broken control</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Signed in as each non-owner at 390px, opened More and listed every tile; searched the Desk for any other link to Ops, Team or Settings.</t>
+          <t>Real mouse click on the desktop bell on My Work, Decision Desk, Team and Finance, tracing aria-expanded, the dropdown and document.activeElement every 25ms.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>A page a role can open on desktop can be reached on the phone.</t>
+          <t>The bell opens the notification dropdown and it stays open until dismissed.</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
+          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>More tiles for all three roles: ['Workflows', 'Leave']; visible links on their Desk to /operating-score, /team, /settings: 0, 0, 0. Desktop nav pills for the same users include nav-ops and nav-team.</t>
+          <t>/inbox: pointerdown 20ms -&gt; expanded true + dropdown at 138ms -&gt; expanded false, dropdown gone, focus BODY at 541ms. /finance: opens at 148ms and stays open. elementFromPoint at the bell centre is the bell on every page (nothing covering).</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>AllAppsPanel filters Ops and Settings with ownerOnly and Team with perm: 'team_manage', while the routes and the desktop nav use looser rules.</t>
+          <t>Likely a remount: Bellicon is declared as a component INSIDE Layout's render (const Bellicon = (...) =&gt; &lt;Popover&gt;...). Every Layout re-render creates a new component type, so React unmounts the open Popover and mounts a closed one. Pages whose data refreshes around the click (Desk polls every 30s, notifications refetch) re-render Layout in that window; Finance happened not to.</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
+          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
+          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -6593,7 +6593,7 @@
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GL-03</t>
+          <t>GL-02</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -6603,22 +6603,22 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>/login while signed in</t>
+          <t>Mobile More panel - non-owners</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Sales / Production / Finance</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -6628,42 +6628,42 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>Navigation parity</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Signed in as the owner, then opened /login directly.</t>
+          <t>Signed in as each non-owner at 390px, opened More and listed every tile; searched the Desk for any other link to Ops, Team or Settings.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>An already signed-in user is taken into the app.</t>
+          <t>A page a role can open on desktop can be reached on the phone.</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
+          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Owner session, /login -&gt; stays on /login showing 'Sign in - Access your company brain', both viewports.</t>
+          <t>More tiles for all three roles: ['Workflows', 'Leave']; visible links on their Desk to /operating-score, /team, /settings: 0, 0, 0. Desktop nav pills for the same users include nav-ops and nav-team.</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Login.js does not check for an existing session before rendering.</t>
+          <t>AllAppsPanel filters Ops and Settings with ownerOnly and Team with perm: 'team_manage', while the routes and the desktop nav use looser rules.</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
+          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js (component top)</t>
+          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -6676,17 +6676,17 @@
     <row r="73" ht="82" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>DD-01</t>
+          <t>GL-03</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>/decisions/:id - missing or not yours</t>
+          <t>/login while signed in</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6699,9 +6699,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -6711,42 +6711,42 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Dead end / misleading error</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Opened /decisions/does-not-exist as all four roles, and a real pending decision as a non-participant; tried Escape and an outside tap; checked in the browser preview.</t>
+          <t>Signed in as the owner, then opened /login directly.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>The page says what went wrong and offers a way back.</t>
+          <t>An already signed-in user is taken into the app.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
+          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>All 4 roles x 1440/390: controls inside the dialog = []; Escape leaves = false; outside tap leaves = false. API 404 for the unknown id, 403 for a non-participant. Preview at 375x812 confirms.</t>
+          <t>Owner session, /login -&gt; stays on /login showing 'Sign in - Access your company brain', both viewports.</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>DecisionDialog's isError branch renders only a title and a sentence - the Close button exists only in the success branch - while variant='page' prevents Escape and outside dismissal (KM-28). isError also does not look at the status code.</t>
+          <t>Login.js does not check for an existing session before rendering.</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
+          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
+          <t>pages/Login.js (component top)</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DD-02</t>
+          <t>DD-01</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Desk board when loading fails</t>
+          <t>/decisions/:id - missing or not yours</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -6794,42 +6794,42 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Error handling / misleading</t>
+          <t>Dead end / misleading error</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Aborted GET /api/desk?chip=* and read the Desk at 1440 and 390.</t>
+          <t>Opened /decisions/does-not-exist as all four roles, and a real pending decision as a non-participant; tried Escape and an outside tap; checked in the browser preview.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>The Desk says it could not load.</t>
+          <t>The page says what went wrong and offers a way back.</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
+          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Board text after the abort: 'Decision desk Nothing waiting on you Needs your decision 0 On fire 0 Due today 0 Important 0'. Without the abort: 53 / 58 / 0 / 0.</t>
+          <t>All 4 roles x 1440/390: controls inside the dialog = []; Escape leaves = false; outside tap leaves = false. API 404 for the unknown id, 403 for a non-participant. Preview at 375x812 confirms.</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>The four useQueries read only data; counters fall back to all-zero when no query has data, and the sections render their empty copy.</t>
+          <t>DecisionDialog's isError branch renders only a title and a sentence - the Close button exists only in the success branch - while variant='page' prevents Escape and outside dismissal (KM-28). isError also does not look at the status code.</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
+          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
+          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DD-03</t>
+          <t>DD-02</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Money tiles for Sales / Production</t>
+          <t>Desk board when loading fails</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Sales / Production</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
@@ -6877,42 +6877,42 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Permissions / endless loading</t>
+          <t>Error handling / misleading</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Signed in as Sales and Production and read every KPI tile on the Desk.</t>
+          <t>Aborted GET /api/desk?chip=* and read the Desk at 1440 and 390.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Tiles a role cannot see are hidden; tiles it can see load.</t>
+          <t>The Desk says it could not load.</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
+          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Sales desktop tiles: Delayed 20 / Complaints 16 / Score mix - / To collect (overdue) Rs 7.5 L / Net profit ... / Spend, this month .... GET /ledger/summary 403.</t>
+          <t>Board text after the abort: 'Decision desk Nothing waiting on you Needs your decision 0 On fire 0 Due today 0 Important 0'. Without the abort: 53 / 58 / 0 / 0.</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>useDeskMetrics fetches the ledger summary for every role and the tiles render a loading glyph when the data never arrives; the receivables figure comes from an ungated source (see CR-12).</t>
+          <t>The four useQueries read only data; counters fall back to all-zero when no query has data, and the sections render their empty copy.</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
+          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
+          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -6925,7 +6925,7 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>DD-04</t>
+          <t>DD-03</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -6935,22 +6935,22 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Company / You switch (mobile)</t>
+          <t>Money tiles for Sales / Production</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Sales / Production</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
@@ -6960,42 +6960,42 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Missing function</t>
+          <t>Permissions / endless loading</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>At 375-390px, listed the scope controls on the Desk.</t>
+          <t>Signed in as Sales and Production and read every KPI tile on the Desk.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>The owner can switch between the company score and their own on a phone.</t>
+          <t>Tiles a role cannot see are hidden; tiles it can see load.</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
+          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>desk-scope-pills and desk-scope-pills-side: width 0 at 375px (preview) and 390px (script); both visible and working at 1440.</t>
+          <t>Sales desktop tiles: Delayed 20 / Complaints 16 / Score mix - / To collect (overdue) Rs 7.5 L / Net profit ... / Spend, this month .... GET /ledger/summary 403.</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Both placements are gated to lg and no mobile placement was kept.</t>
+          <t>useDeskMetrics fetches the ledger summary for every role and the tiles render a loading glyph when the data never arrives; the receivables figure comes from an ungated source (see CR-12).</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Show the joined pill pair above the score below lg.</t>
+          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
+          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -7008,7 +7008,7 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>DD-05</t>
+          <t>DD-04</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Decision review - note mic</t>
+          <t>Company / You switch (mobile)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -7043,42 +7043,42 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Dead control</t>
+          <t>Missing function</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Pressed the microphone under 'Send a note' on a pending decision.</t>
+          <t>At 375-390px, listed the scope controls on the Desk.</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>The mic records a voice note, as its helper line promises ('Or tap the mic - speaking is faster than typing').</t>
+          <t>The owner can switch between the company score and their own on a phone.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
+          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Toast text on both viewports; no recording state, no permission prompt.</t>
+          <t>desk-scope-pills and desk-scope-pills-side: width 0 at 375px (preview) and 390px (script); both visible and working at 1440.</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>onClick is a placeholder toast.</t>
+          <t>Both placements are gated to lg and no mobile placement was kept.</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
+          <t>Show the joined pill pair above the score below lg.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:421-445</t>
+          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -7091,17 +7091,17 @@
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>CL-01</t>
+          <t>DD-05</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Notifications, People, Journal, Calendar when loading fails</t>
+          <t>Decision review - note mic</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -7114,9 +7114,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
@@ -7126,42 +7126,42 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Error handling / misleading</t>
+          <t>Dead control</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Aborted each page's main GET (notifications, users, journal, calendar) at 1440 and 390.</t>
+          <t>Pressed the microphone under 'Send a note' on a pending decision.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Each page says it could not load.</t>
+          <t>The mic records a voice note, as its helper line promises ('Or tap the mic - speaking is faster than typing').</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
+          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Text after each abort, both viewports: see T-650..T-653.</t>
+          <t>Toast text on both viewports; no recording state, no permission prompt.</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>The pages read only data / isLoading and fall through to their empty states.</t>
+          <t>onClick is a placeholder toast.</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
+          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
+          <t>components/DecisionDialog.js:421-445</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -7174,17 +7174,17 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>CL-02</t>
+          <t>CL-01</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Calendar events</t>
+          <t>Notifications, People, Journal, Calendar when loading fails</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -7209,42 +7209,42 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Dead end</t>
+          <t>Error handling / misleading</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Tapped an event in Week view (script at 1440/390 and the browser preview).</t>
+          <t>Aborted each page's main GET (notifications, users, journal, calendar) at 1440 and 390.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>An event opens what it is - the task, meeting, payment or leave it came from.</t>
+          <t>Each page says it could not load.</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
+          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>cal-event-*: tag DIV, no href, no role, cursor auto; URL unchanged after a tap; no dialog opened. 9 events in the week, all the same.</t>
+          <t>Text after each abort, both viewports: see T-650..T-653.</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Calendar renders events for display only.</t>
+          <t>The pages read only data / isLoading and fall through to their empty states.</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
+          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>pages/Calendar.js:233 (cal-event)</t>
+          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -7257,17 +7257,17 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>CL-03</t>
+          <t>CL-02</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Mark all read</t>
+          <t>Calendar events</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -7280,9 +7280,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -7292,42 +7292,42 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Silent failure</t>
+          <t>Dead end</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Pressed Mark all read with the request blocked, on a fresh page.</t>
+          <t>Tapped an event in Week view (script at 1440/390 and the browser preview).</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>A failed action says so.</t>
+          <t>An event opens what it is - the task, meeting, payment or leave it came from.</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
+          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>POST /notifications/read-all blocked -&gt; toasts [], unread dots 28 -&gt; 28.</t>
+          <t>cal-event-*: tag DIV, no href, no role, cursor auto; URL unchanged after a tap; no dialog opened. 9 events in the week, all the same.</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>The mutation has no onError.</t>
+          <t>Calendar renders events for display only.</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>toast.error('Couldn't mark notifications read') in onError.</t>
+          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:17-21</t>
+          <t>pages/Calendar.js:233 (cal-event)</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -7340,27 +7340,27 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>CL-04</t>
+          <t>CL-03</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Operations tab - add links</t>
+          <t>Mark all read</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -7375,42 +7375,42 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Accessibility / tap target</t>
+          <t>Silent failure</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Measured controls on Settings at 1440.</t>
+          <t>Pressed Mark all read with the request blocked, on a fresh page.</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Controls are at least 24px tall.</t>
+          <t>A failed action says so.</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
+          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Under-24px list on /settings at 1440.</t>
+          <t>POST /notifications/read-all blocked -&gt; toasts [], unread dots 28 -&gt; 28.</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Text buttons without vertical padding.</t>
+          <t>The mutation has no onError.</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>py-1 / min-h-6 on both.</t>
+          <t>toast.error('Couldn't mark notifications read') in onError.</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
+          <t>pages/Notifications.js:17-21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -7423,27 +7423,27 @@
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AU-01</t>
+          <t>CL-04</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Login, sign-up and admin fields</t>
+          <t>Operations tab - add links</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Signed out</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -7458,42 +7458,42 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Accessibility / tap target</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Checked every input on /login, /signup and /admin for a programmatic label.</t>
+          <t>Measured controls on Settings at 1440.</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Each field is named for assistive technology.</t>
+          <t>Controls are at least 24px tall.</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
+          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Unlabelled: login-email-input, login-password-input, signup-input-company_name, admin-email-input, admin-password-input (both viewports; admin also in preview).</t>
+          <t>Under-24px list on /settings at 1440.</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Placeholder / visual captions instead of &lt;label htmlFor&gt;.</t>
+          <t>Text buttons without vertical padding.</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
+          <t>py-1 / min-h-6 on both.</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
+          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AU-02</t>
+          <t>AU-01</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Mobile OTP - phone number</t>
+          <t>Login, sign-up and admin fields</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -7541,42 +7541,42 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Entered a 3-digit number on the Mobile OTP tab and pressed Send (request blocked).</t>
+          <t>Checked every input on /login, /signup and /admin for a programmatic label.</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>An obviously invalid number is refused before a code is requested.</t>
+          <t>Each field is named for assistive technology.</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>POST /auth/otp/request fired for '123'; error 'Something went wrong. Please try again.'</t>
+          <t>Unlabelled: login-email-input, login-password-input, signup-input-company_name, admin-email-input, admin-password-input (both viewports; admin also in preview).</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>No client-side length/format check on otp-phone-input.</t>
+          <t>Placeholder / visual captions instead of &lt;label htmlFor&gt;.</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:179-190, :317</t>
+          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -7589,88 +7589,171 @@
     <row r="84" ht="82" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>AU-02</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Mobile OTP - phone number</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Entered a 3-digit number on the Mobile OTP tab and pressed Send (request blocked).</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>An obviously invalid number is refused before a code is requested.</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>POST /auth/otp/request fired for '123'; error 'Something went wrong. Please try again.'</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>No client-side length/format check on otp-phone-input.</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js:179-190, :317</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85" ht="82" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
           <t>AU-03</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Sign-in</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Login - header links (desktop)</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Desktop</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Signed out</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G84" s="7" t="inlineStr">
+      <c r="G85" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Accessibility / tap target</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>Measured controls on /login at 1440.</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>Links are at least 24px tall.</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>Under-24px list on /login at 1440; both fine on mobile.</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>Inline text links without padding.</t>
         </is>
       </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>py-1 on both links.</t>
         </is>
       </c>
-      <c r="O84" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>pages/Login.js:241-246</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr">
+      <c r="P85" s="2" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q84"/>
+  <autoFilter ref="A1:Q85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7681,7 +7764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J271"/>
+  <dimension ref="A1:J273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21051,53 +21134,153 @@
     <row r="271" ht="82" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
+          <t>T-126</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Full control sweep</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844 + Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page (writes blocked)</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>Re-run after the drawer repair: mobile 36 controls, 13 clicked, desktop 43 controls, 20 clicked; 0 click failures, 0 overflow, 0 page errors. Console errors were the harness's own blocked writes. An 'overlay not dismissed by Escape' flag did not reproduce - More and the Dex picker both close on Escape</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272" ht="82" customHeight="1">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>T-127</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Bulk-select checkbox</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>The checkbox has a 24px tap area and near-misses do not open the task</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H272" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>16x22 hit area; taps 10px away open the drawer</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>MW-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="82" customHeight="1">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
           <t>T-676</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
+      <c r="C273" s="2" t="inlineStr">
         <is>
           <t>Admin portal gating</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>Signed out / Owner</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>Only platform admins reach the portal</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H271" s="4" t="inlineStr">
+      <c r="H273" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I271" s="2" t="inlineStr">
+      <c r="I273" s="2" t="inlineStr">
         <is>
           <t>Signed out and tenant owner both get the admin sign-in; /admin/me 401; deep link /admin/tenants too</t>
         </is>
       </c>
-      <c r="J271" s="2" t="inlineStr"/>
+      <c r="J273" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J271"/>
+  <autoFilter ref="A1:J273"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21158,7 +21341,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bulk-select checkboxes measure only 16x16, below the 24px tap-target minimum.</t>
+          <t>Bulk-select checkboxes measure only 16x16, below the 24px tap-target minimum. [SUPERSEDED 2026-09-13: true when recorded; the card redesign (98b43f4) removed the padded wrapper - see MW-22.]</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -21427,7 +21610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25004,7 +25187,7 @@
     <row r="67" ht="82" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GL-01</t>
+          <t>MW-22</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -25014,12 +25197,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Desktop header - notification bell</t>
+          <t>Task card - bulk-select checkbox (mobile)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -25034,17 +25217,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
+          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
+          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
+          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -25057,7 +25240,7 @@
     <row r="68" ht="82" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GL-02</t>
+          <t>GL-01</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -25072,7 +25255,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Mobile More panel - non-owners</t>
+          <t>Desktop header - notification bell</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -25087,17 +25270,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
+          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
+          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
+          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -25110,7 +25293,7 @@
     <row r="69" ht="82" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>DD-03</t>
+          <t>GL-02</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -25120,12 +25303,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Money tiles for Sales / Production</t>
+          <t>Mobile More panel - non-owners</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -25140,17 +25323,17 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
+          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
+          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
+          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -25163,7 +25346,7 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>CL-01</t>
+          <t>DD-03</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -25173,12 +25356,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Notifications, People, Journal, Calendar when loading fails</t>
+          <t>Money tiles for Sales / Production</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -25193,17 +25376,17 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
+          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
+          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
+          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -25216,7 +25399,7 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>CL-02</t>
+          <t>CL-01</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -25226,12 +25409,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Calendar events</t>
+          <t>Notifications, People, Journal, Calendar when loading fails</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -25246,17 +25429,17 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
+          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
+          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>pages/Calendar.js:233 (cal-event)</t>
+          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -25269,7 +25452,7 @@
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>CL-02</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -25279,12 +25462,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Calendar events</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -25292,24 +25475,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/Calendar.js:233 (cal-event)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -25322,7 +25505,7 @@
     <row r="73" ht="82" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MW-19</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -25337,7 +25520,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Department filter dropdown</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -25352,17 +25535,17 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -25375,7 +25558,7 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>MW-19</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -25385,12 +25568,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Department filter dropdown</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -25405,17 +25588,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -25428,7 +25611,7 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>TM-07</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -25443,7 +25626,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog - closing</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -25458,17 +25641,17 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -25481,7 +25664,7 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TM-08</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -25491,12 +25674,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Default close button on every dialog</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -25511,17 +25694,17 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx:37-41</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -25534,7 +25717,7 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -25544,12 +25727,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -25564,17 +25747,17 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -25587,7 +25770,7 @@
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -25602,7 +25785,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -25617,17 +25800,17 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -25640,7 +25823,7 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -25650,12 +25833,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -25670,17 +25853,17 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -25693,7 +25876,7 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -25708,7 +25891,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -25723,17 +25906,17 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -25746,7 +25929,7 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>OP-13</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -25761,7 +25944,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' and 'See all' links</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -25776,17 +25959,17 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -25799,7 +25982,7 @@
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>OP-14</t>
+          <t>OP-13</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -25814,7 +25997,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - error page</t>
+          <t>'Back to company' and 'See all' links</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -25829,17 +26012,17 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
+          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
+          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>pages/WorkCoach.js:36-57</t>
+          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -25852,7 +26035,7 @@
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>CR-09</t>
+          <t>OP-14</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -25862,12 +26045,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - Score with AI</t>
+          <t>AI Work Coach - error page</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -25882,17 +26065,17 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
+          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
+          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
+          <t>pages/WorkCoach.js:36-57</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -25905,7 +26088,7 @@
     <row r="84" ht="82" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>CR-13</t>
+          <t>CR-09</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -25920,7 +26103,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
+          <t>Contact profile (mobile) - Score with AI</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -25935,17 +26118,17 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
+          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
+          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
+          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -25958,7 +26141,7 @@
     <row r="85" ht="82" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>CR-14</t>
+          <t>CR-13</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -25973,7 +26156,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - 'Back to CRM' (desktop)</t>
+          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -25988,17 +26171,17 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>py-1 or min-h-6 on the back link.</t>
+          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
+          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:205 (profile-back)</t>
+          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -26011,7 +26194,7 @@
     <row r="86" ht="82" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FN-10</t>
+          <t>CR-14</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -26021,12 +26204,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Mobile capture card - 'Export' tile</t>
+          <t>Contact profile - 'Back to CRM' (desktop)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -26041,17 +26224,17 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
+          <t>py-1 or min-h-6 on the back link.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
+          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1430-1437</t>
+          <t>pages/ContactProfile.js:205 (profile-back)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -26064,7 +26247,7 @@
     <row r="87" ht="82" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FN-11</t>
+          <t>FN-10</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -26079,7 +26262,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Mobile overview - 'View all 3+ action items'</t>
+          <t>Mobile capture card - 'Export' tile</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -26094,17 +26277,17 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>py-1 on the link.</t>
+          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
+          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
+          <t>pages/Ledger.js:1430-1437</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -26117,7 +26300,7 @@
     <row r="88" ht="82" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>FN-11</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -26127,12 +26310,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Mobile overview - 'View all 3+ action items'</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -26147,17 +26330,17 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>py-1 on the link.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -26170,7 +26353,7 @@
     <row r="89" ht="82" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GL-03</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -26180,12 +26363,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>/login while signed in</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -26200,17 +26383,17 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js (component top)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -26223,7 +26406,7 @@
     <row r="90" ht="82" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>DD-04</t>
+          <t>GL-03</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -26233,12 +26416,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Company / You switch (mobile)</t>
+          <t>/login while signed in</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -26253,17 +26436,17 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Show the joined pill pair above the score below lg.</t>
+          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
+          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
+          <t>pages/Login.js (component top)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -26276,7 +26459,7 @@
     <row r="91" ht="82" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>DD-05</t>
+          <t>DD-04</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -26291,7 +26474,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Decision review - note mic</t>
+          <t>Company / You switch (mobile)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -26306,17 +26489,17 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
+          <t>Show the joined pill pair above the score below lg.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
+          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:421-445</t>
+          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -26329,7 +26512,7 @@
     <row r="92" ht="82" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>CL-03</t>
+          <t>DD-05</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -26339,12 +26522,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Mark all read</t>
+          <t>Decision review - note mic</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -26359,17 +26542,17 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>toast.error('Couldn't mark notifications read') in onError.</t>
+          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
+          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:17-21</t>
+          <t>components/DecisionDialog.js:421-445</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -26382,7 +26565,7 @@
     <row r="93" ht="82" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>CL-04</t>
+          <t>CL-03</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -26392,12 +26575,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Operations tab - add links</t>
+          <t>Mark all read</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -26412,17 +26595,17 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>py-1 / min-h-6 on both.</t>
+          <t>toast.error('Couldn't mark notifications read') in onError.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
+          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
+          <t>pages/Notifications.js:17-21</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -26435,7 +26618,7 @@
     <row r="94" ht="82" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AU-01</t>
+          <t>CL-04</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -26445,12 +26628,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Login, sign-up and admin fields</t>
+          <t>Operations tab - add links</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -26465,17 +26648,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
+          <t>py-1 / min-h-6 on both.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
+          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
+          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -26488,7 +26671,7 @@
     <row r="95" ht="82" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AU-02</t>
+          <t>AU-01</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -26503,7 +26686,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Mobile OTP - phone number</t>
+          <t>Login, sign-up and admin fields</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -26518,17 +26701,17 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:179-190, :317</t>
+          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -26541,7 +26724,7 @@
     <row r="96" ht="82" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>AU-03</t>
+          <t>AU-02</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -26556,7 +26739,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Login - header links (desktop)</t>
+          <t>Mobile OTP - phone number</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -26571,17 +26754,17 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>py-1 on both links.</t>
+          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
+          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:241-246</t>
+          <t>pages/Login.js:179-190, :317</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -26594,7 +26777,7 @@
     <row r="97" ht="82" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>AU-03</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -26604,12 +26787,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Sign-in</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Login - header links (desktop)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -26617,24 +26800,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>py-1 on both links.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/Login.js:241-246</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -26647,7 +26830,7 @@
     <row r="98" ht="82" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -26657,12 +26840,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -26677,17 +26860,17 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -26700,7 +26883,7 @@
     <row r="99" ht="82" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -26710,12 +26893,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -26730,17 +26913,17 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -26753,7 +26936,7 @@
     <row r="100" ht="82" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -26768,7 +26951,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -26783,17 +26966,17 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -26806,7 +26989,7 @@
     <row r="101" ht="82" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -26821,7 +27004,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -26836,17 +27019,17 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
@@ -26859,7 +27042,7 @@
     <row r="102" ht="82" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-04</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -26869,12 +27052,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Member profile dialog</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -26889,17 +27072,17 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -26912,58 +27095,111 @@
     <row r="103" ht="82" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="82" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr">
+      <c r="F104" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="4" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K103"/>
+  <autoFilter ref="A1:K104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27975,7 +28211,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>270 (184 pass, 84 fail, 0 blocked, 2 not run)</t>
+          <t>272 (185 pass, 85 fail, 0 blocked, 2 not run)</t>
         </is>
       </c>
     </row>
@@ -27987,7 +28223,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>2 Critical, 22 High, 27 Medium, 25 Low, 7 Nit</t>
+          <t>2 Critical, 22 High, 28 Medium, 25 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$273</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21610,7 +21610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22749,50 +22749,54 @@
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MW-08</t>
+          <t>ASK-20</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Task card - Update / Escalate</t>
+          <t>One load-error pattern for every page (root cause 1 of 3)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
+          <t>Build ONE shared &lt;QueryError&gt; (message + Retry) and use it wherever a query's data drives the page. It must branch on the failure: 403 -&gt; 'You don't have access to this' (with who to ask), 404 -&gt; 'This no longer exists' (with a way back), network / 5xx -&gt; 'Couldn't load - Retry'. While loading or failed, counts show '-', never 0. Rule for code review: a page may not render its empty state unless the query SUCCEEDED with zero rows.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
+          <t>The audit found the same fault on every major page: the page reads only data / isLoading, so a failed request falls through to the empty state or an endless skeleton. An owner on a weak connection is told 'Nothing waiting on you' (DD-02), 'No expenses yet' (FN-09), 'You're all caught up' (CL-01), or watches a skeleton that never ends (OP-10, CR-10). A missing decision traps the user with no way out (DD-01). Staff refused by the ledger see fake empty books (FN-07, DD-03). Fixing it once, in one component, closes nine findings.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t>pages/Desk.js:284-292, pages/OperatingScore.js:85-92, pages/CRM.js:524-527, pages/Ledger.js:1522-1527, pages/ContactProfile.js:151-160, components/DecisionDialog.js:188-218, pages/Notifications.js, pages/People.js, pages/Journal.js, pages/Calendar.js; pattern to copy: pages/WorkCoach.js:36-57</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>OP-10, CR-10, CR-11, FN-07, FN-09, DD-01, DD-02, DD-03, CL-01</t>
+        </is>
+      </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
           <t>To do</t>
@@ -22802,50 +22806,54 @@
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MW-20</t>
+          <t>ASK-21</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - every click inside closes it</t>
+          <t>One permission map for route, nav and API (root cause 2 of 3)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Stop propagation at the drawer boundary: onClick={(e) =&gt; e.stopPropagation()} and onKeyDown={(e) =&gt; e.stopPropagation()} on SheetContent. Or, better, render the Sheet as a SIBLING of the card root rather than a child, so the drawer is outside the clickable element in the component tree. Also guard the root handler with e.currentTarget.contains(e.target) - that is a DOM check, which a portal click fails. Add the five-click test to the verify script.</t>
+          <t>Define each surface's access rule ONCE - e.g. finance: needs 'finance' or 'ledger'; crm: needs 'people'; ops: everyone (self view); team: everyone (read-only without team_manage) - and have App.js routes, Layout.js nav pills, AllAppsPanel.jsx tiles, the Desk's KPI tiles and the backend require_* guards all read from it. Add a test that walks every role x route and fails if the page opens while its data 403s, or if a nav/tile/link points at a page the role is refused. Decide separately whether data_input-only users get a capture-only Finance.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Every click closes it, on both viewports - 10 of 10. The drawer is now the only place a task can be worked (status, progress, Complete, Attach, Log update, hand off), so none of that is usable. On mobile the status pill tap fired its PATCH before the drawer shut, so the action happens but the user is thrown back to the list without seeing it. Likely also (from the code, not testable while the form cannot be opened): pressing Space or Enter in any drawer field hits the card's onKeyDown, which calls preventDefault and toggles the drawer - so a user could not type a space in an update note.</t>
+          <t>The rules have drifted apart in five places. The Finance route admits data_input but its API needs ledger/finance, so Sales and Production open an empty Finance (FN-07). /crm/outstanding checks nothing and serves per-customer money totals to any signed-in user (CR-12). The Desk links non-CRM roles to Access Denied (CR-13) and fetches ledger data it is refused (DD-03). The mobile More panel hides Ops, Team and Settings that the routes allow (GL-02). Every colleague can read every other colleague's access matrix (TM-05). Each fix done alone will drift again.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1242-1255 (card root onClick / onKeyDown), the &lt;Sheet&gt; rendered inside the same component (~:1360)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
+          <t>App.js:187-254 (Protected perms), components/Layout.js:58-84 (nav perms), components/mobile/AllAppsPanel.jsx:54-128 (tile filters), pages/Desk.js:563-661, lib/perms.js, routers/ledger.py:619-625, routers/crm.py:37-38, routers/finance.py</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>FN-07, CR-12, CR-13, DD-03, GL-02, TM-05; ASK-13, ASK-15</t>
+        </is>
+      </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
           <t>To do</t>
@@ -22855,27 +22863,27 @@
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MW-09</t>
+          <t>ASK-22</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Task card - 'Log update or hand off' (mobile)</t>
+          <t>Phone parity: no desktop-only actions (root cause 3 of 3)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
+          <t>Change request</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -22885,20 +22893,24 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
+          <t>Adopt a rule: any action available on desktop must have a reachable, tappable (24px+) equivalent below lg, or be deliberately marked desktop-only in the code. Audit every 'hidden lg:*' / 'lg:block' control against it. Immediate cases: Add income / expense / asset / inventory on Finance (FN-08), the CRM add menu and filter (CR-04, CR-05), Score with AI on the contact profile (CR-09), Company / You on the Desk (DD-04), Ops / Team / Settings for staff (GL-02), and a 44px bulk-select checkbox that does not open the task on a near-miss (MW-22).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
+          <t>DecisionOS is used from the owner's phone first, yet six findings are actions that exist on desktop and vanish, clip or shrink on a phone - most often because a control was wrapped in 'hidden lg:block' with no mobile placement. A cash expense with no bill cannot be recorded from a phone at all (FN-08).</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t>pages/Ledger.js:1422-1437, :1630; pages/CRM.js (mobile add + filter); pages/mobile/ContactProfileMobile.jsx; pages/Desk.js:426, :470; components/mobile/AllAppsPanel.jsx; pages/MyWork.js (bulk-select checkbox)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>FN-08, CR-04, CR-05, CR-09, DD-04, GL-02, MW-22</t>
+        </is>
+      </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
           <t>To do</t>
@@ -22908,7 +22920,7 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MW-10</t>
+          <t>MW-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -22918,12 +22930,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application shell</t>
+          <t>Task card - Update / Escalate</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -22931,24 +22943,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
+          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
+          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
+          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -22961,7 +22973,7 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MW-01</t>
+          <t>MW-20</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -22976,7 +22988,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Task card - status control</t>
+          <t>Task drawer - every click inside closes it</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -22984,24 +22996,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
+          <t>Stop propagation at the drawer boundary: onClick={(e) =&gt; e.stopPropagation()} and onKeyDown={(e) =&gt; e.stopPropagation()} on SheetContent. Or, better, render the Sheet as a SIBLING of the card root rather than a child, so the drawer is outside the clickable element in the component tree. Also guard the root handler with e.currentTarget.contains(e.target) - that is a DOM check, which a portal click fails. Add the five-click test to the verify script.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
+          <t>Every click closes it, on both viewports - 10 of 10. The drawer is now the only place a task can be worked (status, progress, Complete, Attach, Log update, hand off), so none of that is usable. On mobile the status pill tap fired its PATCH before the drawer shut, so the action happens but the user is thrown back to the list without seeing it. Likely also (from the code, not testable while the form cannot be opened): pressing Space or Enter in any drawer field hits the card's onKeyDown, which calls preventDefault and toggles the drawer - so a user could not type a space in an update note.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
+          <t>pages/MyWork.js:1242-1255 (card root onClick / onKeyDown), the &lt;Sheet&gt; rendered inside the same component (~:1360)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -23014,7 +23026,7 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MW-02</t>
+          <t>MW-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -23029,7 +23041,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Task card - detail dialog</t>
+          <t>Task card - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -23044,17 +23056,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
+          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
+          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
+          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -23067,7 +23079,7 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MW-21</t>
+          <t>MW-10</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -23077,12 +23089,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Task - Delete</t>
+          <t>Application shell</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -23097,17 +23109,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Put 'Delete task' in the drawer - a quiet destructive button at the foot of the drawer, keeping the existing confirm step - or restore a 'View details' entry. Owner-only, as it was.</t>
+          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>There is no way to delete a task. The detail dialog still contains 'Delete task' with its confirmation, but nothing opens that dialog any more. Its only entry point was 'View details' in the card's ••• menu, and 98b43f4 removed that menu on the reasoning that 'the drawer already exposes every detail action' - but the drawer has no Delete.</t>
+          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:782-940 (TaskDetailDialog + delete), :1074 and :1941 (detailOpen with no opener)</t>
+          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -23120,7 +23132,7 @@
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MW-15</t>
+          <t>MW-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -23135,7 +23147,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - close (mobile)</t>
+          <t>Task card - status control</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -23150,17 +23162,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Below sm, put the close INSIDE the drawer header (a 44px X at the right of the sticky title bar, or a back chevron at its left) and keep the protruding tab for sm and up: e.g. 'right-3 top-3 sm:left-0 sm:right-auto sm:-translate-x-full'. Alternatively leave a strip of scrim on phones (w-[92%]) so tapping outside works. Either way, test on a phone width before shipping a change to the drawer frame.</t>
+          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>There is no way to close it. The drawer is w-full, so it covers the whole screen and there is no scrim left to tap. The new left-edge close tab sits at x=-43, entirely off-screen. The stock Radix close is at top-right but the sticky title bar paints over it - only a sliver of its focus ring peeks out. Escape closes it, but phones have no Escape key. Browser Back does not close the drawer either: it leaves My Work for the previous route. A phone user who opens a task is stuck.</t>
+          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1427-1441 (SheetContent w-full + SheetClose -translate-x-full)</t>
+          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -23173,7 +23185,7 @@
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MW-16</t>
+          <t>MW-02</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -23188,7 +23200,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - 'Log update or hand off' (mobile)</t>
+          <t>Task card - detail dialog</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -23203,17 +23215,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Render TaskTrail (or at least its UpdateForm) outside the lg-gated body, shared by both layouts, or mount a second instance inside the mobile body. Add the MW-09 check to the verify script so the next drawer change cannot regress it silently.</t>
+          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Nothing appears. The button is visible and tappable, and the form IS mounted - but inside the desktop body, which is display:none below lg. This is MW-09 back: the one control that records what happened is inert on phones again. Desktop is unaffected (form opens, no crash).</t>
+          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1658-1662 (mobile trigger), :1679 (desktop body 'hidden lg:block'), :1960 (the only &lt;TaskTrail&gt;)</t>
+          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -23226,7 +23238,7 @@
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CR-04</t>
+          <t>MW-21</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -23236,12 +23248,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Add contact menu (mobile)</t>
+          <t>Task - Delete</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -23256,17 +23268,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
+          <t>Put 'Delete task' in the drawer - a quiet destructive button at the foot of the drawer, keeping the existing confirm step - or restore a 'View details' entry. Owner-only, as it was.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
+          <t>There is no way to delete a task. The detail dialog still contains 'Delete task' with its confirmation, but nothing opens that dialog any more. Its only entry point was 'View details' in the card's ••• menu, and 98b43f4 removed that menu on the reasoning that 'the drawer already exposes every detail action' - but the drawer has no Delete.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
+          <t>pages/MyWork.js:782-940 (TaskDetailDialog + delete), :1074 and :1941 (detailOpen with no opener)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -23279,7 +23291,7 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CR-05</t>
+          <t>MW-15</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -23289,12 +23301,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Filter button (mobile)</t>
+          <t>Task drawer - close (mobile)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -23309,17 +23321,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
+          <t>Below sm, put the close INSIDE the drawer header (a 44px X at the right of the sticky title bar, or a back chevron at its left) and keep the protruding tab for sm and up: e.g. 'right-3 top-3 sm:left-0 sm:right-auto sm:-translate-x-full'. Alternatively leave a strip of scrim on phones (w-[92%]) so tapping outside works. Either way, test on a phone width before shipping a change to the drawer frame.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
+          <t>There is no way to close it. The drawer is w-full, so it covers the whole screen and there is no scrim left to tap. The new left-edge close tab sits at x=-43, entirely off-screen. The stock Radix close is at top-right but the sticky title bar paints over it - only a sliver of its focus ring peeks out. Escape closes it, but phones have no Escape key. Browser Back does not close the drawer either: it leaves My Work for the previous route. A phone user who opens a task is stuck.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
+          <t>pages/MyWork.js:1427-1441 (SheetContent w-full + SheetClose -translate-x-full)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -23332,7 +23344,7 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>OP-01</t>
+          <t>MW-16</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -23342,12 +23354,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Team execution panel</t>
+          <t>Task drawer - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -23362,17 +23374,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Decide which is true and make them agree. A rolling window is the more useful of the two -- an operating score should recover when the business recovers -- so filter each query to the last 30 days and keep the caption. If all-time is deliberate, the caption has to say so.</t>
+          <t>Render TaskTrail (or at least its UpdateForm) outside the lg-gated body, shared by both layouts, or mount a second instance inside the mobile body. Add the MW-09 check to the verify script so the next drawer change cannot regress it silently.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>The panel says 'Last 30 days - open anyone to see their full ops'. The service applies no date filter anywhere: tasks, decisions, invoices and the per-employee leaderboard are all queried for the whole tenant with no window at all. So an owner reads a colleague's score believing it reflects the last month, when it carries every task since the workspace opened -- somebody who was slow in August can never recover from it, and somebody who has improved this month does not show it.</t>
+          <t>Nothing appears. The button is visible and tappable, and the form IS mounted - but inside the desktop body, which is display:none below lg. This is MW-09 back: the one control that records what happened is inert on phones again. Desktop is unaffected (form opens, no crash).</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (all queries); the caption is in pages/OperatingScore.js, team-execution section</t>
+          <t>pages/MyWork.js:1658-1662 (mobile trigger), :1679 (desktop body 'hidden lg:block'), :1960 (the only &lt;TaskTrail&gt;)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -23385,7 +23397,7 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>OP-02</t>
+          <t>CR-04</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -23395,12 +23407,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>'Do these first' on mobile</t>
+          <t>Add contact menu (mobile)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -23415,17 +23427,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>On mobile the band should flow with the page rather than being pinned, so the score, the actions and the team list scroll as one column. If it must stay pinned, it needs to collapse to a handle the user can pull up.</t>
+          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>It is 90 per cent hidden. 'Do these first' occupies y=425 to 710, and a fixed black 'Team execution' band is pinned from y=454 to the bottom of the screen -- 374px, 46 per cent of the viewport -- covering 256 of its 285px. Scrolling does not help: the document itself does not scroll (scrollHeight equals clientHeight), and the element that does scroll is the dark band, not the page. So the three actions the page exists to recommend are permanently reduced to one visible line.</t>
+          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (kr-dark-band team-execution section)</t>
+          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -23438,7 +23450,7 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>OP-03</t>
+          <t>CR-05</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -23448,12 +23460,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Filter button (mobile)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -23468,17 +23480,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Score each leg as a bounded rate rather than a penalty subtracted from a constant, so the number always has somewhere to move. Where a leg really is at the floor, say 'below floor' rather than printing a 0 that looks like an empty metric. See ASK-19 for the wider redesign.</t>
+          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Two of the four legs are pinned at the floor and carry no information. Execution reads 0 and Responsiveness reads 0. Responsiveness actually computes to -296 before clamping (100 - 16 complaints x 12 - 68 overdue x 3), so it would take closing 8 complaints AND clearing 33 overdue tasks before the number moves off zero by a single point. The page's own advice is 'Close 16 open complaints' -- doing all of that would leave the score exactly where it is. The owner gets no gradient at precisely the moment they most need one.</t>
+          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and the responsiveness expression in _company_operating_view</t>
+          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -23491,7 +23503,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>OP-10</t>
+          <t>OP-01</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -23506,7 +23518,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Ops page when the request fails</t>
+          <t>Team execution panel</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -23521,17 +23533,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Read isError and error from the query and render a message: 403 -&gt; 'Only the owner can view another person's operating page', 404 -&gt; 'This person is no longer on the team', otherwise 'Couldn't load'. Each with a link to /operating-score. WorkCoach.js:36-57 is the pattern to copy. Also set retry: false for 4xx so the error shows at once.</t>
+          <t>Decide which is true and make them agree. A rolling window is the more useful of the two -- an operating score should recover when the business recovers -- so filter each query to the last 30 days and keep the caption. If all-time is deliberate, the caption has to say so.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>The loading skeleton stays on screen forever, with aria-busy=true and no text at all. The API answered in milliseconds - 404 'Team member not found' for the owner, 403 for the three other roles - but the page never shows it. The user cannot tell a slow page from a broken link or a refused one, and there is no way back except the browser. Any stale shared link (a person who has left, a link forwarded to a teammate) lands here.</t>
+          <t>The panel says 'Last 30 days - open anyone to see their full ops'. The service applies no date filter anywhere: tasks, decisions, invoices and the per-employee leaderboard are all queried for the whole tenant with no window at all. So an owner reads a colleague's score believing it reflects the last month, when it carries every task since the workspace opened -- somebody who was slow in August can never recover from it, and somebody who has improved this month does not show it.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js:85-92 (useQuery + the skeleton fallback); pages/WorkCoach.js:36-57 (the working pattern)</t>
+          <t>services/operating_score.py (all queries); the caption is in pages/OperatingScore.js, team-execution section</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -23544,7 +23556,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CR-10</t>
+          <t>OP-02</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -23554,12 +23566,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Contact list when loading fails</t>
+          <t>'Do these first' on mobile</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -23574,17 +23586,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Read isError from the query and render 'Couldn't load your contacts' with a Retry that calls refetch(). Show '-' rather than 0 in the scope chips while loading or failed. Same fix pattern as OP-10 - worth one shared &lt;QueryError&gt; component.</t>
+          <t>On mobile the band should flow with the page rather than being pinned, so the score, the actions and the team list scroll as one column. If it must stay pinned, it needs to collapse to a handle the user can pull up.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>The loading skeleton stays forever. On desktop the chips read 'Buyers 0' and 'Suppliers 0' above six blank placeholder cards, so an owner with a flaky connection sees what looks like a CRM with no customers, still loading. On mobile it is the same skeleton with nothing else. No toast, no message, no retry. The same fault as OP-10 on Ops.</t>
+          <t>It is 90 per cent hidden. 'Do these first' occupies y=425 to 710, and a fixed black 'Team execution' band is pinned from y=454 to the bottom of the screen -- 374px, 46 per cent of the viewport -- covering 256 of its 285px. Scrolling does not help: the document itself does not scroll (scrollHeight equals clientHeight), and the element that does scroll is the dark band, not the page. So the three actions the page exists to recommend are permanently reduced to one visible line.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:524-527 (contacts useQuery), scope-count chips :819-835</t>
+          <t>pages/OperatingScore.js (kr-dark-band team-execution section)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -23597,7 +23609,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FN-01</t>
+          <t>OP-03</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -23607,12 +23619,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Every money figure</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -23627,17 +23639,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
+          <t>Score each leg as a bounded rate rather than a penalty subtracted from a constant, so the number always has somewhere to move. Where a leg really is at the floor, say 'below floor' rather than printing a 0 that looks like an empty metric. See ASK-19 for the wider redesign.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
+          <t>Two of the four legs are pinned at the floor and carry no information. Execution reads 0 and Responsiveness reads 0. Responsiveness actually computes to -296 before clamping (100 - 16 complaints x 12 - 68 overdue x 3), so it would take closing 8 complaints AND clearing 33 overdue tasks before the number moves off zero by a single point. The page's own advice is 'Close 16 open complaints' -- doing all of that would leave the score exactly where it is. The owner gets no gradient at precisely the moment they most need one.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
+          <t>services/operating_score.py:_score_execution and the responsiveness expression in _company_operating_view</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -23650,7 +23662,7 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FN-02</t>
+          <t>OP-10</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -23660,12 +23672,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero (mobile)</t>
+          <t>Ops page when the request fails</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -23680,17 +23692,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
+          <t>Read isError and error from the query and render a message: 403 -&gt; 'Only the owner can view another person's operating page', 404 -&gt; 'This person is no longer on the team', otherwise 'Couldn't load'. Each with a link to /operating-score. WorkCoach.js:36-57 is the pattern to copy. Also set retry: false for 4xx so the error shows at once.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
+          <t>The loading skeleton stays on screen forever, with aria-busy=true and no text at all. The API answered in milliseconds - 404 'Team member not found' for the owner, 403 for the three other roles - but the page never shows it. The user cannot tell a slow page from a broken link or a refused one, and there is no way back except the browser. Any stale shared link (a person who has left, a link forwarded to a teammate) lands here.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
+          <t>pages/OperatingScore.js:85-92 (useQuery + the skeleton fallback); pages/WorkCoach.js:36-57 (the working pattern)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -23703,7 +23715,7 @@
     <row r="39" ht="82" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FN-03</t>
+          <t>CR-10</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -23713,12 +23725,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Revenue and Net profit trend badges (mobile)</t>
+          <t>Contact list when loading fails</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -23733,17 +23745,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
+          <t>Read isError from the query and render 'Couldn't load your contacts' with a Retry that calls refetch(). Show '-' rather than 0 in the scope chips while loading or failed. Same fix pattern as OP-10 - worth one shared &lt;QueryError&gt; component.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
+          <t>The loading skeleton stays forever. On desktop the chips read 'Buyers 0' and 'Suppliers 0' above six blank placeholder cards, so an owner with a flaky connection sees what looks like a CRM with no customers, still loading. On mobile it is the same skeleton with nothing else. No toast, no message, no retry. The same fault as OP-10 on Ops.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
+          <t>pages/CRM.js:524-527 (contacts useQuery), scope-count chips :819-835</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -23756,7 +23768,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FN-06</t>
+          <t>FN-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -23771,7 +23783,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Delete on expenses, invoices and payments</t>
+          <t>Every money figure</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -23786,17 +23798,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Put a confirm step in del() and delRevenue(): an AlertDialog naming the record and amount ('Delete invoice SBT/25-26/0431 for Rs 2,85,000?'). Alternatively delete optimistically with an Undo toast and commit after a few seconds. Either way, one tap must not be final.</t>
+          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>One tap sends the DELETE straight away. No confirmation dialog, no 'are you sure', no undo toast - for all three record types, both viewports, both roles. The trash icon is a 36px target at the end of each row, so a stray tap while scrolling a phone ledger deletes a real invoice or payment and silently changes Revenue, Received and Net profit. (The harness blocked every DELETE, so nothing was removed.)</t>
+          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1541-1549 (del, delRevenue); :886 and :912 (revenue invoice/payment trash); :1264 (expense trash)</t>
+          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -23809,7 +23821,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FN-07</t>
+          <t>FN-02</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -23824,7 +23836,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Finance for Sales and Production</t>
+          <t>Net profit hero (mobile)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -23839,17 +23851,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Decide what data_input-only users should get. If it is capture only, show them the capture bar and Inbox with a line such as 'You can upload bills here; totals are visible to Finance and the Owner', and hide the money tabs. If they should not be here at all, drop data_input from the route and nav perms. In both cases handle 403 in the page (see FN-09).</t>
+          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Both roles see Finance in the nav and the Money dock and can open it - then every ledger request is refused (6 x 403). The Overview sits on 'Loading...' forever. Revenue, Expenses, Assets and Inventory each show their empty state ('No expenses yet...'), telling the user the company has no money records rather than that they are not allowed to see them. Only the capture bar works. So the page misinforms rather than refuses.</t>
+          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>App.js:237 (route perms); components/Layout.js:79 (nav perms); routers/ledger.py:619-625 (require_ledger); pages/Ledger.js:1522-1527 (queries without isError), :1641-1642 (Loading...)</t>
+          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -23862,7 +23874,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FN-08</t>
+          <t>FN-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -23877,7 +23889,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Adding records on a phone</t>
+          <t>Revenue and Net profit trend badges (mobile)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -23892,17 +23904,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Render the per-tab Add button on mobile too (drop hidden lg:block, or add a mobile placement), and have the tile open AddExpenseDialog directly through state rather than clicking a DOM node by testid.</t>
+          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>There is no way to add a record manually on a phone. The four Add buttons (Add income / expense / asset / inventory) are rendered but hidden below lg. The 'Add expense' tile in 'Simplify your finances' does nothing on any tab: it looks for an element that does not exist. Upload and scan still work, so a cash expense with no bill cannot be recorded from the phone at all.</t>
+          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1422-1429 (tile + querySelector), :1630 ('hidden lg:block' addBtn), :1551-1557 (addBtn per tab)</t>
+          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -23915,7 +23927,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DD-01</t>
+          <t>FN-06</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -23925,12 +23937,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>/decisions/:id - missing or not yours</t>
+          <t>Delete on expenses, invoices and payments</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -23945,17 +23957,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
+          <t>Put a confirm step in del() and delRevenue(): an AlertDialog naming the record and amount ('Delete invoice SBT/25-26/0431 for Rs 2,85,000?'). Alternatively delete optimistically with an Undo toast and commit after a few seconds. Either way, one tap must not be final.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
+          <t>One tap sends the DELETE straight away. No confirmation dialog, no 'are you sure', no undo toast - for all three record types, both viewports, both roles. The trash icon is a 36px target at the end of each row, so a stray tap while scrolling a phone ledger deletes a real invoice or payment and silently changes Revenue, Received and Net profit. (The harness blocked every DELETE, so nothing was removed.)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
+          <t>pages/Ledger.js:1541-1549 (del, delRevenue); :886 and :912 (revenue invoice/payment trash); :1264 (expense trash)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -23968,7 +23980,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DD-02</t>
+          <t>FN-07</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -23978,12 +23990,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Desk board when loading fails</t>
+          <t>Finance for Sales and Production</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -23998,17 +24010,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
+          <t>Decide what data_input-only users should get. If it is capture only, show them the capture bar and Inbox with a line such as 'You can upload bills here; totals are visible to Finance and the Owner', and hide the money tabs. If they should not be here at all, drop data_input from the route and nav perms. In both cases handle 403 in the page (see FN-09).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
+          <t>Both roles see Finance in the nav and the Money dock and can open it - then every ledger request is refused (6 x 403). The Overview sits on 'Loading...' forever. Revenue, Expenses, Assets and Inventory each show their empty state ('No expenses yet...'), telling the user the company has no money records rather than that they are not allowed to see them. Only the capture bar works. So the page misinforms rather than refuses.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
+          <t>App.js:237 (route perms); components/Layout.js:79 (nav perms); routers/ledger.py:619-625 (require_ledger); pages/Ledger.js:1522-1527 (queries without isError), :1641-1642 (Loading...)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -24021,7 +24033,7 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>FN-08</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -24031,12 +24043,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Adding records on a phone</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -24044,24 +24056,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Render the per-tab Add button on mobile too (drop hidden lg:block, or add a mobile placement), and have the tile open AddExpenseDialog directly through state rather than clicking a DOM node by testid.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>There is no way to add a record manually on a phone. The four Add buttons (Add income / expense / asset / inventory) are rendered but hidden below lg. The 'Add expense' tile in 'Simplify your finances' does nothing on any tab: it looks for an element that does not exist. Upload and scan still work, so a cash expense with no bill cannot be recorded from the phone at all.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/Ledger.js:1422-1429 (tile + querySelector), :1630 ('hidden lg:block' addBtn), :1551-1557 (addBtn per tab)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -24074,7 +24086,7 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>DD-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -24084,12 +24096,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>/decisions/:id - missing or not yours</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -24097,24 +24109,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -24127,7 +24139,7 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>DD-02</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -24137,12 +24149,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Desk board when loading fails</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -24150,24 +24162,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -24180,7 +24192,7 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -24190,12 +24202,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -24210,17 +24222,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -24233,7 +24245,7 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MW-17</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -24243,12 +24255,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - two close buttons, invisible focus</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -24263,17 +24275,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -24286,7 +24298,7 @@
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MW-18</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -24296,12 +24308,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Application shell at wide widths</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -24316,17 +24328,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:634 (app-shell className)</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -24339,7 +24351,7 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -24349,12 +24361,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -24369,17 +24381,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -24392,7 +24404,7 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>MW-17</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -24402,12 +24414,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Task drawer - two close buttons, invisible focus</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -24422,17 +24434,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -24445,7 +24457,7 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>MW-18</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -24455,12 +24467,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Application shell at wide widths</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -24475,17 +24487,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>components/Layout.js:634 (app-shell className)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -24498,7 +24510,7 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -24508,12 +24520,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -24528,17 +24540,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -24551,7 +24563,7 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -24561,12 +24573,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -24581,17 +24593,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -24604,7 +24616,7 @@
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -24614,12 +24626,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -24634,17 +24646,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_sales</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -24657,7 +24669,7 @@
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -24667,12 +24679,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -24687,17 +24699,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -24710,7 +24722,7 @@
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -24720,12 +24732,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -24740,17 +24752,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_company_operating_view</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -24763,7 +24775,7 @@
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>OP-09</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -24778,7 +24790,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>'View all' links and the formula panel (mobile)</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -24793,17 +24805,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -24816,7 +24828,7 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>OP-11</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -24831,7 +24843,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Personal (self) view - bottom band (mobile)</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -24846,17 +24858,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -24869,7 +24881,7 @@
     <row r="61" ht="82" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>OP-12</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -24884,7 +24896,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - entry point</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -24899,17 +24911,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -24922,7 +24934,7 @@
     <row r="62" ht="82" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CR-11</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -24932,12 +24944,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Contact profile when loading fails</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -24952,17 +24964,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -24975,7 +24987,7 @@
     <row r="63" ht="82" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>CR-12</t>
+          <t>OP-11</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -24985,12 +24997,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>GET /api/crm/outstanding</t>
+          <t>Personal (self) view - bottom band (mobile)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -25005,17 +25017,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
+          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
+          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
+          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -25028,7 +25040,7 @@
     <row r="64" ht="82" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>OP-12</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -25038,12 +25050,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>AI Work Coach - entry point</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -25058,17 +25070,17 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -25081,7 +25093,7 @@
     <row r="65" ht="82" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>CR-11</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -25091,12 +25103,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>Contact profile when loading fails</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -25111,17 +25123,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -25134,7 +25146,7 @@
     <row r="66" ht="82" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FN-09</t>
+          <t>CR-12</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -25144,12 +25156,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Finance when a request fails</t>
+          <t>GET /api/crm/outstanding</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -25164,17 +25176,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
+          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
+          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
+          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -25187,7 +25199,7 @@
     <row r="67" ht="82" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MW-22</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -25197,12 +25209,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Task card - bulk-select checkbox (mobile)</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -25217,17 +25229,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -25240,7 +25252,7 @@
     <row r="68" ht="82" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GL-01</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -25250,12 +25262,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Desktop header - notification bell</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -25270,17 +25282,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -25293,7 +25305,7 @@
     <row r="69" ht="82" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GL-02</t>
+          <t>FN-09</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -25303,12 +25315,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Mobile More panel - non-owners</t>
+          <t>Finance when a request fails</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -25323,17 +25335,17 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
+          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
+          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
+          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -25346,7 +25358,7 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>DD-03</t>
+          <t>MW-22</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -25356,12 +25368,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Money tiles for Sales / Production</t>
+          <t>Task card - bulk-select checkbox (mobile)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -25376,17 +25388,17 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
+          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
+          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
+          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -25399,7 +25411,7 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>CL-01</t>
+          <t>GL-01</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -25414,7 +25426,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Notifications, People, Journal, Calendar when loading fails</t>
+          <t>Desktop header - notification bell</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -25429,17 +25441,17 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
+          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
+          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
+          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -25452,7 +25464,7 @@
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>CL-02</t>
+          <t>GL-02</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -25462,12 +25474,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Calendar events</t>
+          <t>Mobile More panel - non-owners</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -25482,17 +25494,17 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
+          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
+          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>pages/Calendar.js:233 (cal-event)</t>
+          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -25505,7 +25517,7 @@
     <row r="73" ht="82" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>DD-03</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -25515,12 +25527,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Money tiles for Sales / Production</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -25528,24 +25540,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -25558,7 +25570,7 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MW-19</t>
+          <t>CL-01</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -25568,12 +25580,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Department filter dropdown</t>
+          <t>Notifications, People, Journal, Calendar when loading fails</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -25581,24 +25593,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
+          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
+          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
+          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -25611,7 +25623,7 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>CL-02</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -25621,12 +25633,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Calendar events</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -25634,24 +25646,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>pages/Calendar.js:233 (cal-event)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -25664,7 +25676,7 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TM-07</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -25674,12 +25686,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog - closing</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -25694,17 +25706,17 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -25717,7 +25729,7 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TM-08</t>
+          <t>MW-19</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -25727,12 +25739,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Default close button on every dialog</t>
+          <t>Department filter dropdown</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -25747,17 +25759,17 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
+          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
+          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx:37-41</t>
+          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -25770,7 +25782,7 @@
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -25780,12 +25792,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -25800,17 +25812,17 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -25823,7 +25835,7 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -25833,12 +25845,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -25853,17 +25865,17 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -25876,7 +25888,7 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -25886,12 +25898,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -25906,17 +25918,17 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -25929,7 +25941,7 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -25939,12 +25951,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -25959,17 +25971,17 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -25982,7 +25994,7 @@
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>OP-13</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -25992,12 +26004,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' and 'See all' links</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -26012,17 +26024,17 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -26035,7 +26047,7 @@
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>OP-14</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -26050,7 +26062,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - error page</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -26065,17 +26077,17 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>pages/WorkCoach.js:36-57</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -26088,7 +26100,7 @@
     <row r="84" ht="82" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>CR-09</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -26098,12 +26110,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - Score with AI</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -26118,17 +26130,17 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -26141,7 +26153,7 @@
     <row r="85" ht="82" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>CR-13</t>
+          <t>OP-13</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -26151,12 +26163,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
+          <t>'Back to company' and 'See all' links</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -26171,17 +26183,17 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
+          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
+          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
+          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -26194,7 +26206,7 @@
     <row r="86" ht="82" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>CR-14</t>
+          <t>OP-14</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -26204,12 +26216,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - 'Back to CRM' (desktop)</t>
+          <t>AI Work Coach - error page</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -26224,17 +26236,17 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>py-1 or min-h-6 on the back link.</t>
+          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
+          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:205 (profile-back)</t>
+          <t>pages/WorkCoach.js:36-57</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -26247,7 +26259,7 @@
     <row r="87" ht="82" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FN-10</t>
+          <t>CR-09</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -26257,12 +26269,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Mobile capture card - 'Export' tile</t>
+          <t>Contact profile (mobile) - Score with AI</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -26277,17 +26289,17 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
+          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
+          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1430-1437</t>
+          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -26300,7 +26312,7 @@
     <row r="88" ht="82" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FN-11</t>
+          <t>CR-13</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -26310,12 +26322,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Mobile overview - 'View all 3+ action items'</t>
+          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -26330,17 +26342,17 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>py-1 on the link.</t>
+          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
+          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
+          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -26353,7 +26365,7 @@
     <row r="89" ht="82" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>CR-14</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -26363,12 +26375,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Contact profile - 'Back to CRM' (desktop)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -26383,17 +26395,17 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>py-1 or min-h-6 on the back link.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/ContactProfile.js:205 (profile-back)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -26406,7 +26418,7 @@
     <row r="90" ht="82" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GL-03</t>
+          <t>FN-10</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -26416,12 +26428,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>/login while signed in</t>
+          <t>Mobile capture card - 'Export' tile</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -26436,17 +26448,17 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
+          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
+          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js (component top)</t>
+          <t>pages/Ledger.js:1430-1437</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -26459,7 +26471,7 @@
     <row r="91" ht="82" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>DD-04</t>
+          <t>FN-11</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -26469,12 +26481,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Company / You switch (mobile)</t>
+          <t>Mobile overview - 'View all 3+ action items'</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -26489,17 +26501,17 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Show the joined pill pair above the score below lg.</t>
+          <t>py-1 on the link.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
+          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
+          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -26512,7 +26524,7 @@
     <row r="92" ht="82" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>DD-05</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -26522,12 +26534,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Decision review - note mic</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -26542,17 +26554,17 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:421-445</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -26565,7 +26577,7 @@
     <row r="93" ht="82" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>CL-03</t>
+          <t>GL-03</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -26575,12 +26587,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Mark all read</t>
+          <t>/login while signed in</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -26595,17 +26607,17 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>toast.error('Couldn't mark notifications read') in onError.</t>
+          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
+          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:17-21</t>
+          <t>pages/Login.js (component top)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -26618,7 +26630,7 @@
     <row r="94" ht="82" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>CL-04</t>
+          <t>DD-04</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -26628,12 +26640,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Operations tab - add links</t>
+          <t>Company / You switch (mobile)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -26648,17 +26660,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>py-1 / min-h-6 on both.</t>
+          <t>Show the joined pill pair above the score below lg.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
+          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
+          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -26671,7 +26683,7 @@
     <row r="95" ht="82" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AU-01</t>
+          <t>DD-05</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -26681,12 +26693,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Login, sign-up and admin fields</t>
+          <t>Decision review - note mic</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -26701,17 +26713,17 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
+          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
+          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
+          <t>components/DecisionDialog.js:421-445</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -26724,7 +26736,7 @@
     <row r="96" ht="82" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>AU-02</t>
+          <t>CL-03</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -26734,12 +26746,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Mobile OTP - phone number</t>
+          <t>Mark all read</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -26754,17 +26766,17 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+          <t>toast.error('Couldn't mark notifications read') in onError.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:179-190, :317</t>
+          <t>pages/Notifications.js:17-21</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -26777,7 +26789,7 @@
     <row r="97" ht="82" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AU-03</t>
+          <t>CL-04</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -26787,12 +26799,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Login - header links (desktop)</t>
+          <t>Operations tab - add links</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -26807,17 +26819,17 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>py-1 on both links.</t>
+          <t>py-1 / min-h-6 on both.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
+          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:241-246</t>
+          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -26830,7 +26842,7 @@
     <row r="98" ht="82" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>AU-01</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -26840,12 +26852,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Sign-in</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Login, sign-up and admin fields</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -26853,24 +26865,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -26883,7 +26895,7 @@
     <row r="99" ht="82" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>AU-02</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -26893,12 +26905,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Sign-in</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Mobile OTP - phone number</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -26906,24 +26918,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/Login.js:179-190, :317</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -26936,7 +26948,7 @@
     <row r="100" ht="82" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>AU-03</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -26946,12 +26958,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Sign-in</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Login - header links (desktop)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -26959,24 +26971,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>py-1 on both links.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Login.js:241-246</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -26989,7 +27001,7 @@
     <row r="101" ht="82" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -26999,12 +27011,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -27019,17 +27031,17 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
@@ -27042,7 +27054,7 @@
     <row r="102" ht="82" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -27052,12 +27064,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -27072,17 +27084,17 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -27095,7 +27107,7 @@
     <row r="103" ht="82" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -27105,12 +27117,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -27125,17 +27137,17 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
@@ -27148,58 +27160,217 @@
     <row r="104" ht="82" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="82" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="82" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="82" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
+      <c r="F107" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="4" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K104"/>
+  <autoFilter ref="A1:K107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27210,7 +27381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27277,481 +27448,493 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr"/>
-      <c r="B8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="13" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Still happening. Later commits label ASK-18 (Workflows well), ASK-19 (card summary), ASK-20 (My Work scroll) and ASK-21 (New Task dialog) from the other list. In this workbook ASK-18 is the CRM In-progress list, ASK-19 the operating score KPIs, and ASK-20 / ASK-21 / ASK-22 are the three root causes from the full audit (load errors, permission map, phone parity). Match commits to this sheet by content, not by number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr"/>
+      <c r="B9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Leave approvals: who approves, and is the Settings screen needed?</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="B10" s="14" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Raised 2026-09-12 by Yogesh - Owner. Status: DEFERRED, Yogesh deciding. Relates to ASK-8. Nothing is to be built from this note until that call is made.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr"/>
-      <c r="B11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="17" t="inlineStr"/>
-      <c r="B12" s="18" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr"/>
+      <c r="B12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>THE QUESTION</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="15" t="inlineStr"/>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="15" t="inlineStr"/>
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Leave approval is mostly done by either the owner or a manager. The approver is already chosen when a team member is added. So does the 'Leave Approvers by Department' settings screen need to exist at all?</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr"/>
-      <c r="B14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="17" t="inlineStr"/>
-      <c r="B15" s="18" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr"/>
+      <c r="B15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="17" t="inlineStr"/>
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>HOW APPROVAL IS DECIDED TODAY</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="15" t="inlineStr"/>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="15" t="inlineStr"/>
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>When someone requests leave the system asks three questions IN ORDER and stops at the first that answers. The code is services/leave.py, _resolve_leave_approver.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Does this person have a Reporting Manager? If yes, that manager approves. The Reporting Manager is chosen in Team when the member is added or edited (pages/Team.js:144, the member-manager-select dropdown; stored as reporting_manager_id).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Does this person have a Reporting Manager? If yes, that manager approves. The Reporting Manager is chosen in Team when the member is added or edited (pages/Team.js:144, the member-manager-select dropdown; stored as reporting_manager_id).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Otherwise: is there a department rule for their role? If yes, that person approves. THIS IS THE SETTINGS SCREEN under discussion - the gear in the Leave section, which opens 'Leave Approvers by Department' with one dropdown per department and a Save button.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Otherwise the Owner approves.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr"/>
-      <c r="B20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="17" t="inlineStr"/>
-      <c r="B21" s="18" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr"/>
+      <c r="B21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="17" t="inlineStr"/>
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>WHAT THE LIVE DATA SHOWS</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr"/>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr"/>
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Measured against the dev workspace on 2026-09-12, not assumed:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Members</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>12 team members in the workspace.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Tier 1 used</t>
+          <t>Members</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>1 member has a Reporting Manager set (sai, finance).</t>
+          <t>12 team members in the workspace.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Tier 2 used</t>
+          <t>Tier 1 used</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>0. The tenant leave_approvers mapping is EMPTY - every department reads 'Owner (default)'.</t>
+          <t>1 member has a Reporting Manager set (sai, finance).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Tier 3 used</t>
+          <t>Tier 2 used</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>11 of 12 members fall through to the Owner, Rajesh Sharma.</t>
+          <t>0. The tenant leave_approvers mapping is EMPTY - every department reads 'Owner (default)'.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
+          <t>Tier 3 used</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>11 of 12 members fall through to the Owner, Rajesh Sharma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>The Settings screen currently decides leave for NOBODY. It configures a tier that no request reaches.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr"/>
-      <c r="B28" s="16" t="inlineStr"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="17" t="inlineStr"/>
-      <c r="B29" s="18" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr"/>
+      <c r="B29" s="16" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="17" t="inlineStr"/>
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>WHAT THE THREE PIECES ARE</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="15" t="inlineStr"/>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="15" t="inlineStr"/>
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>They are three layers of one feature. Removing one without the others leaves either a screen that cannot save or an endpoint nothing calls.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>The gear</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>The small round icon beside the My Leave / Approvals tabs. It is the only way into the screen. pages/Leave.js:500-510.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>The panel</t>
+          <t>The gear</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>'Leave Approvers by Department' - a dropdown per department plus a Save approvers button. pages/Leave.js:387-417.</t>
+          <t>The small round icon beside the My Leave / Approvals tabs. It is the only way into the screen. pages/Leave.js:500-510.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
+          <t>The panel</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>'Leave Approvers by Department' - a dropdown per department plus a Save approvers button. pages/Leave.js:387-417.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
           <t>The endpoint</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>PATCH /tenant/leave-approvers, which writes the leave_approvers field on the tenant record. routers/calendar.py:24.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr"/>
-      <c r="B34" s="16" t="inlineStr"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="17" t="inlineStr"/>
-      <c r="B35" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr"/>
+      <c r="B35" s="16" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="17" t="inlineStr"/>
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>OPTION A - DELETE TIER 2  (the current recommendation)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>What changes</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Remove the gear, the panel and the endpoint. Approval becomes: reporting manager, else owner.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Effect today</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>NONE. Every one of the 12 members resolves to exactly the same approver before and after, because nothing uses tier 2.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="45" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Argument for</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>The approver is already chosen once, in Team, when the person is added. A second screen expressing the same decision in different words - and silently losing to the first one - mostly creates the chance for the two to disagree with the org chart.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr"/>
-      <c r="B39" s="16" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="17" t="inlineStr"/>
-      <c r="B40" s="18" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr"/>
+      <c r="B40" s="16" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="17" t="inlineStr"/>
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>OPTION B - KEEP TIER 2</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>What it buys</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>One place to say 'all Sales leave goes to Priya' without making Priya anyone's reporting manager.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Cost of A</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>To get that same outcome after deleting, Priya would have to be set as the reporting manager of each Sales person individually, in Team.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
+          <t>Cost of A</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>To get that same outcome after deleting, Priya would have to be set as the reporting manager of each Sales person individually, in Team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
           <t>If kept</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>Then the fix is not to move it into Settings but to make it visible - today it is hidden behind an unlabelled gear inside a work surface, which is why it has stayed empty.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr"/>
-      <c r="B44" s="16" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="17" t="inlineStr"/>
-      <c r="B45" s="18" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr"/>
+      <c r="B45" s="16" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="17" t="inlineStr"/>
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>THE ONE QUESTION THAT DECIDES IT</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr"/>
-      <c r="B46" s="16" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr"/>
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>Is 'who approves your leave' always the same person as 'who you report to'?</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>They are always the same -&gt; Option A. Tier 2 is pure duplication.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>They can differ - for example a department lead signs off leave while people report to a project manager -&gt; Option B, and the work is to surface the screen properly rather than hide it.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>They can differ - for example a department lead signs off leave while people report to a project manager -&gt; Option B, and the work is to surface the screen properly rather than hide it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>For an SME the answer is usually yes, which is why A is the standing recommendation - but this is a business call, not a technical one, which is why it is parked rather than filed as a defect.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr"/>
-      <c r="B50" s="16" t="inlineStr"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="17" t="inlineStr"/>
-      <c r="B51" s="18" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr"/>
+      <c r="B51" s="16" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="17" t="inlineStr"/>
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>IF OPTION A IS CHOSEN, THE WORK IS</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>Delete the gear and the settings tab from pages/Leave.js (:500-510).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>Delete the LeaveApproverConfig block from pages/Leave.js (:387-417).</t>
+          <t>Delete the gear and the settings tab from pages/Leave.js (:500-510).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Delete the LeaveApproverConfig block from pages/Leave.js (:387-417).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>Delete PATCH /tenant/leave-approvers from routers/calendar.py (:24) and the LeaveApproverMapInput model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>Drop the tier-2 lookup from _resolve_leave_approver in services/leave.py, leaving reporting manager then owner.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>Leave the leave_approvers field on existing tenant records alone, or clear it in the migration - it is empty in practice either way.</t>
+          <t>Drop the tier-2 lookup from _resolve_leave_approver in services/leave.py, leaving reporting manager then owner.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>Make sure Team makes the consequence visible: the Reporting Manager dropdown should say that this person also approves their leave, since after this change that is the only place the decision is made.</t>
+          <t>Leave the leave_approvers field on existing tenant records alone, or clear it in the migration - it is empty in practice either way.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Make sure Team makes the consequence visible: the Reporting Manager dropdown should say that this person also approves their leave, since after this change that is the only place the decision is made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>This depends on ASK-6. If Leave moves into Team first, the gear disappears with it and steps 1 and 2 become part of that move rather than separate work.</t>
         </is>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$283</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6427,22 +6427,22 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MW-22</t>
+          <t>DX-01</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Task card - bulk-select checkbox (mobile)</t>
+          <t>Ask Dex - money questions</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6450,9 +6450,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -6462,42 +6462,42 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Accessibility / mis-tap</t>
+          <t>Wrong answer (live AI)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Measured the bulk-select checkbox on a 390px phone after the card redesign, and hit-tested taps 10px to its left, above and right.</t>
+          <t>LIVE run (founder-approved): asked Dex 'How much do customers owe us in total, and who owes the most?' as the owner, and compared with the ledger API. Read the saved query plan (brain_query_cache) to find why.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>The checkbox has at least a 24px tap area (it had 44x114 through its padded wrapper when N-01 was recorded), and a near-miss does not trigger something else.</t>
+          <t>Rs 7,49,000 outstanding, Krishna Garments owing the most (Rs 4,00,000).</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
+          <t>Dex answered, in bold, 'zero invoices, zero billed amount, and zero outstanding balance - the receivables table is empty', with three KPI tiles reading Invoices 0 / Billed Rs 0 / Outstanding Rs 0, suggested the data 'hasn't been synced', and cited 8 unrelated sources (test tasks, a dispatch, resolved complaints). The ledger holds Rs 26,85,000 billed and Rs 7,49,000 outstanding. An owner asking the most basic money question is told, confidently, that nobody owes them anything.</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Full control sweep at 390x844: 25 controls under 24px, the bulk-select-* checkboxes at 16x22. Probe: own 16x16, label 16x22; taps at -10px left / top / right hit the card (false, false, false for the checkbox).</t>
+          <t>Plan: primary_entity invoices, status unpaid, group_by contact, date_preset all - correct - but keywords ['outstanding','owe','customers','receivable']. 'outstanding' and 'customers' are stop-words; 'owe' and 'receivable' are not, so retrieval ran {number|contact_name ~ /owe|receivable/i} and matched 0 invoices. 17.0s. Screenshot ai_live_0913/dex_receivables_desk.png.</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>98b43f4 moved the checkbox to the card's top-left corner and dropped the padded wrapper that gave it the 44x114 hit box N-01 relied on.</t>
+          <t>_retrieve turns the planner's keywords into a record filter on invoice number and customer name. The keywords are words from the QUESTION, not names of records, and the _KW_STOP list only catches some of them. Numbers are computed deterministically (good), but from an empty set, so the LLM then narrates zeros.</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
+          <t>Only apply keywords as a record filter when they look like an entity reference (a customer, vendor or invoice number that exists in the tenant); otherwise ignore them for aggregation intents. At minimum add owe/owes/owed/receivable(s)/payable(s)/dues to _KW_STOP. And when an aggregation over a finance entity returns 0 rows while the collection is non-empty, re-run without keywords rather than answer 'zero'.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
+          <t>routers/brain.py:172-187 (_KW_STOP, _rx), :294-299 (invoices retrieval), :836-843</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -6510,32 +6510,32 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GL-01</t>
+          <t>DX-02</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Desktop header - notification bell</t>
+          <t>Ask Dex - 'What needs my attention today?'</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -6545,42 +6545,42 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Broken control</t>
+          <t>Wrong answer (live AI)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Real mouse click on the desktop bell on My Work, Decision Desk, Team and Finance, tracing aria-expanded, the dropdown and document.activeElement every 25ms.</t>
+          <t>LIVE run: asked Dex its own first suggested question, 'What needs my attention today?', as the owner; then asked 'Which tasks are overdue?' and compared.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>The bell opens the notification dropdown and it stays open until dismissed.</t>
+          <t>The overdue work, decisions waiting and money at risk - the owner has 24 open and 6 overdue tasks, 53 decisions waiting and 58 items on fire.</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
+          <t>'Good news - there are no open or overdue tasks requiring your attention right now', followed by a list of things already completed. One question later, 'Which tasks are overdue?' answered 'All 34 matching tasks are overdue'. The page's headline suggestion gives the owner false reassurance.</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>/inbox: pointerdown 20ms -&gt; expanded true + dropdown at 138ms -&gt; expanded false, dropdown gone, focus BODY at 541ms. /finance: opens at 148ms and stays open. elementFromPoint at the bell centre is the bell on every page (nothing covering).</t>
+          <t>Plan: entity tasks, status todo, date_preset today, group_by priority. _compute_tasks keeps only tasks created or due TODAY with status exactly 'todo' (in_progress excluded), so overdue work from earlier days is filtered out. 24.1s. Second question plan: status overdue, no date -&gt; 34 rows.</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Likely a remount: Bellicon is declared as a component INSIDE Layout's render (const Bellicon = (...) =&gt; &lt;Popover&gt;...). Every Layout re-render creates a new component type, so React unmounts the open Popover and mounts a closed one. Pages whose data refreshes around the click (Desk polls every 30s, notifications refetch) re-render Layout in that window; Finance happened not to.</t>
+          <t>'Needs my attention today' is read literally as a date filter, and 'todo' as a status match. Decisions, overdue items and money are never considered, because the planner picks ONE primary entity.</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
+          <t>Treat 'what needs my attention' as a composite intent served from the Desk's own counters (needs_decision, on_fire, overdue, receivables) rather than a single-entity list; or map it to status overdue|in_progress|todo with no date window. Add it to the planner guardrails in _refine_plan, since it is Dex's first suggested question.</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
+          <t>routers/brain.py:127-141 (_plan), :144+ (_refine_plan), :463-478 (_compute_tasks filters); pages/Brain.js suggestions</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -6593,32 +6593,32 @@
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GL-02</t>
+          <t>FN-12</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Mobile More panel - non-owners</t>
+          <t>Ask AI about your expenses - answer</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sales / Production / Finance</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Owner / Finance</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -6628,42 +6628,42 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Navigation parity</t>
+          <t>Rendering</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Signed in as each non-owner at 390px, opened More and listed every tile; searched the Desk for any other link to Ops, Team or Settings.</t>
+          <t>LIVE run: asked 'Which supplier do we owe the most right now, and how much?' on the Expenses tab.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>A page a role can open on desktop can be reached on the phone.</t>
+          <t>A readable answer.</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
+          <t>The answer is correct - Surat Spinners, Rs 4,80,000, matching the data - but it is shown with literal markdown: '**Surat Spinners**' and '**Rs 4,80,000**', asterisks visible.</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>More tiles for all three roles: ['Workflows', 'Leave']; visible links on their Desk to /operating-score, /team, /settings: 0, 0, 0. Desktop nav pills for the same users include nav-ops and nav-team.</t>
+          <t>Screenshot ai_live_0913/finance_ai_desk.png; 7.3s. Dex renders the same model's bold correctly, so it is the Finance panel.</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>AllAppsPanel filters Ops and Settings with ownerOnly and Team with perm: 'team_manage', while the routes and the desktop nav use looser rules.</t>
+          <t>ai-answer-* renders the model text as a plain string.</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
+          <t>Render the answer through the same markdown renderer Dex uses (or strip ** server-side).</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
+          <t>pages/Ledger.js:539 (ai-answer)</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -6676,17 +6676,17 @@
     <row r="73" ht="82" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GL-03</t>
+          <t>FN-13</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>/login while signed in</t>
+          <t>Capture - extraction review</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner / Finance</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -6711,42 +6711,42 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>Data capture (live AI)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Signed in as the owner, then opened /login directly.</t>
+          <t>LIVE run: uploaded testdata/1.png, a real-format GST invoice (Sleek Bill X33, 24 Feb 2018, due 1 Mar 2018, 3 items + shipping, total Rs 27,625, supplier GSTIN 17ABGSP1111P1Z1). Left the result in review; did NOT file it.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>An already signed-in user is taken into the app.</t>
+          <t>The key fields a GST purchase bill needs, and a warning when the bill is years old.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
+          <t>Good overall, in 31.9s at 92% confidence: supplier Service TEST 123 with phone and email, number X33, amount 27,625, due 2018-03-01, booked as Inventory, and a 'Pay vendor bill' follow-up task. But the invoice DATE, the supplier GSTIN and the line items are not captured, and nothing warns that the bill fell due eight years ago - filing it would add an overdue payable dated 2018 without comment.</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Owner session, /login -&gt; stays on /login showing 'Sign in - Access your company brain', both viewports.</t>
+          <t>Review panel: Supplier / Purchase bill / Inventory / X33 / 27625 / due 2018-03-01; no date, GSTIN or item rows. Screenshot ai_live_0913/extraction_desk.png. Ingestion 79ed62dd-9114-45cb-8788-0dd5a108538d left in status review.</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Login.js does not check for an existing session before rendering.</t>
+          <t>The review schema carries party, number, amount and due date only.</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
+          <t>Carry invoice date, GSTIN (and GST amount) and line items through to review; flag bills whose date or due date is more than ~12 months old before 'File it'.</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js (component top)</t>
+          <t>pages/finance/ReviewPanel.js; services/ingestion.py (ai_extract_document)</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -6759,32 +6759,32 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DD-01</t>
+          <t>MW-22</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>/decisions/:id - missing or not yours</t>
+          <t>Task card - bulk-select checkbox (mobile)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -6794,42 +6794,42 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Dead end / misleading error</t>
+          <t>Accessibility / mis-tap</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Opened /decisions/does-not-exist as all four roles, and a real pending decision as a non-participant; tried Escape and an outside tap; checked in the browser preview.</t>
+          <t>Measured the bulk-select checkbox on a 390px phone after the card redesign, and hit-tested taps 10px to its left, above and right.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>The page says what went wrong and offers a way back.</t>
+          <t>The checkbox has at least a 24px tap area (it had 44x114 through its padded wrapper when N-01 was recorded), and a near-miss does not trigger something else.</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
+          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>All 4 roles x 1440/390: controls inside the dialog = []; Escape leaves = false; outside tap leaves = false. API 404 for the unknown id, 403 for a non-participant. Preview at 375x812 confirms.</t>
+          <t>Full control sweep at 390x844: 25 controls under 24px, the bulk-select-* checkboxes at 16x22. Probe: own 16x16, label 16x22; taps at -10px left / top / right hit the card (false, false, false for the checkbox).</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>DecisionDialog's isError branch renders only a title and a sentence - the Close button exists only in the success branch - while variant='page' prevents Escape and outside dismissal (KM-28). isError also does not look at the status code.</t>
+          <t>98b43f4 moved the checkbox to the card's top-left corner and dropped the padded wrapper that gave it the 44x114 hit box N-01 relied on.</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
+          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
+          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -6842,32 +6842,32 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DD-02</t>
+          <t>GL-01</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Desk board when loading fails</t>
+          <t>Desktop header - notification bell</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
@@ -6877,42 +6877,42 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Error handling / misleading</t>
+          <t>Broken control</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Aborted GET /api/desk?chip=* and read the Desk at 1440 and 390.</t>
+          <t>Real mouse click on the desktop bell on My Work, Decision Desk, Team and Finance, tracing aria-expanded, the dropdown and document.activeElement every 25ms.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>The Desk says it could not load.</t>
+          <t>The bell opens the notification dropdown and it stays open until dismissed.</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
+          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Board text after the abort: 'Decision desk Nothing waiting on you Needs your decision 0 On fire 0 Due today 0 Important 0'. Without the abort: 53 / 58 / 0 / 0.</t>
+          <t>/inbox: pointerdown 20ms -&gt; expanded true + dropdown at 138ms -&gt; expanded false, dropdown gone, focus BODY at 541ms. /finance: opens at 148ms and stays open. elementFromPoint at the bell centre is the bell on every page (nothing covering).</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>The four useQueries read only data; counters fall back to all-zero when no query has data, and the sections render their empty copy.</t>
+          <t>Likely a remount: Bellicon is declared as a component INSIDE Layout's render (const Bellicon = (...) =&gt; &lt;Popover&gt;...). Every Layout re-render creates a new component type, so React unmounts the open Popover and mounts a closed one. Pages whose data refreshes around the click (Desk polls every 30s, notifications refetch) re-render Layout in that window; Finance happened not to.</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
+          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
+          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -6925,27 +6925,27 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>DD-03</t>
+          <t>GL-02</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Money tiles for Sales / Production</t>
+          <t>Mobile More panel - non-owners</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sales / Production</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -6960,42 +6960,42 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Permissions / endless loading</t>
+          <t>Navigation parity</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Signed in as Sales and Production and read every KPI tile on the Desk.</t>
+          <t>Signed in as each non-owner at 390px, opened More and listed every tile; searched the Desk for any other link to Ops, Team or Settings.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Tiles a role cannot see are hidden; tiles it can see load.</t>
+          <t>A page a role can open on desktop can be reached on the phone.</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
+          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Sales desktop tiles: Delayed 20 / Complaints 16 / Score mix - / To collect (overdue) Rs 7.5 L / Net profit ... / Spend, this month .... GET /ledger/summary 403.</t>
+          <t>More tiles for all three roles: ['Workflows', 'Leave']; visible links on their Desk to /operating-score, /team, /settings: 0, 0, 0. Desktop nav pills for the same users include nav-ops and nav-team.</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>useDeskMetrics fetches the ledger summary for every role and the tiles render a loading glyph when the data never arrives; the receivables figure comes from an ungated source (see CR-12).</t>
+          <t>AllAppsPanel filters Ops and Settings with ownerOnly and Team with perm: 'team_manage', while the routes and the desktop nav use looser rules.</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
+          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
+          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -7008,27 +7008,27 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>DD-04</t>
+          <t>GL-03</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Company / You switch (mobile)</t>
+          <t>/login while signed in</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -7043,42 +7043,42 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Missing function</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>At 375-390px, listed the scope controls on the Desk.</t>
+          <t>Signed in as the owner, then opened /login directly.</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>The owner can switch between the company score and their own on a phone.</t>
+          <t>An already signed-in user is taken into the app.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
+          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>desk-scope-pills and desk-scope-pills-side: width 0 at 375px (preview) and 390px (script); both visible and working at 1440.</t>
+          <t>Owner session, /login -&gt; stays on /login showing 'Sign in - Access your company brain', both viewports.</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Both placements are gated to lg and no mobile placement was kept.</t>
+          <t>Login.js does not check for an existing session before rendering.</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Show the joined pill pair above the score below lg.</t>
+          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
+          <t>pages/Login.js (component top)</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DD-05</t>
+          <t>DD-01</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Decision review - note mic</t>
+          <t>/decisions/:id - missing or not yours</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
@@ -7126,42 +7126,42 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Dead control</t>
+          <t>Dead end / misleading error</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Pressed the microphone under 'Send a note' on a pending decision.</t>
+          <t>Opened /decisions/does-not-exist as all four roles, and a real pending decision as a non-participant; tried Escape and an outside tap; checked in the browser preview.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>The mic records a voice note, as its helper line promises ('Or tap the mic - speaking is faster than typing').</t>
+          <t>The page says what went wrong and offers a way back.</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
+          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Toast text on both viewports; no recording state, no permission prompt.</t>
+          <t>All 4 roles x 1440/390: controls inside the dialog = []; Escape leaves = false; outside tap leaves = false. API 404 for the unknown id, 403 for a non-participant. Preview at 375x812 confirms.</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>onClick is a placeholder toast.</t>
+          <t>DecisionDialog's isError branch renders only a title and a sentence - the Close button exists only in the success branch - while variant='page' prevents Escape and outside dismissal (KM-28). isError also does not look at the status code.</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
+          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:421-445</t>
+          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -7174,17 +7174,17 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>CL-01</t>
+          <t>DD-02</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Notifications, People, Journal, Calendar when loading fails</t>
+          <t>Desk board when loading fails</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -7197,9 +7197,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -7214,37 +7214,37 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Aborted each page's main GET (notifications, users, journal, calendar) at 1440 and 390.</t>
+          <t>Aborted GET /api/desk?chip=* and read the Desk at 1440 and 390.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Each page says it could not load.</t>
+          <t>The Desk says it could not load.</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
+          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Text after each abort, both viewports: see T-650..T-653.</t>
+          <t>Board text after the abort: 'Decision desk Nothing waiting on you Needs your decision 0 On fire 0 Due today 0 Important 0'. Without the abort: 53 / 58 / 0 / 0.</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>The pages read only data / isLoading and fall through to their empty states.</t>
+          <t>The four useQueries read only data; counters fall back to all-zero when no query has data, and the sections render their empty copy.</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
+          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
+          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -7257,17 +7257,17 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>CL-02</t>
+          <t>DD-03</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Calendar events</t>
+          <t>Money tiles for Sales / Production</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Sales / Production</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -7292,42 +7292,42 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Dead end</t>
+          <t>Permissions / endless loading</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Tapped an event in Week view (script at 1440/390 and the browser preview).</t>
+          <t>Signed in as Sales and Production and read every KPI tile on the Desk.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>An event opens what it is - the task, meeting, payment or leave it came from.</t>
+          <t>Tiles a role cannot see are hidden; tiles it can see load.</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
+          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>cal-event-*: tag DIV, no href, no role, cursor auto; URL unchanged after a tap; no dialog opened. 9 events in the week, all the same.</t>
+          <t>Sales desktop tiles: Delayed 20 / Complaints 16 / Score mix - / To collect (overdue) Rs 7.5 L / Net profit ... / Spend, this month .... GET /ledger/summary 403.</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Calendar renders events for display only.</t>
+          <t>useDeskMetrics fetches the ledger summary for every role and the tiles render a loading glyph when the data never arrives; the receivables figure comes from an ungated source (see CR-12).</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
+          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>pages/Calendar.js:233 (cal-event)</t>
+          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -7340,27 +7340,27 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>CL-03</t>
+          <t>DD-04</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Mark all read</t>
+          <t>Company / You switch (mobile)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -7375,42 +7375,42 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Silent failure</t>
+          <t>Missing function</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Pressed Mark all read with the request blocked, on a fresh page.</t>
+          <t>At 375-390px, listed the scope controls on the Desk.</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>A failed action says so.</t>
+          <t>The owner can switch between the company score and their own on a phone.</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
+          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>POST /notifications/read-all blocked -&gt; toasts [], unread dots 28 -&gt; 28.</t>
+          <t>desk-scope-pills and desk-scope-pills-side: width 0 at 375px (preview) and 390px (script); both visible and working at 1440.</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>The mutation has no onError.</t>
+          <t>Both placements are gated to lg and no mobile placement was kept.</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>toast.error('Couldn't mark notifications read') in onError.</t>
+          <t>Show the joined pill pair above the score below lg.</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:17-21</t>
+          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -7423,22 +7423,22 @@
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>CL-04</t>
+          <t>DD-05</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Operations tab - add links</t>
+          <t>Decision review - note mic</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7458,42 +7458,42 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Accessibility / tap target</t>
+          <t>Dead control</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Measured controls on Settings at 1440.</t>
+          <t>Pressed the microphone under 'Send a note' on a pending decision.</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Controls are at least 24px tall.</t>
+          <t>The mic records a voice note, as its helper line promises ('Or tap the mic - speaking is faster than typing').</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
+          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Under-24px list on /settings at 1440.</t>
+          <t>Toast text on both viewports; no recording state, no permission prompt.</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Text buttons without vertical padding.</t>
+          <t>onClick is a placeholder toast.</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>py-1 / min-h-6 on both.</t>
+          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
+          <t>components/DecisionDialog.js:421-445</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -7506,17 +7506,17 @@
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AU-01</t>
+          <t>CL-01</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Login, sign-up and admin fields</t>
+          <t>Notifications, People, Journal, Calendar when loading fails</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Signed out</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
@@ -7541,42 +7541,42 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Error handling / misleading</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Checked every input on /login, /signup and /admin for a programmatic label.</t>
+          <t>Aborted each page's main GET (notifications, users, journal, calendar) at 1440 and 390.</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Each field is named for assistive technology.</t>
+          <t>Each page says it could not load.</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
+          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Unlabelled: login-email-input, login-password-input, signup-input-company_name, admin-email-input, admin-password-input (both viewports; admin also in preview).</t>
+          <t>Text after each abort, both viewports: see T-650..T-653.</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Placeholder / visual captions instead of &lt;label htmlFor&gt;.</t>
+          <t>The pages read only data / isLoading and fall through to their empty states.</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
+          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
+          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -7589,17 +7589,17 @@
     <row r="84" ht="82" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>AU-02</t>
+          <t>CL-02</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Mobile OTP - phone number</t>
+          <t>Calendar events</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Signed out</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -7624,42 +7624,42 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Dead end</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Entered a 3-digit number on the Mobile OTP tab and pressed Send (request blocked).</t>
+          <t>Tapped an event in Week view (script at 1440/390 and the browser preview).</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>An obviously invalid number is refused before a code is requested.</t>
+          <t>An event opens what it is - the task, meeting, payment or leave it came from.</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>POST /auth/otp/request fired for '123'; error 'Something went wrong. Please try again.'</t>
+          <t>cal-event-*: tag DIV, no href, no role, cursor auto; URL unchanged after a tap; no dialog opened. 9 events in the week, all the same.</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>No client-side length/format check on otp-phone-input.</t>
+          <t>Calendar renders events for display only.</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:179-190, :317</t>
+          <t>pages/Calendar.js:233 (cal-event)</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -7672,88 +7672,420 @@
     <row r="85" ht="82" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>CL-03</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Mark all read</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Silent failure</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Pressed Mark all read with the request blocked, on a fresh page.</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>A failed action says so.</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>POST /notifications/read-all blocked -&gt; toasts [], unread dots 28 -&gt; 28.</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>The mutation has no onError.</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>toast.error('Couldn't mark notifications read') in onError.</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>pages/Notifications.js:17-21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86" ht="82" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>CL-04</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Operations tab - add links</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility / tap target</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Measured controls on Settings at 1440.</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Controls are at least 24px tall.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Under-24px list on /settings at 1440.</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>Text buttons without vertical padding.</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>py-1 / min-h-6 on both.</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" ht="82" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>AU-01</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Login, sign-up and admin fields</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Checked every input on /login, /signup and /admin for a programmatic label.</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Each field is named for assistive technology.</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Unlabelled: login-email-input, login-password-input, signup-input-company_name, admin-email-input, admin-password-input (both viewports; admin also in preview).</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>Placeholder / visual captions instead of &lt;label htmlFor&gt;.</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="82" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>AU-02</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Mobile OTP - phone number</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Entered a 3-digit number on the Mobile OTP tab and pressed Send (request blocked).</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>An obviously invalid number is refused before a code is requested.</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>POST /auth/otp/request fired for '123'; error 'Something went wrong. Please try again.'</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>No client-side length/format check on otp-phone-input.</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>pages/Login.js:179-190, :317</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="82" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
           <t>AU-03</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Sign-in</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Login - header links (desktop)</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Desktop</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Signed out</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Accessibility / tap target</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>Measured controls on /login at 1440.</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>Links are at least 24px tall.</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>Under-24px list on /login at 1440; both fine on mobile.</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="M89" s="2" t="inlineStr">
         <is>
           <t>Inline text links without padding.</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>py-1 on both links.</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>pages/Login.js:241-246</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr">
+      <c r="P89" s="2" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q85"/>
+  <autoFilter ref="A1:Q89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7764,7 +8096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J273"/>
+  <dimension ref="A1:J283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21234,53 +21566,549 @@
     <row r="273" ht="82" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
+          <t>T-680</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - receivables question</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Dex answers how much customers owe with the ledger's figure</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>AI accuracy</t>
+        </is>
+      </c>
+      <c r="H273" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>Said zero invoices / Rs 0 outstanding; ledger has Rs 7,49,000 outstanding (17.0s)</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>DX-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="82" customHeight="1">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>T-681</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - what needs my attention</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Dex surfaces the overdue work and pending decisions</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>AI accuracy</t>
+        </is>
+      </c>
+      <c r="H274" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>Said nothing open or overdue; owner has 24 open / 6 overdue (24.1s)</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>DX-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="82" customHeight="1">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>T-682</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - global search hand-off</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>A question from global search is answered on arrival</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>AI flow</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>'Which tasks are overdue?' answered on /brain?q= with a task list (17.5s)</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr"/>
+    </row>
+    <row r="276" ht="82" customHeight="1">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>T-683</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - coach refresh</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Generate coaching produces a review grounded in the stats</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>AI flow</t>
+        </is>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>TEST_member: 'AI coach updated' in 8.7s; strengths / improvements reference the 13 actionable tasks and plan use</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277" ht="82" customHeight="1">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>T-684</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - Score with AI</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>Rescore updates the relationship card sensibly</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>AI flow</t>
+        </is>
+      </c>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>E2E Test Co: 'Relationship scored by AI' in 7.8s; Relationship 12 / Risk 78, reason cites 4 open complaints and no billing - matches the record</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278" ht="82" customHeight="1">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>T-685</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - AI analysis refresh</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Refresh produces an analysis grounded in the ledger</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>AI accuracy</t>
+        </is>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>'Analysis refreshed' in 20.6s; Rs 6.6L outstanding (ledger 6,55,466), Surat Spinners Rs 4.8L unpaid 33 days (correct), duplicates flagged</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279" ht="82" customHeight="1">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>T-686</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - Ask AI</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>The answer is correct and readable</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>AI accuracy</t>
+        </is>
+      </c>
+      <c r="H279" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>Correct (Surat Spinners Rs 4,80,000, 7.3s) but literal ** markdown shown</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
+        <is>
+          <t>FN-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="82" customHeight="1">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>T-688</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - owner on a phone</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>Dex answers on mobile and the answer fits the screen</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>AI flow</t>
+        </is>
+      </c>
+      <c r="H280" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>'53 decisions pending approval across 77' - correct; 17.6s; no overflow</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281" ht="82" customHeight="1">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>T-689</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - Sales asks money questions</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Dex refuses finance answers to a role the finance API refuses</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>Receivables and profit questions both refused ('You do not have permission to access financial...'), 5.8s / 1.6s; no figures leaked</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282" ht="82" customHeight="1">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>T-687</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>LIVE - bill extraction</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>A GST bill is extracted into a reviewable record with the key fields</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>AI accuracy</t>
+        </is>
+      </c>
+      <c r="H282" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>Party, number, amount, due date, category and follow-up correct (31.9s, 92%); date, GSTIN, items missing; no stale-date warning. Left in review, not filed</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>FN-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="82" customHeight="1">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
           <t>T-676</t>
         </is>
       </c>
-      <c r="B273" s="2" t="inlineStr">
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr">
+      <c r="C283" s="2" t="inlineStr">
         <is>
           <t>Admin portal gating</t>
         </is>
       </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>Signed out / Owner</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="F283" s="2" t="inlineStr">
         <is>
           <t>Only platform admins reach the portal</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr">
+      <c r="G283" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H273" s="4" t="inlineStr">
+      <c r="H283" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I273" s="2" t="inlineStr">
+      <c r="I283" s="2" t="inlineStr">
         <is>
           <t>Signed out and tenant owner both get the admin sign-in; /admin/me 401; deep link /admin/tenants too</t>
         </is>
       </c>
-      <c r="J273" s="2" t="inlineStr"/>
+      <c r="J283" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J273"/>
+  <autoFilter ref="A1:J283"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21610,7 +22438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24086,7 +24914,7 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>DD-01</t>
+          <t>DX-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -24096,12 +24924,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>/decisions/:id - missing or not yours</t>
+          <t>Ask Dex - money questions</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -24116,17 +24944,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
+          <t>Only apply keywords as a record filter when they look like an entity reference (a customer, vendor or invoice number that exists in the tenant); otherwise ignore them for aggregation intents. At minimum add owe/owes/owed/receivable(s)/payable(s)/dues to _KW_STOP. And when an aggregation over a finance entity returns 0 rows while the collection is non-empty, re-run without keywords rather than answer 'zero'.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
+          <t>Dex answered, in bold, 'zero invoices, zero billed amount, and zero outstanding balance - the receivables table is empty', with three KPI tiles reading Invoices 0 / Billed Rs 0 / Outstanding Rs 0, suggested the data 'hasn't been synced', and cited 8 unrelated sources (test tasks, a dispatch, resolved complaints). The ledger holds Rs 26,85,000 billed and Rs 7,49,000 outstanding. An owner asking the most basic money question is told, confidently, that nobody owes them anything.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
+          <t>routers/brain.py:172-187 (_KW_STOP, _rx), :294-299 (invoices retrieval), :836-843</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -24139,7 +24967,7 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>DD-02</t>
+          <t>DX-02</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -24149,12 +24977,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Desk board when loading fails</t>
+          <t>Ask Dex - 'What needs my attention today?'</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -24169,17 +24997,17 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
+          <t>Treat 'what needs my attention' as a composite intent served from the Desk's own counters (needs_decision, on_fire, overdue, receivables) rather than a single-entity list; or map it to status overdue|in_progress|todo with no date window. Add it to the planner guardrails in _refine_plan, since it is Dex's first suggested question.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
+          <t>'Good news - there are no open or overdue tasks requiring your attention right now', followed by a list of things already completed. One question later, 'Which tasks are overdue?' answered 'All 34 matching tasks are overdue'. The page's headline suggestion gives the owner false reassurance.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
+          <t>routers/brain.py:127-141 (_plan), :144+ (_refine_plan), :463-478 (_compute_tasks filters); pages/Brain.js suggestions</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -24192,7 +25020,7 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>DD-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -24202,12 +25030,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>/decisions/:id - missing or not yours</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -24215,24 +25043,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -24245,7 +25073,7 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>DD-02</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -24255,12 +25083,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Desk board when loading fails</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -24268,24 +25096,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -24298,7 +25126,7 @@
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -24308,12 +25136,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -24328,17 +25156,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -24351,7 +25179,7 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -24361,12 +25189,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -24381,17 +25209,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -24404,7 +25232,7 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MW-17</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -24419,7 +25247,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - two close buttons, invisible focus</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -24434,17 +25262,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -24457,7 +25285,7 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MW-18</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -24467,12 +25295,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application shell at wide widths</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -24487,17 +25315,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:634 (app-shell className)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -24510,7 +25338,7 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-17</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -24520,12 +25348,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Task drawer - two close buttons, invisible focus</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -24540,17 +25368,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -24563,7 +25391,7 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>MW-18</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -24573,12 +25401,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Application shell at wide widths</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -24593,17 +25421,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>components/Layout.js:634 (app-shell className)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -24616,7 +25444,7 @@
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -24626,12 +25454,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -24646,17 +25474,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -24669,7 +25497,7 @@
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -24679,12 +25507,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -24699,17 +25527,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -24722,7 +25550,7 @@
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -24737,7 +25565,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -24752,17 +25580,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -24775,7 +25603,7 @@
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -24785,12 +25613,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -24805,17 +25633,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_sales</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -24828,7 +25656,7 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -24838,12 +25666,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -24858,17 +25686,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -24881,7 +25709,7 @@
     <row r="61" ht="82" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -24896,7 +25724,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -24911,17 +25739,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_company_operating_view</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -24934,7 +25762,7 @@
     <row r="62" ht="82" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>OP-09</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -24949,7 +25777,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>'View all' links and the formula panel (mobile)</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -24964,17 +25792,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -24987,7 +25815,7 @@
     <row r="63" ht="82" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>OP-11</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -25002,7 +25830,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Personal (self) view - bottom band (mobile)</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -25017,17 +25845,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -25040,7 +25868,7 @@
     <row r="64" ht="82" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>OP-12</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -25055,7 +25883,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - entry point</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -25070,17 +25898,17 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -25093,7 +25921,7 @@
     <row r="65" ht="82" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>CR-11</t>
+          <t>OP-11</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -25103,12 +25931,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Contact profile when loading fails</t>
+          <t>Personal (self) view - bottom band (mobile)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -25123,17 +25951,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
+          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
+          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
+          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -25146,7 +25974,7 @@
     <row r="66" ht="82" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>CR-12</t>
+          <t>OP-12</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -25156,12 +25984,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>GET /api/crm/outstanding</t>
+          <t>AI Work Coach - entry point</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -25176,17 +26004,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
+          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
+          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
+          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -25199,7 +26027,7 @@
     <row r="67" ht="82" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>CR-11</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -25209,12 +26037,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>Contact profile when loading fails</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -25229,17 +26057,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -25252,7 +26080,7 @@
     <row r="68" ht="82" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>CR-12</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -25262,12 +26090,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>GET /api/crm/outstanding</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -25282,17 +26110,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -25305,7 +26133,7 @@
     <row r="69" ht="82" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FN-09</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -25320,7 +26148,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Finance when a request fails</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -25335,17 +26163,17 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -25358,7 +26186,7 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MW-22</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -25368,12 +26196,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Task card - bulk-select checkbox (mobile)</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -25388,17 +26216,17 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -25411,7 +26239,7 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GL-01</t>
+          <t>FN-09</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -25421,12 +26249,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Desktop header - notification bell</t>
+          <t>Finance when a request fails</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -25441,17 +26269,17 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
+          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
+          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
+          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -25464,7 +26292,7 @@
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GL-02</t>
+          <t>MW-22</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -25474,12 +26302,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Mobile More panel - non-owners</t>
+          <t>Task card - bulk-select checkbox (mobile)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -25494,17 +26322,17 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
+          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
+          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
+          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -25517,7 +26345,7 @@
     <row r="73" ht="82" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>DD-03</t>
+          <t>GL-01</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -25527,12 +26355,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Money tiles for Sales / Production</t>
+          <t>Desktop header - notification bell</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -25547,17 +26375,17 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
+          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
+          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
+          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -25570,7 +26398,7 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>CL-01</t>
+          <t>GL-02</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -25585,7 +26413,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Notifications, People, Journal, Calendar when loading fails</t>
+          <t>Mobile More panel - non-owners</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -25600,17 +26428,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
+          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
+          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
+          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -25623,7 +26451,7 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>CL-02</t>
+          <t>DD-03</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -25633,12 +26461,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Calendar events</t>
+          <t>Money tiles for Sales / Production</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -25653,17 +26481,17 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
+          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
+          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>pages/Calendar.js:233 (cal-event)</t>
+          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -25676,7 +26504,7 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>CL-01</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -25686,12 +26514,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Notifications, People, Journal, Calendar when loading fails</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -25699,24 +26527,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -25729,7 +26557,7 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>MW-19</t>
+          <t>CL-02</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -25739,12 +26567,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Department filter dropdown</t>
+          <t>Calendar events</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -25752,24 +26580,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
+          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
+          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
+          <t>pages/Calendar.js:233 (cal-event)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -25782,7 +26610,7 @@
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -25792,12 +26620,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -25812,17 +26640,17 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -25835,7 +26663,7 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TM-07</t>
+          <t>MW-19</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -25845,12 +26673,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog - closing</t>
+          <t>Department filter dropdown</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -25865,17 +26693,17 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
+          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
+          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
+          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -25888,7 +26716,7 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TM-08</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -25898,12 +26726,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Default close button on every dialog</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -25918,17 +26746,17 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx:37-41</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -25941,7 +26769,7 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -25951,12 +26779,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -25971,17 +26799,17 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -25994,7 +26822,7 @@
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -26004,12 +26832,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -26024,17 +26852,17 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -26047,7 +26875,7 @@
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -26057,12 +26885,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -26077,17 +26905,17 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -26100,7 +26928,7 @@
     <row r="84" ht="82" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -26110,12 +26938,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -26130,17 +26958,17 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -26153,7 +26981,7 @@
     <row r="85" ht="82" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>OP-13</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -26168,7 +26996,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' and 'See all' links</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -26183,17 +27011,17 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -26206,7 +27034,7 @@
     <row r="86" ht="82" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>OP-14</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -26221,7 +27049,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - error page</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -26236,17 +27064,17 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>pages/WorkCoach.js:36-57</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -26259,7 +27087,7 @@
     <row r="87" ht="82" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>CR-09</t>
+          <t>OP-13</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -26269,12 +27097,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - Score with AI</t>
+          <t>'Back to company' and 'See all' links</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -26289,17 +27117,17 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
+          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
+          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
+          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -26312,7 +27140,7 @@
     <row r="88" ht="82" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>CR-13</t>
+          <t>OP-14</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -26322,12 +27150,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
+          <t>AI Work Coach - error page</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -26342,17 +27170,17 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
+          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
+          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
+          <t>pages/WorkCoach.js:36-57</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -26365,7 +27193,7 @@
     <row r="89" ht="82" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>CR-14</t>
+          <t>CR-09</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -26380,7 +27208,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - 'Back to CRM' (desktop)</t>
+          <t>Contact profile (mobile) - Score with AI</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -26395,17 +27223,17 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>py-1 or min-h-6 on the back link.</t>
+          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
+          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:205 (profile-back)</t>
+          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -26418,7 +27246,7 @@
     <row r="90" ht="82" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>FN-10</t>
+          <t>CR-13</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -26428,12 +27256,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Mobile capture card - 'Export' tile</t>
+          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -26448,17 +27276,17 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
+          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
+          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1430-1437</t>
+          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -26471,7 +27299,7 @@
     <row r="91" ht="82" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>FN-11</t>
+          <t>CR-14</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -26481,12 +27309,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Mobile overview - 'View all 3+ action items'</t>
+          <t>Contact profile - 'Back to CRM' (desktop)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -26501,17 +27329,17 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>py-1 on the link.</t>
+          <t>py-1 or min-h-6 on the back link.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
+          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
+          <t>pages/ContactProfile.js:205 (profile-back)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -26524,7 +27352,7 @@
     <row r="92" ht="82" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>FN-10</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -26534,12 +27362,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Mobile capture card - 'Export' tile</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -26554,17 +27382,17 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Ledger.js:1430-1437</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -26577,7 +27405,7 @@
     <row r="93" ht="82" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GL-03</t>
+          <t>FN-11</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -26587,12 +27415,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>/login while signed in</t>
+          <t>Mobile overview - 'View all 3+ action items'</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -26607,17 +27435,17 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
+          <t>py-1 on the link.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
+          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js (component top)</t>
+          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -26630,7 +27458,7 @@
     <row r="94" ht="82" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>DD-04</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -26640,12 +27468,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Company / You switch (mobile)</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -26660,17 +27488,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Show the joined pill pair above the score below lg.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -26683,7 +27511,7 @@
     <row r="95" ht="82" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>DD-05</t>
+          <t>FN-12</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -26693,12 +27521,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Decision review - note mic</t>
+          <t>Ask AI about your expenses - answer</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -26713,17 +27541,17 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
+          <t>Render the answer through the same markdown renderer Dex uses (or strip ** server-side).</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
+          <t>The answer is correct - Surat Spinners, Rs 4,80,000, matching the data - but it is shown with literal markdown: '**Surat Spinners**' and '**Rs 4,80,000**', asterisks visible.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:421-445</t>
+          <t>pages/Ledger.js:539 (ai-answer)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -26736,7 +27564,7 @@
     <row r="96" ht="82" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>CL-03</t>
+          <t>FN-13</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -26746,12 +27574,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Mark all read</t>
+          <t>Capture - extraction review</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -26766,17 +27594,17 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>toast.error('Couldn't mark notifications read') in onError.</t>
+          <t>Carry invoice date, GSTIN (and GST amount) and line items through to review; flag bills whose date or due date is more than ~12 months old before 'File it'.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
+          <t>Good overall, in 31.9s at 92% confidence: supplier Service TEST 123 with phone and email, number X33, amount 27,625, due 2018-03-01, booked as Inventory, and a 'Pay vendor bill' follow-up task. But the invoice DATE, the supplier GSTIN and the line items are not captured, and nothing warns that the bill fell due eight years ago - filing it would add an overdue payable dated 2018 without comment.</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:17-21</t>
+          <t>pages/finance/ReviewPanel.js; services/ingestion.py (ai_extract_document)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -26789,7 +27617,7 @@
     <row r="97" ht="82" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>CL-04</t>
+          <t>GL-03</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -26799,12 +27627,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Operations tab - add links</t>
+          <t>/login while signed in</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -26819,17 +27647,17 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>py-1 / min-h-6 on both.</t>
+          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
+          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
+          <t>pages/Login.js (component top)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -26842,7 +27670,7 @@
     <row r="98" ht="82" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AU-01</t>
+          <t>DD-04</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -26852,12 +27680,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Login, sign-up and admin fields</t>
+          <t>Company / You switch (mobile)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -26872,17 +27700,17 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
+          <t>Show the joined pill pair above the score below lg.</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
+          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
+          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -26895,7 +27723,7 @@
     <row r="99" ht="82" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AU-02</t>
+          <t>DD-05</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -26905,12 +27733,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Mobile OTP - phone number</t>
+          <t>Decision review - note mic</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -26925,17 +27753,17 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:179-190, :317</t>
+          <t>components/DecisionDialog.js:421-445</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -26948,7 +27776,7 @@
     <row r="100" ht="82" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>AU-03</t>
+          <t>CL-03</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -26958,12 +27786,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Login - header links (desktop)</t>
+          <t>Mark all read</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -26978,17 +27806,17 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>py-1 on both links.</t>
+          <t>toast.error('Couldn't mark notifications read') in onError.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
+          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:241-246</t>
+          <t>pages/Notifications.js:17-21</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -27001,7 +27829,7 @@
     <row r="101" ht="82" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>CL-04</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -27011,12 +27839,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Operations tab - add links</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -27024,24 +27852,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>py-1 / min-h-6 on both.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
@@ -27054,7 +27882,7 @@
     <row r="102" ht="82" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>AU-01</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -27064,12 +27892,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Sign-in</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Login, sign-up and admin fields</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -27077,24 +27905,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -27107,7 +27935,7 @@
     <row r="103" ht="82" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>AU-02</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -27117,12 +27945,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Sign-in</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Mobile OTP - phone number</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -27130,24 +27958,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Login.js:179-190, :317</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
@@ -27160,7 +27988,7 @@
     <row r="104" ht="82" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>AU-03</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -27170,12 +27998,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Sign-in</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Login - header links (desktop)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -27183,24 +28011,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>py-1 on both links.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Login.js:241-246</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -27213,7 +28041,7 @@
     <row r="105" ht="82" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -27223,12 +28051,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -27243,17 +28071,17 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
@@ -27266,7 +28094,7 @@
     <row r="106" ht="82" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -27276,12 +28104,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -27296,17 +28124,17 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
@@ -27319,58 +28147,270 @@
     <row r="107" ht="82" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="82" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="82" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="82" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="82" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
+      <c r="F111" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="4" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K107"/>
+  <autoFilter ref="A1:K111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28394,7 +29434,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>272 (185 pass, 85 fail, 0 blocked, 2 not run)</t>
+          <t>282 (191 pass, 89 fail, 0 blocked, 2 not run)</t>
         </is>
       </c>
     </row>
@@ -28406,7 +29446,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>2 Critical, 22 High, 28 Medium, 25 Low, 7 Nit</t>
+          <t>2 Critical, 24 High, 28 Medium, 27 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$283</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -99,7 +99,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -119,6 +119,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FDE7E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6EEFB"/>
       </patternFill>
     </fill>
     <fill>
@@ -154,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -186,6 +191,9 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -204,10 +212,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6455,9 +6463,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>Assigned - Yokesh</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -6505,7 +6513,11 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>OWNER: Yokesh (founder call, 2026-09-13) - all Dex issues are his; not to be worked on elsewhere.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -6538,9 +6550,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>Assigned - Yokesh</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -6588,7 +6600,11 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>OWNER: Yokesh (founder call, 2026-09-13) - all Dex issues are his; not to be worked on elsewhere.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -7451,9 +7467,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>Assigned - Yokesh</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -7501,7 +7517,11 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>OWNER: Yokesh (founder call, 2026-09-13) - all Dex issues are his; not to be worked on elsewhere.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
@@ -12243,7 +12263,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="H84" s="11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17591,7 +17611,7 @@
           <t>AI</t>
         </is>
       </c>
-      <c r="H192" s="10" t="inlineStr">
+      <c r="H192" s="11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22438,7 +22458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22778,7 +22798,7 @@
           <t>ASK-4</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>Parked - needs design</t>
         </is>
@@ -22949,7 +22969,7 @@
           <t>ASK-6</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>Deferred - founder</t>
         </is>
@@ -23397,7 +23417,7 @@
           <t>TM-03</t>
         </is>
       </c>
-      <c r="K17" s="10" t="inlineStr">
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>Parked - needs design</t>
         </is>
@@ -23748,60 +23768,64 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MW-08</t>
+          <t>ASK-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Task card - Update / Escalate</t>
+          <t>Dex answers what it is asked - taken over by Yokesh</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
+          <t>OWNER: YOKESH - all Dex issues are taken over by him (founder call, 2026-09-13); do not action them outside his work. SCOPE, from the live AI runs: (1) DX-01 - money questions answered with zeros: the planner's question words ('owe', 'receivable') are applied as an invoice-name filter, so 'How much do customers owe us?' returns Rs 0 against a real Rs 7,49,000. Only filter by keywords that match real records, extend the stop-word list, and never answer 'zero' from an empty filtered set when the collection has rows. (2) DX-02 - 'What needs my attention today?' (Dex's own first suggestion) reads 'today' as a created/due-today filter and 'todo' as an exact status, so it tells the owner nothing is open or overdue while 24 are open and 6 overdue. Serve it from the Desk's counters (decisions, on fire, overdue, receivables). (3) DD-05 - the decision-note mic only toasts 'Voice capture is available from the Dex panel'; wire it to Dex capture or remove it. ACCEPTANCE: re-run backend/scripts/ux_ai_live_0913.py - both questions must match the ledger / task counts, and the Sales refusal must still hold.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
+          <t>Dex is the product's answer surface; an owner who asks it the two most basic questions gets confident, wrong answers with KPI tiles reading Rs 0. What already works and must survive: numbers are computed in code, not by the model; Sales is refused money questions; mobile answers render; global search hands off. Finance AI (analysis + ask), coach, rescore and extraction were checked separately and are NOT in this ask.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>routers/brain.py:127-187 (_plan, _refine_plan, _KW_STOP, _rx), :241-309 (_retrieve), :463-478 (_compute_tasks), :836-843; components/DecisionDialog.js:421-445 (note mic)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>DX-01, DX-02, DD-05</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>Assigned - Yokesh</t>
         </is>
       </c>
     </row>
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MW-20</t>
+          <t>MW-08</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -23816,7 +23840,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - every click inside closes it</t>
+          <t>Task card - Update / Escalate</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -23831,17 +23855,17 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Stop propagation at the drawer boundary: onClick={(e) =&gt; e.stopPropagation()} and onKeyDown={(e) =&gt; e.stopPropagation()} on SheetContent. Or, better, render the Sheet as a SIBLING of the card root rather than a child, so the drawer is outside the clickable element in the component tree. Also guard the root handler with e.currentTarget.contains(e.target) - that is a DOM check, which a portal click fails. Add the five-click test to the verify script.</t>
+          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Every click closes it, on both viewports - 10 of 10. The drawer is now the only place a task can be worked (status, progress, Complete, Attach, Log update, hand off), so none of that is usable. On mobile the status pill tap fired its PATCH before the drawer shut, so the action happens but the user is thrown back to the list without seeing it. Likely also (from the code, not testable while the form cannot be opened): pressing Space or Enter in any drawer field hits the card's onKeyDown, which calls preventDefault and toggles the drawer - so a user could not type a space in an update note.</t>
+          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1242-1255 (card root onClick / onKeyDown), the &lt;Sheet&gt; rendered inside the same component (~:1360)</t>
+          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -23854,7 +23878,7 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MW-09</t>
+          <t>MW-20</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -23869,7 +23893,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Task card - 'Log update or hand off' (mobile)</t>
+          <t>Task drawer - every click inside closes it</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -23877,24 +23901,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
+          <t>Stop propagation at the drawer boundary: onClick={(e) =&gt; e.stopPropagation()} and onKeyDown={(e) =&gt; e.stopPropagation()} on SheetContent. Or, better, render the Sheet as a SIBLING of the card root rather than a child, so the drawer is outside the clickable element in the component tree. Also guard the root handler with e.currentTarget.contains(e.target) - that is a DOM check, which a portal click fails. Add the five-click test to the verify script.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
+          <t>Every click closes it, on both viewports - 10 of 10. The drawer is now the only place a task can be worked (status, progress, Complete, Attach, Log update, hand off), so none of that is usable. On mobile the status pill tap fired its PATCH before the drawer shut, so the action happens but the user is thrown back to the list without seeing it. Likely also (from the code, not testable while the form cannot be opened): pressing Space or Enter in any drawer field hits the card's onKeyDown, which calls preventDefault and toggles the drawer - so a user could not type a space in an update note.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
+          <t>pages/MyWork.js:1242-1255 (card root onClick / onKeyDown), the &lt;Sheet&gt; rendered inside the same component (~:1360)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -23907,7 +23931,7 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MW-10</t>
+          <t>MW-09</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -23917,12 +23941,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Application shell</t>
+          <t>Task card - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -23937,17 +23961,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
+          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
+          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
+          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -23960,7 +23984,7 @@
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MW-01</t>
+          <t>MW-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -23970,12 +23994,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Task card - status control</t>
+          <t>Application shell</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -23990,17 +24014,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
+          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
+          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
+          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -24013,7 +24037,7 @@
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MW-02</t>
+          <t>MW-01</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -24028,7 +24052,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Task card - detail dialog</t>
+          <t>Task card - status control</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -24043,17 +24067,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
+          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
+          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
+          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -24066,7 +24090,7 @@
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MW-21</t>
+          <t>MW-02</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -24081,7 +24105,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Task - Delete</t>
+          <t>Task card - detail dialog</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -24096,17 +24120,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Put 'Delete task' in the drawer - a quiet destructive button at the foot of the drawer, keeping the existing confirm step - or restore a 'View details' entry. Owner-only, as it was.</t>
+          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>There is no way to delete a task. The detail dialog still contains 'Delete task' with its confirmation, but nothing opens that dialog any more. Its only entry point was 'View details' in the card's ••• menu, and 98b43f4 removed that menu on the reasoning that 'the drawer already exposes every detail action' - but the drawer has no Delete.</t>
+          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:782-940 (TaskDetailDialog + delete), :1074 and :1941 (detailOpen with no opener)</t>
+          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -24119,7 +24143,7 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MW-15</t>
+          <t>MW-21</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -24134,7 +24158,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - close (mobile)</t>
+          <t>Task - Delete</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -24149,17 +24173,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Below sm, put the close INSIDE the drawer header (a 44px X at the right of the sticky title bar, or a back chevron at its left) and keep the protruding tab for sm and up: e.g. 'right-3 top-3 sm:left-0 sm:right-auto sm:-translate-x-full'. Alternatively leave a strip of scrim on phones (w-[92%]) so tapping outside works. Either way, test on a phone width before shipping a change to the drawer frame.</t>
+          <t>Put 'Delete task' in the drawer - a quiet destructive button at the foot of the drawer, keeping the existing confirm step - or restore a 'View details' entry. Owner-only, as it was.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>There is no way to close it. The drawer is w-full, so it covers the whole screen and there is no scrim left to tap. The new left-edge close tab sits at x=-43, entirely off-screen. The stock Radix close is at top-right but the sticky title bar paints over it - only a sliver of its focus ring peeks out. Escape closes it, but phones have no Escape key. Browser Back does not close the drawer either: it leaves My Work for the previous route. A phone user who opens a task is stuck.</t>
+          <t>There is no way to delete a task. The detail dialog still contains 'Delete task' with its confirmation, but nothing opens that dialog any more. Its only entry point was 'View details' in the card's ••• menu, and 98b43f4 removed that menu on the reasoning that 'the drawer already exposes every detail action' - but the drawer has no Delete.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1427-1441 (SheetContent w-full + SheetClose -translate-x-full)</t>
+          <t>pages/MyWork.js:782-940 (TaskDetailDialog + delete), :1074 and :1941 (detailOpen with no opener)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -24172,7 +24196,7 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MW-16</t>
+          <t>MW-15</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -24187,7 +24211,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - 'Log update or hand off' (mobile)</t>
+          <t>Task drawer - close (mobile)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -24202,17 +24226,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Render TaskTrail (or at least its UpdateForm) outside the lg-gated body, shared by both layouts, or mount a second instance inside the mobile body. Add the MW-09 check to the verify script so the next drawer change cannot regress it silently.</t>
+          <t>Below sm, put the close INSIDE the drawer header (a 44px X at the right of the sticky title bar, or a back chevron at its left) and keep the protruding tab for sm and up: e.g. 'right-3 top-3 sm:left-0 sm:right-auto sm:-translate-x-full'. Alternatively leave a strip of scrim on phones (w-[92%]) so tapping outside works. Either way, test on a phone width before shipping a change to the drawer frame.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Nothing appears. The button is visible and tappable, and the form IS mounted - but inside the desktop body, which is display:none below lg. This is MW-09 back: the one control that records what happened is inert on phones again. Desktop is unaffected (form opens, no crash).</t>
+          <t>There is no way to close it. The drawer is w-full, so it covers the whole screen and there is no scrim left to tap. The new left-edge close tab sits at x=-43, entirely off-screen. The stock Radix close is at top-right but the sticky title bar paints over it - only a sliver of its focus ring peeks out. Escape closes it, but phones have no Escape key. Browser Back does not close the drawer either: it leaves My Work for the previous route. A phone user who opens a task is stuck.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1658-1662 (mobile trigger), :1679 (desktop body 'hidden lg:block'), :1960 (the only &lt;TaskTrail&gt;)</t>
+          <t>pages/MyWork.js:1427-1441 (SheetContent w-full + SheetClose -translate-x-full)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -24225,7 +24249,7 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CR-04</t>
+          <t>MW-16</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -24235,12 +24259,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Add contact menu (mobile)</t>
+          <t>Task drawer - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -24255,17 +24279,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
+          <t>Render TaskTrail (or at least its UpdateForm) outside the lg-gated body, shared by both layouts, or mount a second instance inside the mobile body. Add the MW-09 check to the verify script so the next drawer change cannot regress it silently.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
+          <t>Nothing appears. The button is visible and tappable, and the form IS mounted - but inside the desktop body, which is display:none below lg. This is MW-09 back: the one control that records what happened is inert on phones again. Desktop is unaffected (form opens, no crash).</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
+          <t>pages/MyWork.js:1658-1662 (mobile trigger), :1679 (desktop body 'hidden lg:block'), :1960 (the only &lt;TaskTrail&gt;)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -24278,7 +24302,7 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CR-05</t>
+          <t>CR-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -24293,7 +24317,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Filter button (mobile)</t>
+          <t>Add contact menu (mobile)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -24308,17 +24332,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
+          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
+          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
+          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -24331,7 +24355,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>OP-01</t>
+          <t>CR-05</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -24341,12 +24365,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Team execution panel</t>
+          <t>Filter button (mobile)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -24361,17 +24385,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Decide which is true and make them agree. A rolling window is the more useful of the two -- an operating score should recover when the business recovers -- so filter each query to the last 30 days and keep the caption. If all-time is deliberate, the caption has to say so.</t>
+          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>The panel says 'Last 30 days - open anyone to see their full ops'. The service applies no date filter anywhere: tasks, decisions, invoices and the per-employee leaderboard are all queried for the whole tenant with no window at all. So an owner reads a colleague's score believing it reflects the last month, when it carries every task since the workspace opened -- somebody who was slow in August can never recover from it, and somebody who has improved this month does not show it.</t>
+          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (all queries); the caption is in pages/OperatingScore.js, team-execution section</t>
+          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -24384,7 +24408,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>OP-02</t>
+          <t>OP-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -24399,7 +24423,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>'Do these first' on mobile</t>
+          <t>Team execution panel</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -24414,17 +24438,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>On mobile the band should flow with the page rather than being pinned, so the score, the actions and the team list scroll as one column. If it must stay pinned, it needs to collapse to a handle the user can pull up.</t>
+          <t>Decide which is true and make them agree. A rolling window is the more useful of the two -- an operating score should recover when the business recovers -- so filter each query to the last 30 days and keep the caption. If all-time is deliberate, the caption has to say so.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>It is 90 per cent hidden. 'Do these first' occupies y=425 to 710, and a fixed black 'Team execution' band is pinned from y=454 to the bottom of the screen -- 374px, 46 per cent of the viewport -- covering 256 of its 285px. Scrolling does not help: the document itself does not scroll (scrollHeight equals clientHeight), and the element that does scroll is the dark band, not the page. So the three actions the page exists to recommend are permanently reduced to one visible line.</t>
+          <t>The panel says 'Last 30 days - open anyone to see their full ops'. The service applies no date filter anywhere: tasks, decisions, invoices and the per-employee leaderboard are all queried for the whole tenant with no window at all. So an owner reads a colleague's score believing it reflects the last month, when it carries every task since the workspace opened -- somebody who was slow in August can never recover from it, and somebody who has improved this month does not show it.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (kr-dark-band team-execution section)</t>
+          <t>services/operating_score.py (all queries); the caption is in pages/OperatingScore.js, team-execution section</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -24437,7 +24461,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>OP-03</t>
+          <t>OP-02</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -24452,7 +24476,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>'Do these first' on mobile</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -24467,17 +24491,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Score each leg as a bounded rate rather than a penalty subtracted from a constant, so the number always has somewhere to move. Where a leg really is at the floor, say 'below floor' rather than printing a 0 that looks like an empty metric. See ASK-19 for the wider redesign.</t>
+          <t>On mobile the band should flow with the page rather than being pinned, so the score, the actions and the team list scroll as one column. If it must stay pinned, it needs to collapse to a handle the user can pull up.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Two of the four legs are pinned at the floor and carry no information. Execution reads 0 and Responsiveness reads 0. Responsiveness actually computes to -296 before clamping (100 - 16 complaints x 12 - 68 overdue x 3), so it would take closing 8 complaints AND clearing 33 overdue tasks before the number moves off zero by a single point. The page's own advice is 'Close 16 open complaints' -- doing all of that would leave the score exactly where it is. The owner gets no gradient at precisely the moment they most need one.</t>
+          <t>It is 90 per cent hidden. 'Do these first' occupies y=425 to 710, and a fixed black 'Team execution' band is pinned from y=454 to the bottom of the screen -- 374px, 46 per cent of the viewport -- covering 256 of its 285px. Scrolling does not help: the document itself does not scroll (scrollHeight equals clientHeight), and the element that does scroll is the dark band, not the page. So the three actions the page exists to recommend are permanently reduced to one visible line.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and the responsiveness expression in _company_operating_view</t>
+          <t>pages/OperatingScore.js (kr-dark-band team-execution section)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -24490,7 +24514,7 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>OP-10</t>
+          <t>OP-03</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -24505,7 +24529,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Ops page when the request fails</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -24520,17 +24544,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Read isError and error from the query and render a message: 403 -&gt; 'Only the owner can view another person's operating page', 404 -&gt; 'This person is no longer on the team', otherwise 'Couldn't load'. Each with a link to /operating-score. WorkCoach.js:36-57 is the pattern to copy. Also set retry: false for 4xx so the error shows at once.</t>
+          <t>Score each leg as a bounded rate rather than a penalty subtracted from a constant, so the number always has somewhere to move. Where a leg really is at the floor, say 'below floor' rather than printing a 0 that looks like an empty metric. See ASK-19 for the wider redesign.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>The loading skeleton stays on screen forever, with aria-busy=true and no text at all. The API answered in milliseconds - 404 'Team member not found' for the owner, 403 for the three other roles - but the page never shows it. The user cannot tell a slow page from a broken link or a refused one, and there is no way back except the browser. Any stale shared link (a person who has left, a link forwarded to a teammate) lands here.</t>
+          <t>Two of the four legs are pinned at the floor and carry no information. Execution reads 0 and Responsiveness reads 0. Responsiveness actually computes to -296 before clamping (100 - 16 complaints x 12 - 68 overdue x 3), so it would take closing 8 complaints AND clearing 33 overdue tasks before the number moves off zero by a single point. The page's own advice is 'Close 16 open complaints' -- doing all of that would leave the score exactly where it is. The owner gets no gradient at precisely the moment they most need one.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js:85-92 (useQuery + the skeleton fallback); pages/WorkCoach.js:36-57 (the working pattern)</t>
+          <t>services/operating_score.py:_score_execution and the responsiveness expression in _company_operating_view</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -24543,7 +24567,7 @@
     <row r="39" ht="82" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CR-10</t>
+          <t>OP-10</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -24553,12 +24577,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Contact list when loading fails</t>
+          <t>Ops page when the request fails</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -24573,17 +24597,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Read isError from the query and render 'Couldn't load your contacts' with a Retry that calls refetch(). Show '-' rather than 0 in the scope chips while loading or failed. Same fix pattern as OP-10 - worth one shared &lt;QueryError&gt; component.</t>
+          <t>Read isError and error from the query and render a message: 403 -&gt; 'Only the owner can view another person's operating page', 404 -&gt; 'This person is no longer on the team', otherwise 'Couldn't load'. Each with a link to /operating-score. WorkCoach.js:36-57 is the pattern to copy. Also set retry: false for 4xx so the error shows at once.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>The loading skeleton stays forever. On desktop the chips read 'Buyers 0' and 'Suppliers 0' above six blank placeholder cards, so an owner with a flaky connection sees what looks like a CRM with no customers, still loading. On mobile it is the same skeleton with nothing else. No toast, no message, no retry. The same fault as OP-10 on Ops.</t>
+          <t>The loading skeleton stays on screen forever, with aria-busy=true and no text at all. The API answered in milliseconds - 404 'Team member not found' for the owner, 403 for the three other roles - but the page never shows it. The user cannot tell a slow page from a broken link or a refused one, and there is no way back except the browser. Any stale shared link (a person who has left, a link forwarded to a teammate) lands here.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:524-527 (contacts useQuery), scope-count chips :819-835</t>
+          <t>pages/OperatingScore.js:85-92 (useQuery + the skeleton fallback); pages/WorkCoach.js:36-57 (the working pattern)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -24596,7 +24620,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FN-01</t>
+          <t>CR-10</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -24606,12 +24630,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Every money figure</t>
+          <t>Contact list when loading fails</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -24626,17 +24650,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
+          <t>Read isError from the query and render 'Couldn't load your contacts' with a Retry that calls refetch(). Show '-' rather than 0 in the scope chips while loading or failed. Same fix pattern as OP-10 - worth one shared &lt;QueryError&gt; component.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
+          <t>The loading skeleton stays forever. On desktop the chips read 'Buyers 0' and 'Suppliers 0' above six blank placeholder cards, so an owner with a flaky connection sees what looks like a CRM with no customers, still loading. On mobile it is the same skeleton with nothing else. No toast, no message, no retry. The same fault as OP-10 on Ops.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
+          <t>pages/CRM.js:524-527 (contacts useQuery), scope-count chips :819-835</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -24649,7 +24673,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FN-02</t>
+          <t>FN-01</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -24664,7 +24688,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Net profit hero (mobile)</t>
+          <t>Every money figure</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -24679,17 +24703,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
+          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
+          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
+          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -24702,7 +24726,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FN-03</t>
+          <t>FN-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -24717,7 +24741,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Revenue and Net profit trend badges (mobile)</t>
+          <t>Net profit hero (mobile)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -24732,17 +24756,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
+          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
+          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
+          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -24755,7 +24779,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FN-06</t>
+          <t>FN-03</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -24770,7 +24794,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Delete on expenses, invoices and payments</t>
+          <t>Revenue and Net profit trend badges (mobile)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -24785,17 +24809,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Put a confirm step in del() and delRevenue(): an AlertDialog naming the record and amount ('Delete invoice SBT/25-26/0431 for Rs 2,85,000?'). Alternatively delete optimistically with an Undo toast and commit after a few seconds. Either way, one tap must not be final.</t>
+          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>One tap sends the DELETE straight away. No confirmation dialog, no 'are you sure', no undo toast - for all three record types, both viewports, both roles. The trash icon is a 36px target at the end of each row, so a stray tap while scrolling a phone ledger deletes a real invoice or payment and silently changes Revenue, Received and Net profit. (The harness blocked every DELETE, so nothing was removed.)</t>
+          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1541-1549 (del, delRevenue); :886 and :912 (revenue invoice/payment trash); :1264 (expense trash)</t>
+          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -24808,7 +24832,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FN-07</t>
+          <t>FN-06</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -24823,7 +24847,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Finance for Sales and Production</t>
+          <t>Delete on expenses, invoices and payments</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -24838,17 +24862,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Decide what data_input-only users should get. If it is capture only, show them the capture bar and Inbox with a line such as 'You can upload bills here; totals are visible to Finance and the Owner', and hide the money tabs. If they should not be here at all, drop data_input from the route and nav perms. In both cases handle 403 in the page (see FN-09).</t>
+          <t>Put a confirm step in del() and delRevenue(): an AlertDialog naming the record and amount ('Delete invoice SBT/25-26/0431 for Rs 2,85,000?'). Alternatively delete optimistically with an Undo toast and commit after a few seconds. Either way, one tap must not be final.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Both roles see Finance in the nav and the Money dock and can open it - then every ledger request is refused (6 x 403). The Overview sits on 'Loading...' forever. Revenue, Expenses, Assets and Inventory each show their empty state ('No expenses yet...'), telling the user the company has no money records rather than that they are not allowed to see them. Only the capture bar works. So the page misinforms rather than refuses.</t>
+          <t>One tap sends the DELETE straight away. No confirmation dialog, no 'are you sure', no undo toast - for all three record types, both viewports, both roles. The trash icon is a 36px target at the end of each row, so a stray tap while scrolling a phone ledger deletes a real invoice or payment and silently changes Revenue, Received and Net profit. (The harness blocked every DELETE, so nothing was removed.)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>App.js:237 (route perms); components/Layout.js:79 (nav perms); routers/ledger.py:619-625 (require_ledger); pages/Ledger.js:1522-1527 (queries without isError), :1641-1642 (Loading...)</t>
+          <t>pages/Ledger.js:1541-1549 (del, delRevenue); :886 and :912 (revenue invoice/payment trash); :1264 (expense trash)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -24861,7 +24885,7 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FN-08</t>
+          <t>FN-07</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -24876,7 +24900,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Adding records on a phone</t>
+          <t>Finance for Sales and Production</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -24891,17 +24915,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Render the per-tab Add button on mobile too (drop hidden lg:block, or add a mobile placement), and have the tile open AddExpenseDialog directly through state rather than clicking a DOM node by testid.</t>
+          <t>Decide what data_input-only users should get. If it is capture only, show them the capture bar and Inbox with a line such as 'You can upload bills here; totals are visible to Finance and the Owner', and hide the money tabs. If they should not be here at all, drop data_input from the route and nav perms. In both cases handle 403 in the page (see FN-09).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>There is no way to add a record manually on a phone. The four Add buttons (Add income / expense / asset / inventory) are rendered but hidden below lg. The 'Add expense' tile in 'Simplify your finances' does nothing on any tab: it looks for an element that does not exist. Upload and scan still work, so a cash expense with no bill cannot be recorded from the phone at all.</t>
+          <t>Both roles see Finance in the nav and the Money dock and can open it - then every ledger request is refused (6 x 403). The Overview sits on 'Loading...' forever. Revenue, Expenses, Assets and Inventory each show their empty state ('No expenses yet...'), telling the user the company has no money records rather than that they are not allowed to see them. Only the capture bar works. So the page misinforms rather than refuses.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1422-1429 (tile + querySelector), :1630 ('hidden lg:block' addBtn), :1551-1557 (addBtn per tab)</t>
+          <t>App.js:237 (route perms); components/Layout.js:79 (nav perms); routers/ledger.py:619-625 (require_ledger); pages/Ledger.js:1522-1527 (queries without isError), :1641-1642 (Loading...)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -24914,7 +24938,7 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>DX-01</t>
+          <t>FN-08</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -24924,12 +24948,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Ask Dex - money questions</t>
+          <t>Adding records on a phone</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -24944,17 +24968,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Only apply keywords as a record filter when they look like an entity reference (a customer, vendor or invoice number that exists in the tenant); otherwise ignore them for aggregation intents. At minimum add owe/owes/owed/receivable(s)/payable(s)/dues to _KW_STOP. And when an aggregation over a finance entity returns 0 rows while the collection is non-empty, re-run without keywords rather than answer 'zero'.</t>
+          <t>Render the per-tab Add button on mobile too (drop hidden lg:block, or add a mobile placement), and have the tile open AddExpenseDialog directly through state rather than clicking a DOM node by testid.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Dex answered, in bold, 'zero invoices, zero billed amount, and zero outstanding balance - the receivables table is empty', with three KPI tiles reading Invoices 0 / Billed Rs 0 / Outstanding Rs 0, suggested the data 'hasn't been synced', and cited 8 unrelated sources (test tasks, a dispatch, resolved complaints). The ledger holds Rs 26,85,000 billed and Rs 7,49,000 outstanding. An owner asking the most basic money question is told, confidently, that nobody owes them anything.</t>
+          <t>There is no way to add a record manually on a phone. The four Add buttons (Add income / expense / asset / inventory) are rendered but hidden below lg. The 'Add expense' tile in 'Simplify your finances' does nothing on any tab: it looks for an element that does not exist. Upload and scan still work, so a cash expense with no bill cannot be recorded from the phone at all.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>routers/brain.py:172-187 (_KW_STOP, _rx), :294-299 (invoices retrieval), :836-843</t>
+          <t>pages/Ledger.js:1422-1429 (tile + querySelector), :1630 ('hidden lg:block' addBtn), :1551-1557 (addBtn per tab)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -24967,7 +24991,7 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>DX-02</t>
+          <t>DX-01</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -24982,7 +25006,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Ask Dex - 'What needs my attention today?'</t>
+          <t>Ask Dex - money questions</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -24997,17 +25021,17 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Treat 'what needs my attention' as a composite intent served from the Desk's own counters (needs_decision, on_fire, overdue, receivables) rather than a single-entity list; or map it to status overdue|in_progress|todo with no date window. Add it to the planner guardrails in _refine_plan, since it is Dex's first suggested question.</t>
+          <t>Only apply keywords as a record filter when they look like an entity reference (a customer, vendor or invoice number that exists in the tenant); otherwise ignore them for aggregation intents. At minimum add owe/owes/owed/receivable(s)/payable(s)/dues to _KW_STOP. And when an aggregation over a finance entity returns 0 rows while the collection is non-empty, re-run without keywords rather than answer 'zero'.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>'Good news - there are no open or overdue tasks requiring your attention right now', followed by a list of things already completed. One question later, 'Which tasks are overdue?' answered 'All 34 matching tasks are overdue'. The page's headline suggestion gives the owner false reassurance.</t>
+          <t>Dex answered, in bold, 'zero invoices, zero billed amount, and zero outstanding balance - the receivables table is empty', with three KPI tiles reading Invoices 0 / Billed Rs 0 / Outstanding Rs 0, suggested the data 'hasn't been synced', and cited 8 unrelated sources (test tasks, a dispatch, resolved complaints). The ledger holds Rs 26,85,000 billed and Rs 7,49,000 outstanding. An owner asking the most basic money question is told, confidently, that nobody owes them anything.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>routers/brain.py:127-141 (_plan), :144+ (_refine_plan), :463-478 (_compute_tasks filters); pages/Brain.js suggestions</t>
+          <t>routers/brain.py:172-187 (_KW_STOP, _rx), :294-299 (invoices retrieval), :836-843</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -25020,7 +25044,7 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>DD-01</t>
+          <t>DX-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -25030,12 +25054,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>/decisions/:id - missing or not yours</t>
+          <t>Ask Dex - 'What needs my attention today?'</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -25050,17 +25074,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
+          <t>Treat 'what needs my attention' as a composite intent served from the Desk's own counters (needs_decision, on_fire, overdue, receivables) rather than a single-entity list; or map it to status overdue|in_progress|todo with no date window. Add it to the planner guardrails in _refine_plan, since it is Dex's first suggested question.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
+          <t>'Good news - there are no open or overdue tasks requiring your attention right now', followed by a list of things already completed. One question later, 'Which tasks are overdue?' answered 'All 34 matching tasks are overdue'. The page's headline suggestion gives the owner false reassurance.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
+          <t>routers/brain.py:127-141 (_plan), :144+ (_refine_plan), :463-478 (_compute_tasks filters); pages/Brain.js suggestions</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -25073,7 +25097,7 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>DD-02</t>
+          <t>DD-01</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -25088,7 +25112,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Desk board when loading fails</t>
+          <t>/decisions/:id - missing or not yours</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -25103,17 +25127,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
+          <t>Give the error branch a 'Back to Decision Desk' button (and the same close control). Branch the copy on status: 403 -&gt; no access, 404 -&gt; 'This decision no longer exists', otherwise 'Couldn't load - Retry'.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
+          <t>Full-screen 'Access restricted - You don't have access to this decision.' with no Close, no Back and no link. Escape and outside taps are deliberately ignored on the page variant, so the user is trapped until they find the browser Back button. The message is also wrong for a missing decision (the API said 404 'Not found') and for a network error. Decisions are opened from notifications and pasted links, so this is where stale links land.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
+          <t>components/DecisionDialog.js:188-218 (error branch, page variant handlers)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -25126,7 +25150,7 @@
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>DD-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -25136,12 +25160,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Desk board when loading fails</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -25149,24 +25173,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Check isError on the board queries; render 'Couldn't load your desk - Retry' and keep counts as '-' rather than 0. Same shared &lt;QueryError&gt; as OP-10 / CR-10 / FN-09.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>It says 'Nothing waiting on you' with Needs your decision 0, On fire 0, Due today 0, Important 0. The real counts at the time were 53 decisions and 58 on fire. An owner on a weak connection is told the desk is clear.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/Desk.js:284-292 (boardQs + zero counters)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -25179,7 +25203,7 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -25194,7 +25218,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -25209,17 +25233,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -25232,7 +25256,7 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -25242,12 +25266,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -25262,17 +25286,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -25285,7 +25309,7 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -25300,7 +25324,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -25315,17 +25339,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -25338,7 +25362,7 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>MW-17</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -25353,7 +25377,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Task drawer - two close buttons, invisible focus</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -25368,17 +25392,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -25391,7 +25415,7 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MW-18</t>
+          <t>MW-17</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -25401,12 +25425,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application shell at wide widths</t>
+          <t>Task drawer - two close buttons, invisible focus</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -25421,17 +25445,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
+          <t>Give SheetContent a hideClose prop (default false, so other sheets are unchanged) and pass it here; set onOpenAutoFocus to focus the title or the close tab. That also resolves which close MW-15 should keep.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
+          <t>Every drawer carries TWO close buttons: the new 'Close task' tab and the stock shadcn 'Close' that SheetContent always renders. The stock one is covered by the sticky title bar, yet Radix focuses it on open - so keyboard focus starts on a control nobody can see, and a screen reader announces 'Close' and 'Close task' as two separate buttons.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:634 (app-shell className)</t>
+          <t>components/ui/sheet.jsx:46-58; pages/MyWork.js:1427-1445</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -25444,7 +25468,7 @@
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-18</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -25454,12 +25478,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Application shell at wide widths</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -25474,17 +25498,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Restore the cap in Layout and lift it only where wanted: give My Work its own page-level wrapper (or a data-wide flag the shell reads). If wider is wanted everywhere, cap at ~1600px rather than none, and constrain the Finance tiles and AI brief rows internally.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>The cap was removed in the shared Layout, so EVERY page now runs edge-to-edge. On Finance each KPI tile is ~610px wide with its value at the far left and its arrow ~550px away; the Capture bar is 1,856px wide holding three small buttons; AI brief rows put the 'Urgent' tag ~1,700px from the sentence it qualifies. On Team each member card is ~610px wide with the name and '6 permissions' at opposite ends. Nothing overflows - it just reads as sparse and makes the eye travel.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>components/Layout.js:634 (app-shell className)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -25497,7 +25521,7 @@
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -25512,7 +25536,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -25527,17 +25551,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -25550,7 +25574,7 @@
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -25560,12 +25584,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -25580,17 +25604,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -25603,7 +25627,7 @@
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -25618,7 +25642,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -25633,17 +25657,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -25656,7 +25680,7 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -25671,7 +25695,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -25686,17 +25710,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -25709,7 +25733,7 @@
     <row r="61" ht="82" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -25719,12 +25743,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -25739,17 +25763,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_sales</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -25762,7 +25786,7 @@
     <row r="62" ht="82" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -25777,7 +25801,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -25792,17 +25816,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -25815,7 +25839,7 @@
     <row r="63" ht="82" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -25845,17 +25869,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_company_operating_view</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -25868,7 +25892,7 @@
     <row r="64" ht="82" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>OP-09</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -25883,7 +25907,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>'View all' links and the formula panel (mobile)</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -25898,17 +25922,17 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -25921,7 +25945,7 @@
     <row r="65" ht="82" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>OP-11</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -25936,7 +25960,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Personal (self) view - bottom band (mobile)</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -25951,17 +25975,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -25974,7 +25998,7 @@
     <row r="66" ht="82" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>OP-12</t>
+          <t>OP-11</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -25989,7 +26013,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - entry point</t>
+          <t>Personal (self) view - bottom band (mobile)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -26004,17 +26028,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
+          <t>Keep KM-33 for the owner view. In the self view, drop the kr-dark-band class (or add a variant that stays in the scroll flow) and show the peer ranking as an ordinary line or card above the open work. If a pinned sheet is wanted here, it needs content worth pinning and bottom padding that clears the dock.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
+          <t>A 176px near-black band is pinned to the bottom of every non-owner's phone screen - over a fifth of the viewport - and it holds ONE sentence: 'Among your sales peers you are ranked 2 of 7.' That sentence sits behind the floating dock, so it is only partly readable, and the band does not move when the page scrolls. It reads as a black rendering fault rather than a panel.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
+          <t>pages/OperatingScore.js (operating-self-band section); index.css:2171-2190 (.kr-dark-band fixed below lg, KM-33)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -26027,7 +26051,7 @@
     <row r="67" ht="82" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>CR-11</t>
+          <t>OP-12</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -26037,12 +26061,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Contact profile when loading fails</t>
+          <t>AI Work Coach - entry point</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -26057,17 +26081,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
+          <t>Add 'AI coach' next to 'Back to company' in the view-as banner (owner coaching a teammate), and 'My AI coach' on the self view and in the More panel. If the coach is being retired, remove the route and its endpoints instead of leaving it reachable only by URL.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
+          <t>Nothing in the app links to the AI Work Coach. It still works - it loads for all four roles, the owner can open a teammate's coach, the permission message is right - but the only way in is typing /coach. On 2026-09-12 the Ops employee card opened the coach (plan item D3); it now opens that person's Ops page instead, which removed the last route in. Two of the four demo seats already have coaching generated on 29 Aug, so this is a feature people used.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
+          <t>App.js:228 (/coach route); pages/OperatingScore.js:931 (employee card link); pages/OperatingScore.js:119-141 (ViewAsBanner)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -26080,7 +26104,7 @@
     <row r="68" ht="82" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>CR-12</t>
+          <t>CR-11</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -26095,7 +26119,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>GET /api/crm/outstanding</t>
+          <t>Contact profile when loading fails</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -26110,17 +26134,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
+          <t>Split the branch: if error has no response (network) or a 5xx, say 'Couldn't load this contact' with Retry; keep the 'isn't here' copy for a 404 or an empty body.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
+          <t>The page says 'That contact isn't here. It may have been merged or removed.' The customer exists; only the request failed. An owner reading this on a weak phone signal is told a real customer has been deleted or merged.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
+          <t>pages/ContactProfile.js:151-160; pages/mobile/ContactProfileMobile.jsx:85-99</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -26133,7 +26157,7 @@
     <row r="69" ht="82" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>CR-12</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -26143,12 +26167,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' tile</t>
+          <t>GET /api/crm/outstanding</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -26163,17 +26187,17 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
+          <t>Gate it with require_perm('people') (it only feeds the CRM grid) or require_perm('finance') to match the profile endpoint.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
+          <t>GET /api/contacts and GET /api/contacts/&lt;id&gt;/profile correctly refuse Sales with 403 - but GET /api/crm/outstanding answers 200 with every customer's receivables, payables, invoice count and days overdue. The keys are contact ids rather than names, so it is not a full leak on its own, but it hands money data to roles the rest of the app deliberately keeps out of finance.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
+          <t>routers/crm.py:37-38 (outstanding_by_contact, Depends(get_current_user))</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -26186,7 +26210,7 @@
     <row r="70" ht="82" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -26201,7 +26225,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>All figures</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -26216,17 +26240,17 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -26239,7 +26263,7 @@
     <row r="71" ht="82" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FN-09</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -26254,7 +26278,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Finance when a request fails</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -26269,17 +26293,17 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -26292,7 +26316,7 @@
     <row r="72" ht="82" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MW-22</t>
+          <t>FN-09</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -26302,12 +26326,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Task card - bulk-select checkbox (mobile)</t>
+          <t>Finance when a request fails</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -26322,17 +26346,17 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
+          <t>Check isError on each query and render 'Couldn't load &lt;tab&gt;' with Retry (403: 'You don't have access to the ledger'). One shared &lt;QueryError&gt; would serve this, OP-10 and CR-10.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
+          <t>Summary fails: the Overview says 'Loading...' indefinitely. Expenses fails: the Expenses tab shows 'No expenses yet - approved purchase bills and payments show up here automatically, or add one manually', directly under an AI panel that is still analysing those same expenses. An owner on a bad connection is told their books are empty. The same missing branch is behind FN-07.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
+          <t>pages/Ledger.js:1522-1527, :1641-1642, :1657-1659</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -26345,7 +26369,7 @@
     <row r="73" ht="82" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GL-01</t>
+          <t>MW-22</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -26355,12 +26379,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Desktop header - notification bell</t>
+          <t>Task card - bulk-select checkbox (mobile)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -26375,17 +26399,17 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
+          <t>Give the checkbox a 44x44 hit area again (a padded label around it, or a transparent ::before), and keep stopPropagation on that area so it never opens the drawer.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
+          <t>The checkbox is now 16x16 inside a 16x22 label - nothing larger is clickable. A tap 10px off in any direction lands on the card, and since 78d01df the whole card opens the task drawer. So on a phone, trying to select tasks for a bulk action frequently opens a task instead. 12 checkboxes on the first screen, all the same.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
+          <t>pages/MyWork.js (task card summary - bulk-select checkbox, top-left)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -26398,7 +26422,7 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GL-02</t>
+          <t>GL-01</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -26413,7 +26437,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Mobile More panel - non-owners</t>
+          <t>Desktop header - notification bell</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -26428,17 +26452,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
+          <t>Move Bellicon to module scope (a real component that takes notif/unread/bellCount as props), or render the Popover JSX inline rather than through an inner component. The same applies to any other component declared inside Layout.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
+          <t>On Decision Desk, My Work and Team the dropdown opens and then closes on its own about 0.4s later, dropping focus to &lt;body&gt;; nothing was clicked in between. On Finance it stays open. So on the desktop's most-used pages a user clicks the bell, sees a flash, and cannot read or open a notification. (The phone bell works.)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
+          <t>components/Layout.js:366-424 (Bellicon inside Layout)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -26451,7 +26475,7 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DD-03</t>
+          <t>GL-02</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -26461,12 +26485,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Money tiles for Sales / Production</t>
+          <t>Mobile More panel - non-owners</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -26481,17 +26505,17 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
+          <t>Align the tile filters with the routes: show Ops to everyone (it already renders a self view), Team to everyone (read-only for non-managers), and Settings to everyone (profile + security for non-owners).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
+          <t>On a phone, Sales, Production and Finance see only two tiles: Workflows and Leave. They cannot reach Ops, Team or Settings, although all three routes open for them and the desktop nav shows them Ops and Team. Ops was deliberately opened to every role so staff see their own metrics (App.js:222-226) - on mobile that view is unreachable.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
+          <t>components/mobile/AllAppsPanel.jsx:70-83 and :127 (tile filters)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -26504,7 +26528,7 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>CL-01</t>
+          <t>DD-03</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -26514,12 +26538,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Notifications, People, Journal, Calendar when loading fails</t>
+          <t>Money tiles for Sales / Production</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -26534,17 +26558,17 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
+          <t>Render money tiles only when hasPerm(user,'finance') || hasPerm(user,'ledger'); otherwise show the role's own tiles.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
+          <t>'Net profit' and 'Spend, this month' show '...' forever - their data (ledger summary) is refused with 403 - while 'To collect (overdue) Rs 7.5 L' is shown to these roles, a customer-receivables figure they have no finance permission for. Tapping the money tiles leads to the empty Finance page of FN-07.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
+          <t>pages/Desk.js:563-661 (KPI tiles), pages/desk/useDeskMetrics.js</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -26557,7 +26581,7 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>CL-02</t>
+          <t>CL-01</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -26567,12 +26591,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Calendar events</t>
+          <t>Notifications, People, Journal, Calendar when loading fails</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -26587,17 +26611,17 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
+          <t>One shared &lt;QueryError onRetry&gt; used wherever a query's data drives the page; branch 403 vs other errors. Fixing it once fixes OP-10, CR-10, FN-09, DD-02 and this.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
+          <t>Notifications says 'You're all caught up.' People says 'Members 0 - No team members yet.' Calendar shows every filter at 0. Journal shows only its header and nothing below. None says anything failed. With OP-10, CR-10, FN-09 and DD-02 this is the same fault on nine surfaces.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>pages/Calendar.js:233 (cal-event)</t>
+          <t>pages/Notifications.js:14, pages/People.js:47-53, pages/Journal.js:185, pages/Calendar.js:62</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -26610,7 +26634,7 @@
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>CL-02</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -26620,12 +26644,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Calendar events</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -26633,24 +26657,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Wrap each event in a Link to its source (task -&gt; /my-work?task=, decision -&gt; /decisions/, invoice -&gt; /finance?tab=revenue, leave -&gt; /team).</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Nothing happens. Events are plain &lt;div&gt;s with no link or handler, so the calendar shows 'Vendor Call - Next Monday - Overdue' but the user cannot get from it to the task to act on it.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/Calendar.js:233 (cal-event)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -26663,7 +26687,7 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>MW-19</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -26678,7 +26702,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Department filter dropdown</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -26693,17 +26717,17 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -26716,7 +26740,7 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>MW-19</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -26726,12 +26750,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Department filter dropdown</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -26746,17 +26770,17 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Filter options to count &gt; 0 (keep All), or render zero-count ones disabled; move Completed into the Status dropdown.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Three problems. (1) 'Completed 7' is listed as a Department - it is a state, and the Status dropdown beside it is where it belongs. (2) Six of the nine options read 0 (Sales 0, Production 0, Quality Control 0, Inventory 0, Finance 0, HR 0) - the old chip strip hid empty categories on a founder ask (U7-05.9). (3) Picking an empty one is silently undone: the trigger still reads 'Department: All 26' and nothing tells the user why.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>pages/MyWork.js:2042-2075 (FilterDropdown), :2735-2743 (Department options), :2288-2298 (snap-back effect)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -26769,7 +26793,7 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TM-07</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -26784,7 +26808,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog - closing</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -26799,17 +26823,17 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -26822,7 +26846,7 @@
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TM-08</t>
+          <t>TM-07</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -26832,12 +26856,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Default close button on every dialog</t>
+          <t>Member profile dialog - closing</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -26852,17 +26876,17 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
+          <t>Keep the Dialog mounted with open={!!u} and render only its content conditionally, so Radix's own focus return runs; or remember the opening card and focus it in onCloseAutoFocus.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
+          <t>Focus drops to &lt;body&gt;. A keyboard or screen-reader user who opens the fifth card and closes it is thrown back to the top of the page and has to Tab through the header, search and every earlier card to get back. On a 12-person roster that is a nuisance; on the larger teams the search box is built for, it makes the roster hard to work through.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx:37-41</t>
+          <t>pages/Team.js:450 (onOpen sets profileUser), :541-542 (openChange, 'if (!u) return null')</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -26875,7 +26899,7 @@
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>TM-08</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -26885,12 +26909,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Default close button on every dialog</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -26905,17 +26929,17 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Give the default close a hit area: 'grid h-8 w-8 place-items-center' around the icon (32px), keeping the icon at 16px. One change fixes every dialog at once.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>On desktop the close X is 16x16px - the bare icon with no padding. On mobile the same control measures 44x44, so the fault is desktop-only. It comes from the shared dialog component, so it applies to every dialog that keeps the default close: Add member, Edit access, the invite link modal, and the rest of the app's dialogs that use it. The Team profile dialog avoids it by hiding the default and drawing its own 36px close.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>components/ui/dialog.jsx:37-41</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -26928,7 +26952,7 @@
     <row r="84" ht="82" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -26943,7 +26967,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -26958,17 +26982,17 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -26981,7 +27005,7 @@
     <row r="85" ht="82" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -26991,12 +27015,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -27011,17 +27035,17 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -27034,7 +27058,7 @@
     <row r="86" ht="82" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -27049,7 +27073,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -27064,17 +27088,17 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -27087,7 +27111,7 @@
     <row r="87" ht="82" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>OP-13</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -27102,7 +27126,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' and 'See all' links</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -27117,17 +27141,17 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -27140,7 +27164,7 @@
     <row r="88" ht="82" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>OP-14</t>
+          <t>OP-13</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -27155,7 +27179,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>AI Work Coach - error page</t>
+          <t>'Back to company' and 'See all' links</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -27170,17 +27194,17 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
+          <t>Give both links py-1.5 (or min-h-6 with inline-flex items-center) so the hit area reaches 24px without changing the look. Fix with OP-09 in one pass.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
+          <t>'Back to company' in the view-as banner is 109x16 on desktop and 117x20 on mobile - and it is the only way out of view-as mode other than the browser. 'See all' above 'Your open work' is 52x16 on desktop and 55x20 on mobile, on every non-owner's page. Same pattern as the 'View all' links in OP-09, on two screens OP-09 did not cover.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>pages/WorkCoach.js:36-57</t>
+          <t>pages/OperatingScore.js:133-139 (Back to company); the 'See all' link in the self view's open-work header</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -27193,7 +27217,7 @@
     <row r="89" ht="82" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>CR-09</t>
+          <t>OP-14</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -27203,12 +27227,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - Score with AI</t>
+          <t>AI Work Coach - error page</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -27223,17 +27247,17 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
+          <t>Branch the title too: 403 -&gt; 'Not allowed', 404 -&gt; 'Person not found', otherwise 'Couldn't load coaching'.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
+          <t>The page is titled 'Access denied' while its body says 'Couldn't load coaching - Something went wrong.' Nothing was denied: the owner may view anyone's coach, and the API answered 404 'Employee not found'. The title blames permissions for a missing person.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
+          <t>pages/WorkCoach.js:36-57</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -27246,7 +27270,7 @@
     <row r="90" ht="82" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>CR-13</t>
+          <t>CR-09</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -27261,7 +27285,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
+          <t>Contact profile (mobile) - Score with AI</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -27276,17 +27300,17 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
+          <t>Add a 'Score with AI' action to the mobile profile's action row, reusing the same POST /contacts/{id}/rescore mutation - or record that scoring is desktop-only by design.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
+          <t>Desktop has 'Score with AI' (and 'Re-score'); its failure path works - 'Could not score right now', label restored. The mobile contact profile has no scoring control at all, only a read-only 'Health nn/100' row, so the score cannot be refreshed from a phone.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
+          <t>pages/ContactProfile.js:134-137 + :250-273 (desktop); pages/mobile/ContactProfileMobile.jsx:254 (Health row only)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -27299,7 +27323,7 @@
     <row r="91" ht="82" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>CR-14</t>
+          <t>CR-13</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -27314,7 +27338,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - 'Back to CRM' (desktop)</t>
+          <t>Decision Desk 'Complaints' tile -&gt; /crm</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -27329,17 +27353,17 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>py-1 or min-h-6 on the back link.</t>
+          <t>Only set the link when hasPerm(user, 'people'); otherwise render the tile as plain (non-link) or point it at a view the role can open.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
+          <t>CRM itself is correctly hidden and a direct visit shows Access Denied - but the 'Complaints' KPI tile on Decision Desk links to /crm for all three roles, on desktop and mobile. Tapping the number lands on 'ACCESS DENIED'. It is the most prominent link on their home screen to a page they are not allowed to see.</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js:205 (profile-back)</t>
+          <t>pages/Desk.js:569-572 (mobile tile), :614-617 (desktop tile)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -27352,7 +27376,7 @@
     <row r="92" ht="82" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FN-10</t>
+          <t>CR-14</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -27362,12 +27386,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Mobile capture card - 'Export' tile</t>
+          <t>Contact profile - 'Back to CRM' (desktop)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -27382,17 +27406,17 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
+          <t>py-1 or min-h-6 on the back link.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
+          <t>'Back to CRM' is 103x20 - the only other interactive element under 24px on the page. The mobile 'Back to people' is fine.</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1430-1437</t>
+          <t>pages/ContactProfile.js:205 (profile-back)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -27405,7 +27429,7 @@
     <row r="93" ht="82" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>FN-11</t>
+          <t>FN-10</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -27420,7 +27444,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Mobile overview - 'View all 3+ action items'</t>
+          <t>Mobile capture card - 'Export' tile</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -27435,17 +27459,17 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>py-1 on the link.</t>
+          <t>Rename it 'Import - CSV, Excel' with an upload icon. If export is wanted, build it as a separate action.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
+          <t>The fourth tile reads 'Export - CSV, Excel' but is a file picker that UPLOADS a spreadsheet to /ingest/csv. An owner wanting to download their books for the accountant taps it and gets a file-open dialog. Desktop labels the same control correctly as 'CSV / Excel' under Capture. There is no export anywhere on the page.</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
+          <t>pages/Ledger.js:1430-1437</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -27458,7 +27482,7 @@
     <row r="94" ht="82" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>FN-11</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -27468,12 +27492,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Mobile overview - 'View all 3+ action items'</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -27488,17 +27512,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>py-1 on the link.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>'View all 3+ action items' is 322x20 - wide but under 24px tall. It works (opens the Revenue tab).</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Ledger.js:1075 (ledger-mobile-viewall)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -27511,7 +27535,7 @@
     <row r="95" ht="82" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FN-12</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -27521,12 +27545,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Ask AI about your expenses - answer</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -27541,17 +27565,17 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Render the answer through the same markdown renderer Dex uses (or strip ** server-side).</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>The answer is correct - Surat Spinners, Rs 4,80,000, matching the data - but it is shown with literal markdown: '**Surat Spinners**' and '**Rs 4,80,000**', asterisks visible.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>pages/Ledger.js:539 (ai-answer)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -27564,7 +27588,7 @@
     <row r="96" ht="82" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FN-13</t>
+          <t>FN-12</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -27579,7 +27603,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Capture - extraction review</t>
+          <t>Ask AI about your expenses - answer</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -27594,17 +27618,17 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Carry invoice date, GSTIN (and GST amount) and line items through to review; flag bills whose date or due date is more than ~12 months old before 'File it'.</t>
+          <t>Render the answer through the same markdown renderer Dex uses (or strip ** server-side).</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Good overall, in 31.9s at 92% confidence: supplier Service TEST 123 with phone and email, number X33, amount 27,625, due 2018-03-01, booked as Inventory, and a 'Pay vendor bill' follow-up task. But the invoice DATE, the supplier GSTIN and the line items are not captured, and nothing warns that the bill fell due eight years ago - filing it would add an overdue payable dated 2018 without comment.</t>
+          <t>The answer is correct - Surat Spinners, Rs 4,80,000, matching the data - but it is shown with literal markdown: '**Surat Spinners**' and '**Rs 4,80,000**', asterisks visible.</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>pages/finance/ReviewPanel.js; services/ingestion.py (ai_extract_document)</t>
+          <t>pages/Ledger.js:539 (ai-answer)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -27617,7 +27641,7 @@
     <row r="97" ht="82" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GL-03</t>
+          <t>FN-13</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -27627,12 +27651,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>/login while signed in</t>
+          <t>Capture - extraction review</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -27647,17 +27671,17 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
+          <t>Carry invoice date, GSTIN (and GST amount) and line items through to review; flag bills whose date or due date is more than ~12 months old before 'File it'.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
+          <t>Good overall, in 31.9s at 92% confidence: supplier Service TEST 123 with phone and email, number X33, amount 27,625, due 2018-03-01, booked as Inventory, and a 'Pay vendor bill' follow-up task. But the invoice DATE, the supplier GSTIN and the line items are not captured, and nothing warns that the bill fell due eight years ago - filing it would add an overdue payable dated 2018 without comment.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js (component top)</t>
+          <t>pages/finance/ReviewPanel.js; services/ingestion.py (ai_extract_document)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -27670,7 +27694,7 @@
     <row r="98" ht="82" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>DD-04</t>
+          <t>GL-03</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -27680,12 +27704,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Decision Desk</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Company / You switch (mobile)</t>
+          <t>/login while signed in</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -27700,17 +27724,17 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Show the joined pill pair above the score below lg.</t>
+          <t>If the auth context has a user, &lt;Navigate to='/app' replace/&gt; (the same hand-off Home already uses).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
+          <t>The sign-in form is shown again. A user following an old bookmark or a 'Sign in' link sees a login screen while already logged in.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
+          <t>pages/Login.js (component top)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -27723,7 +27747,7 @@
     <row r="99" ht="82" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>DD-05</t>
+          <t>DD-04</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -27738,7 +27762,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Decision review - note mic</t>
+          <t>Company / You switch (mobile)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -27753,17 +27777,17 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
+          <t>Show the joined pill pair above the score below lg.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
+          <t>Both copies of the Company / You pills are in the DOM but invisible at phone width, so the phone only ever shows the company score.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js:421-445</t>
+          <t>pages/Desk.js:426 and :470 (scope pill placements)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -27776,7 +27800,7 @@
     <row r="100" ht="82" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>CL-03</t>
+          <t>DD-05</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -27786,12 +27810,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Decision Desk</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Mark all read</t>
+          <t>Decision review - note mic</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -27806,17 +27830,17 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>toast.error('Couldn't mark notifications read') in onError.</t>
+          <t>Wire it to the same capture Dex uses, or remove the mic and its helper line until it is.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
+          <t>It only shows a toast: 'Voice capture is available from the Dex panel'. The button and the helper line invite an action the page does not do.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>pages/Notifications.js:17-21</t>
+          <t>components/DecisionDialog.js:421-445</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -27829,7 +27853,7 @@
     <row r="101" ht="82" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>CL-04</t>
+          <t>CL-03</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -27839,12 +27863,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Operations tab - add links</t>
+          <t>Mark all read</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -27859,17 +27883,17 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>py-1 / min-h-6 on both.</t>
+          <t>toast.error('Couldn't mark notifications read') in onError.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
+          <t>Nothing happens and nothing is said - no toast, the unread dots stay - so the user cannot tell whether it worked.</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
+          <t>pages/Notifications.js:17-21</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
@@ -27882,7 +27906,7 @@
     <row r="102" ht="82" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AU-01</t>
+          <t>CL-04</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -27892,12 +27916,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Sign-in</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Login, sign-up and admin fields</t>
+          <t>Operations tab - add links</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -27912,17 +27936,17 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
+          <t>py-1 / min-h-6 on both.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
+          <t>'Add operational task' (149x20) and 'Add approval rule' (131x20) are under 24px.</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
+          <t>pages/Settings.js (OperatingModelEditor add buttons)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -27935,7 +27959,7 @@
     <row r="103" ht="82" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AU-02</t>
+          <t>AU-01</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -27950,7 +27974,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Mobile OTP - phone number</t>
+          <t>Login, sign-up and admin fields</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -27965,17 +27989,17 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
+          <t>Add labels (visually hidden where the design has none). Same fix as TM-06.</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
+          <t>Login email and password, the sign-up company name, and the admin email and password have no associated label or aria-label. The admin screen shows the words EMAIL and PASSWORD but they are not tied to the inputs.</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:179-190, :317</t>
+          <t>pages/Login.js:298-299, pages/Signup.js (basics), pages/admin/AdminLogin.js:44-57</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
@@ -27988,7 +28012,7 @@
     <row r="104" ht="82" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AU-03</t>
+          <t>AU-02</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -28003,7 +28027,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Login - header links (desktop)</t>
+          <t>Mobile OTP - phone number</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -28018,17 +28042,17 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>py-1 on both links.</t>
+          <t>Require 10 digits (after stripping +91 / spaces) before enabling Send, and say 'Enter a 10-digit mobile number'.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
+          <t>The 3-digit number is sent to the server; with no provider reachable the user only sees 'Something went wrong. Please try again.', which does not tell them the number is wrong.</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>pages/Login.js:241-246</t>
+          <t>pages/Login.js:179-190, :317</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -28041,7 +28065,7 @@
     <row r="105" ht="82" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>AU-03</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -28051,12 +28075,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Sign-in</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Login - header links (desktop)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -28064,24 +28088,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>py-1 on both links.</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>The 'DecisionOS' logo link is 91x21 and 'Need a workspace? Register' is 194x20.</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/Login.js:241-246</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
@@ -28094,7 +28118,7 @@
     <row r="106" ht="82" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -28104,12 +28128,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -28124,17 +28148,17 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
@@ -28147,7 +28171,7 @@
     <row r="107" ht="82" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -28157,12 +28181,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -28177,17 +28201,17 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
@@ -28200,7 +28224,7 @@
     <row r="108" ht="82" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -28215,7 +28239,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -28230,17 +28254,17 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
@@ -28253,7 +28277,7 @@
     <row r="109" ht="82" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -28268,7 +28292,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -28283,17 +28307,17 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
@@ -28306,7 +28330,7 @@
     <row r="110" ht="82" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-04</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -28316,12 +28340,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Member profile dialog</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -28336,17 +28360,17 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
@@ -28359,58 +28383,111 @@
     <row r="111" ht="82" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="82" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F112" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="4" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K111"/>
+  <autoFilter ref="A1:K112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28421,7 +28498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28429,552 +28506,564 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr"/>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr"/>
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>ASK numbers in commit messages do not match this workbook</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="12" t="inlineStr"/>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr"/>
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Found 2026-09-13 while verifying the 9 commits pulled that day. No decision needed - a bookkeeping hazard to fix before it causes a wrong status change.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr"/>
-      <c r="B3" s="16" t="inlineStr"/>
+      <c r="A3" s="16" t="inlineStr"/>
+      <c r="B3" s="17" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="17" t="inlineStr"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr"/>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>WHAT HAPPENED</t>
         </is>
       </c>
     </row>
     <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="15" t="inlineStr"/>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr"/>
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Only 5105ed1 (ASK-11) uses this workbook's numbering. The other commits label their work ASK-13, ASK-14, ASK-15, ASK-16 and ASK-17, but in this workbook those IDs are TEAM asks (stop showing access, redesign Add member, gate Edit access, org chart, member card data). The commits are all My Work / Workflows changes - uniform grid and dropdowns, the segmented slider, the task drawer, the Workflows board, the drawer close tab - taken from a different list of founder asks.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>The Team asks ASK-13 to ASK-17 are still To do; nothing in those commits touches Team.js. Anyone matching commits to this sheet by ID would wrongly close five Team items.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Suggest</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Use this workbook as the one numbering source, or prefix the other list (e.g. FA-13) so the two cannot collide.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Dex owner</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Founder call 2026-09-13: every Dex issue (DX-01, DX-02, DD-05 and anything found later in Dex) is taken over by Yokesh - tracked as ASK-23 with status 'Assigned - Yokesh'. Do not work on them outside his work; Finance AI, coach, rescore and extraction are not part of that hand-over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Still happening. Later commits label ASK-18 (Workflows well), ASK-19 (card summary), ASK-20 (My Work scroll) and ASK-21 (New Task dialog) from the other list. In this workbook ASK-18 is the CRM In-progress list, ASK-19 the operating score KPIs, and ASK-20 / ASK-21 / ASK-22 are the three root causes from the full audit (load errors, permission map, phone parity). Match commits to this sheet by content, not by number.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr"/>
-      <c r="B9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="B10" s="13" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr"/>
+      <c r="B10" s="17" t="inlineStr"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="13" t="inlineStr"/>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Leave approvals: who approves, and is the Settings screen needed?</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="B11" s="14" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="13" t="inlineStr"/>
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Raised 2026-09-12 by Yogesh - Owner. Status: DEFERRED, Yogesh deciding. Relates to ASK-8. Nothing is to be built from this note until that call is made.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr"/>
-      <c r="B12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="17" t="inlineStr"/>
-      <c r="B13" s="18" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr"/>
+      <c r="B13" s="17" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="18" t="inlineStr"/>
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>THE QUESTION</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="15" t="inlineStr"/>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="16" t="inlineStr"/>
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Leave approval is mostly done by either the owner or a manager. The approver is already chosen when a team member is added. So does the 'Leave Approvers by Department' settings screen need to exist at all?</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr"/>
-      <c r="B15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="17" t="inlineStr"/>
-      <c r="B16" s="18" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr"/>
+      <c r="B16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="18" t="inlineStr"/>
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>HOW APPROVAL IS DECIDED TODAY</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="15" t="inlineStr"/>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="16" t="inlineStr"/>
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>When someone requests leave the system asks three questions IN ORDER and stops at the first that answers. The code is services/leave.py, _resolve_leave_approver.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Does this person have a Reporting Manager? If yes, that manager approves. The Reporting Manager is chosen in Team when the member is added or edited (pages/Team.js:144, the member-manager-select dropdown; stored as reporting_manager_id).</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Otherwise: is there a department rule for their role? If yes, that person approves. THIS IS THE SETTINGS SCREEN under discussion - the gear in the Leave section, which opens 'Leave Approvers by Department' with one dropdown per department and a Save button.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Otherwise the Owner approves.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr"/>
-      <c r="B21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="17" t="inlineStr"/>
-      <c r="B22" s="18" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr"/>
+      <c r="B22" s="17" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="18" t="inlineStr"/>
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>WHAT THE LIVE DATA SHOWS</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr"/>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Measured against the dev workspace on 2026-09-12, not assumed:</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Members</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>12 team members in the workspace.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Tier 1 used</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>1 member has a Reporting Manager set (sai, finance).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Tier 2 used</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>0. The tenant leave_approvers mapping is EMPTY - every department reads 'Owner (default)'.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Tier 3 used</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>11 of 12 members fall through to the Owner, Rajesh Sharma.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>The Settings screen currently decides leave for NOBODY. It configures a tier that no request reaches.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr"/>
-      <c r="B29" s="16" t="inlineStr"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="18" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr"/>
+      <c r="B30" s="17" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="18" t="inlineStr"/>
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>WHAT THE THREE PIECES ARE</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="15" t="inlineStr"/>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="16" t="inlineStr"/>
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>They are three layers of one feature. Removing one without the others leaves either a screen that cannot save or an endpoint nothing calls.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>The gear</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>The small round icon beside the My Leave / Approvals tabs. It is the only way into the screen. pages/Leave.js:500-510.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>The panel</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>'Leave Approvers by Department' - a dropdown per department plus a Save approvers button. pages/Leave.js:387-417.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>The endpoint</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>PATCH /tenant/leave-approvers, which writes the leave_approvers field on the tenant record. routers/calendar.py:24.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr"/>
-      <c r="B35" s="16" t="inlineStr"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="17" t="inlineStr"/>
-      <c r="B36" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr"/>
+      <c r="B36" s="17" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="18" t="inlineStr"/>
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>OPTION A - DELETE TIER 2  (the current recommendation)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>What changes</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>Remove the gear, the panel and the endpoint. Approval becomes: reporting manager, else owner.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Effect today</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>NONE. Every one of the 12 members resolves to exactly the same approver before and after, because nothing uses tier 2.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="45" customHeight="1">
-      <c r="A39" s="15" t="inlineStr">
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Argument for</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>The approver is already chosen once, in Team, when the person is added. A second screen expressing the same decision in different words - and silently losing to the first one - mostly creates the chance for the two to disagree with the org chart.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr"/>
-      <c r="B40" s="16" t="inlineStr"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="17" t="inlineStr"/>
-      <c r="B41" s="18" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr"/>
+      <c r="B41" s="17" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="18" t="inlineStr"/>
+      <c r="B42" s="19" t="inlineStr">
         <i